--- a/template/DS_FTX_Automation_Summary.xlsx
+++ b/template/DS_FTX_Automation_Summary.xlsx
@@ -3,12 +3,12 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="71" documentId="13_ncr:1_{3921D751-0C97-4068-A9FE-A5F6B4B236B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1DE72655-055E-488B-AF82-C1E7EEA23898}"/>
+  <xr:revisionPtr revIDLastSave="77" documentId="13_ncr:1_{3921D751-0C97-4068-A9FE-A5F6B4B236B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4C70AB01-37CB-4487-BC16-B0A54B32E5AC}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="DS-FTX Summary Test Results" sheetId="2" r:id="rId1"/>
+    <sheet name="DS_FTX Summary Test Results" sheetId="2" r:id="rId1"/>
     <sheet name="DS_FTX_Reconcile" sheetId="7" r:id="rId2"/>
     <sheet name="DS_FTX " sheetId="6" r:id="rId3"/>
     <sheet name="Test Data" sheetId="4" r:id="rId4"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1517" uniqueCount="480">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1521" uniqueCount="484">
   <si>
     <t>Report File Name:</t>
   </si>
@@ -59,12 +59,6 @@
     <t>2026-07-21</t>
   </si>
   <si>
-    <t>Execution Time:</t>
-  </si>
-  <si>
-    <t>09:27:00</t>
-  </si>
-  <si>
     <t>Run ID:</t>
   </si>
   <si>
@@ -461,9 +455,6 @@
     <t>DS_FTX</t>
   </si>
   <si>
-    <t>DS_FTX_Compare_Result_20260721_092700.xlsx</t>
-  </si>
-  <si>
     <t>DEPT CODE</t>
   </si>
   <si>
@@ -1479,13 +1470,37 @@
   </si>
   <si>
     <t>From Debit Amount</t>
+  </si>
+  <si>
+    <t>ACTUAL 
+(Execution %)</t>
+  </si>
+  <si>
+    <t>PASSED
+(Pass Rate %)</t>
+  </si>
+  <si>
+    <t>FAILED 
+(Fail Rate%)</t>
+  </si>
+  <si>
+    <t>DS_LTX Summary Test Results_20260721_092700.xlsx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Actual Execution Time Start : </t>
+  </si>
+  <si>
+    <t>Actual Execution Time End:</t>
+  </si>
+  <si>
+    <t>Duration Time:</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="26">
+  <fonts count="29">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1658,14 +1673,38 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="23">
+  <fills count="25">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1790,8 +1829,20 @@
         <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1" tint="0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE53935"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="26">
+  <borders count="29">
     <border>
       <left/>
       <right/>
@@ -2108,11 +2159,53 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD9D9D9"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FFD9D9D9"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD9D9D9"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD9D9D9"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD9D9D9"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFD9D9D9"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="26" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="74">
+  <cellXfs count="80">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -2252,6 +2345,9 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2264,27 +2360,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="11" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2298,18 +2378,46 @@
     <xf numFmtId="0" fontId="16" fillId="11" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="27" fillId="23" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="14" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="24" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="27" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="27" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="27" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
+    <xf numFmtId="21" fontId="28" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2322,10 +2430,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2617,7 +2721,7 @@
     <tabColor rgb="FF002060"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:Z27"/>
+  <dimension ref="B1:Z29"/>
   <sheetFormatPr defaultRowHeight="14.45" customHeight="1" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -2655,34 +2759,34 @@
       <c r="L1" s="1"/>
     </row>
     <row r="2" spans="2:26" ht="28.5" customHeight="1">
-      <c r="B2" s="57" t="s">
-        <v>478</v>
-      </c>
-      <c r="C2" s="58"/>
-      <c r="D2" s="58"/>
-      <c r="E2" s="58"/>
-      <c r="F2" s="58"/>
-      <c r="G2" s="58"/>
-      <c r="H2" s="58"/>
-      <c r="I2" s="58"/>
-      <c r="J2" s="58"/>
-      <c r="K2" s="58"/>
-      <c r="L2" s="58"/>
+      <c r="B2" s="58" t="s">
+        <v>475</v>
+      </c>
+      <c r="C2" s="59"/>
+      <c r="D2" s="59"/>
+      <c r="E2" s="59"/>
+      <c r="F2" s="59"/>
+      <c r="G2" s="59"/>
+      <c r="H2" s="59"/>
+      <c r="I2" s="59"/>
+      <c r="J2" s="59"/>
+      <c r="K2" s="59"/>
+      <c r="L2" s="59"/>
     </row>
     <row r="3" spans="2:26" ht="15" customHeight="1">
-      <c r="B3" s="58"/>
-      <c r="C3" s="58"/>
-      <c r="D3" s="58"/>
-      <c r="E3" s="58"/>
-      <c r="F3" s="58"/>
-      <c r="G3" s="58"/>
-      <c r="H3" s="58"/>
-      <c r="I3" s="58"/>
-      <c r="J3" s="58"/>
-      <c r="K3" s="58"/>
-      <c r="L3" s="58"/>
+      <c r="B3" s="59"/>
+      <c r="C3" s="59"/>
+      <c r="D3" s="59"/>
+      <c r="E3" s="59"/>
+      <c r="F3" s="59"/>
+      <c r="G3" s="59"/>
+      <c r="H3" s="59"/>
+      <c r="I3" s="59"/>
+      <c r="J3" s="59"/>
+      <c r="K3" s="59"/>
+      <c r="L3" s="59"/>
     </row>
-    <row r="4" spans="2:26" ht="15" customHeight="1" outlineLevel="1" collapsed="1">
+    <row r="4" spans="2:26" ht="36.75" customHeight="1" outlineLevel="1" collapsed="1">
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
@@ -2690,271 +2794,319 @@
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
       <c r="H4" s="1"/>
-      <c r="I4" s="1"/>
-      <c r="J4" s="1"/>
-      <c r="K4" s="1"/>
-      <c r="L4" s="1"/>
+      <c r="I4" s="66"/>
+      <c r="J4" s="67" t="s">
+        <v>477</v>
+      </c>
+      <c r="K4" s="68" t="s">
+        <v>478</v>
+      </c>
+      <c r="L4" s="69" t="s">
+        <v>479</v>
+      </c>
+      <c r="M4" s="69"/>
     </row>
-    <row r="5" spans="2:26" ht="15" customHeight="1" outlineLevel="1" collapsed="1">
-      <c r="B5" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>140</v>
-      </c>
+    <row r="5" spans="2:26" ht="15" customHeight="1" outlineLevel="1">
+      <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
       <c r="E5" s="1"/>
       <c r="F5" s="1"/>
       <c r="G5" s="1"/>
       <c r="H5" s="1"/>
-      <c r="I5" s="1"/>
-      <c r="J5" s="61" t="s">
+      <c r="I5" s="66"/>
+      <c r="J5" s="70">
+        <f>J8/(J8-0)</f>
         <v>1</v>
       </c>
-      <c r="K5" s="63" t="s">
-        <v>2</v>
-      </c>
-      <c r="L5" s="59" t="s">
-        <v>3</v>
-      </c>
-      <c r="M5" s="60"/>
+      <c r="K5" s="71">
+        <f>K8/J8</f>
+        <v>0.92307692307692313</v>
+      </c>
+      <c r="L5" s="72">
+        <f>L8/J8</f>
+        <v>7.6923076923076927E-2</v>
+      </c>
+      <c r="M5" s="72"/>
     </row>
     <row r="6" spans="2:26" ht="15" customHeight="1" outlineLevel="1" collapsed="1">
       <c r="B6" s="2" t="s">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>5</v>
+        <v>480</v>
       </c>
       <c r="E6" s="1"/>
       <c r="F6" s="1"/>
       <c r="G6" s="1"/>
       <c r="H6" s="1"/>
-      <c r="I6" s="1"/>
-      <c r="J6" s="62"/>
-      <c r="K6" s="62"/>
-      <c r="L6" s="59"/>
-      <c r="M6" s="60"/>
+      <c r="I6" s="66"/>
+      <c r="J6" s="73" t="s">
+        <v>1</v>
+      </c>
+      <c r="K6" s="74" t="s">
+        <v>2</v>
+      </c>
+      <c r="L6" s="75" t="s">
+        <v>3</v>
+      </c>
+      <c r="M6" s="75"/>
     </row>
     <row r="7" spans="2:26" ht="15" customHeight="1" outlineLevel="1" collapsed="1">
       <c r="B7" s="2" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E7" s="1"/>
       <c r="F7" s="1"/>
       <c r="G7" s="1"/>
       <c r="H7" s="1"/>
-      <c r="I7" s="1"/>
-      <c r="J7" s="66">
-        <v>13</v>
-      </c>
-      <c r="K7" s="66">
-        <v>12</v>
-      </c>
-      <c r="L7" s="64">
-        <v>1</v>
-      </c>
-      <c r="M7" s="65"/>
+      <c r="I7" s="66"/>
+      <c r="J7" s="76"/>
+      <c r="K7" s="76"/>
+      <c r="L7" s="75"/>
+      <c r="M7" s="75"/>
     </row>
-    <row r="8" spans="2:26" ht="15" customHeight="1" outlineLevel="1" collapsed="1">
+    <row r="8" spans="2:26" ht="15" customHeight="1" outlineLevel="1">
       <c r="B8" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>9</v>
+        <v>481</v>
+      </c>
+      <c r="C8" s="77">
+        <v>0.37552083333333336</v>
       </c>
       <c r="E8" s="1"/>
       <c r="F8" s="1"/>
       <c r="G8" s="1"/>
       <c r="H8" s="1"/>
-      <c r="I8" s="1"/>
-      <c r="J8" s="62"/>
-      <c r="K8" s="62"/>
-      <c r="L8" s="64"/>
-      <c r="M8" s="65"/>
+      <c r="I8" s="66"/>
+      <c r="J8" s="78">
+        <v>13</v>
+      </c>
+      <c r="K8" s="78">
+        <v>12</v>
+      </c>
+      <c r="L8" s="78">
+        <v>1</v>
+      </c>
+      <c r="M8" s="78"/>
     </row>
-    <row r="9" spans="2:26" ht="15" customHeight="1" outlineLevel="1" collapsed="1">
+    <row r="9" spans="2:26" ht="15" customHeight="1" outlineLevel="1">
       <c r="B9" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>11</v>
+        <v>482</v>
+      </c>
+      <c r="C9" s="77">
+        <v>0.39149305555555558</v>
       </c>
       <c r="E9" s="1"/>
       <c r="F9" s="1"/>
       <c r="G9" s="1"/>
       <c r="H9" s="1"/>
-      <c r="I9" s="1"/>
-      <c r="J9" s="62"/>
-      <c r="K9" s="62"/>
-      <c r="L9" s="64"/>
-      <c r="M9" s="65"/>
+      <c r="I9" s="66"/>
+      <c r="J9" s="78"/>
+      <c r="K9" s="78"/>
+      <c r="L9" s="78"/>
+      <c r="M9" s="78"/>
     </row>
     <row r="10" spans="2:26" ht="15" customHeight="1" outlineLevel="1" collapsed="1">
-      <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
-      <c r="D10" s="1"/>
+      <c r="B10" s="2" t="s">
+        <v>483</v>
+      </c>
+      <c r="C10" s="77">
+        <v>1.5972222222222221E-2</v>
+      </c>
       <c r="E10" s="1"/>
       <c r="F10" s="1"/>
       <c r="G10" s="1"/>
       <c r="H10" s="1"/>
-      <c r="I10" s="1"/>
-      <c r="J10" s="1"/>
-      <c r="K10" s="1"/>
-      <c r="L10" s="1"/>
+      <c r="I10" s="66"/>
+      <c r="J10" s="78"/>
+      <c r="K10" s="78"/>
+      <c r="L10" s="78"/>
+      <c r="M10" s="78"/>
     </row>
     <row r="11" spans="2:26" ht="15" customHeight="1" outlineLevel="1" collapsed="1">
-      <c r="B11" s="1"/>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
+      <c r="B11" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>7</v>
+      </c>
       <c r="E11" s="1"/>
       <c r="F11" s="1"/>
       <c r="G11" s="1"/>
       <c r="H11" s="1"/>
-      <c r="I11" s="1"/>
-      <c r="J11" s="1"/>
-      <c r="K11" s="1"/>
-      <c r="L11" s="1"/>
+      <c r="I11" s="66"/>
+      <c r="J11" s="78"/>
+      <c r="K11" s="78"/>
+      <c r="L11" s="78"/>
+      <c r="M11" s="78"/>
     </row>
-    <row r="12" spans="2:26" ht="15.75" customHeight="1" thickBot="1">
-      <c r="B12" s="54" t="s">
+    <row r="12" spans="2:26" ht="15" customHeight="1" outlineLevel="1" collapsed="1">
+      <c r="B12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E12" s="1"/>
+      <c r="F12" s="1"/>
+      <c r="G12" s="1"/>
+      <c r="H12" s="1"/>
+      <c r="I12" s="66"/>
+      <c r="J12" s="78"/>
+      <c r="K12" s="78"/>
+      <c r="L12" s="78"/>
+      <c r="M12" s="78"/>
+    </row>
+    <row r="13" spans="2:26" ht="15" customHeight="1" outlineLevel="1" collapsed="1">
+      <c r="B13" s="1"/>
+      <c r="C13" s="1"/>
+      <c r="D13" s="1"/>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1"/>
+      <c r="G13" s="1"/>
+      <c r="H13" s="1"/>
+      <c r="I13" s="1"/>
+      <c r="J13" s="79"/>
+      <c r="K13" s="79"/>
+      <c r="L13" s="79"/>
+    </row>
+    <row r="14" spans="2:26" ht="15.75" customHeight="1" thickBot="1">
+      <c r="B14" s="54" t="s">
+        <v>10</v>
+      </c>
+      <c r="C14" s="55"/>
+      <c r="D14" s="55"/>
+      <c r="E14" s="55"/>
+      <c r="F14" s="55"/>
+      <c r="G14" s="55"/>
+      <c r="H14" s="55"/>
+      <c r="I14" s="55"/>
+      <c r="J14" s="55"/>
+      <c r="K14" s="55"/>
+      <c r="L14" s="55"/>
+      <c r="M14" s="55"/>
+      <c r="N14" s="55"/>
+      <c r="O14" s="55"/>
+      <c r="P14" s="55"/>
+      <c r="Q14" s="55"/>
+      <c r="R14" s="55"/>
+      <c r="S14" s="55"/>
+      <c r="T14" s="55"/>
+      <c r="U14" s="55"/>
+      <c r="V14" s="55"/>
+      <c r="W14" s="55"/>
+      <c r="X14" s="55"/>
+      <c r="Y14" s="55"/>
+      <c r="Z14" s="55"/>
+    </row>
+    <row r="15" spans="2:26" ht="21.75" customHeight="1" thickBot="1">
+      <c r="B15" s="60" t="s">
+        <v>137</v>
+      </c>
+      <c r="C15" s="60"/>
+      <c r="D15" s="60"/>
+      <c r="E15" s="60"/>
+      <c r="F15" s="60"/>
+      <c r="G15" s="60"/>
+      <c r="H15" s="60"/>
+      <c r="I15" s="60"/>
+      <c r="J15" s="60"/>
+      <c r="K15" s="61"/>
+      <c r="L15" s="3"/>
+      <c r="M15" s="56" t="s">
+        <v>11</v>
+      </c>
+      <c r="N15" s="57"/>
+      <c r="O15" s="57"/>
+      <c r="P15" s="57"/>
+      <c r="Q15" s="57"/>
+      <c r="R15" s="57"/>
+      <c r="S15" s="57"/>
+      <c r="T15" s="57"/>
+      <c r="U15" s="57"/>
+      <c r="V15" s="57"/>
+      <c r="W15" s="57"/>
+      <c r="X15" s="57"/>
+      <c r="Y15" s="57"/>
+      <c r="Z15" s="57"/>
+    </row>
+    <row r="16" spans="2:26" s="4" customFormat="1" ht="45" customHeight="1">
+      <c r="B16" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C12" s="71"/>
-      <c r="D12" s="71"/>
-      <c r="E12" s="71"/>
-      <c r="F12" s="71"/>
-      <c r="G12" s="71"/>
-      <c r="H12" s="71"/>
-      <c r="I12" s="71"/>
-      <c r="J12" s="71"/>
-      <c r="K12" s="71"/>
-      <c r="L12" s="71"/>
-      <c r="M12" s="71"/>
-      <c r="N12" s="71"/>
-      <c r="O12" s="71"/>
-      <c r="P12" s="71"/>
-      <c r="Q12" s="71"/>
-      <c r="R12" s="71"/>
-      <c r="S12" s="71"/>
-      <c r="T12" s="71"/>
-      <c r="U12" s="71"/>
-      <c r="V12" s="71"/>
-      <c r="W12" s="71"/>
-      <c r="X12" s="71"/>
-      <c r="Y12" s="71"/>
-      <c r="Z12" s="71"/>
+      <c r="C16" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E16" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="F16" s="8" t="s">
+        <v>148</v>
+      </c>
+      <c r="G16" s="8" t="s">
+        <v>169</v>
+      </c>
+      <c r="H16" s="8" t="s">
+        <v>171</v>
+      </c>
+      <c r="I16" s="8" t="s">
+        <v>172</v>
+      </c>
+      <c r="J16" s="8" t="s">
+        <v>174</v>
+      </c>
+      <c r="K16" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="L16" s="10"/>
+      <c r="M16" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="N16" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="O16" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="P16" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q16" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="R16" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="S16" s="15" t="s">
+        <v>476</v>
+      </c>
+      <c r="T16" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="U16" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="V16" s="53" t="s">
+        <v>73</v>
+      </c>
+      <c r="W16" s="53" t="s">
+        <v>74</v>
+      </c>
+      <c r="X16" s="53" t="s">
+        <v>87</v>
+      </c>
+      <c r="Y16" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="Z16" s="53" t="s">
+        <v>89</v>
+      </c>
     </row>
-    <row r="13" spans="2:26" ht="21.75" customHeight="1" thickBot="1">
-      <c r="B13" s="72" t="s">
-        <v>139</v>
-      </c>
-      <c r="C13" s="72"/>
-      <c r="D13" s="72"/>
-      <c r="E13" s="72"/>
-      <c r="F13" s="72"/>
-      <c r="G13" s="72"/>
-      <c r="H13" s="72"/>
-      <c r="I13" s="72"/>
-      <c r="J13" s="72"/>
-      <c r="K13" s="73"/>
-      <c r="L13" s="3"/>
-      <c r="M13" s="55" t="s">
-        <v>13</v>
-      </c>
-      <c r="N13" s="56"/>
-      <c r="O13" s="56"/>
-      <c r="P13" s="56"/>
-      <c r="Q13" s="56"/>
-      <c r="R13" s="56"/>
-      <c r="S13" s="56"/>
-      <c r="T13" s="56"/>
-      <c r="U13" s="56"/>
-      <c r="V13" s="56"/>
-      <c r="W13" s="56"/>
-      <c r="X13" s="56"/>
-      <c r="Y13" s="56"/>
-      <c r="Z13" s="56"/>
-    </row>
-    <row r="14" spans="2:26" s="4" customFormat="1" ht="45" customHeight="1">
-      <c r="B14" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="C14" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="D14" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="E14" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="F14" s="8" t="s">
-        <v>151</v>
-      </c>
-      <c r="G14" s="8" t="s">
-        <v>172</v>
-      </c>
-      <c r="H14" s="8" t="s">
-        <v>174</v>
-      </c>
-      <c r="I14" s="8" t="s">
-        <v>175</v>
-      </c>
-      <c r="J14" s="8" t="s">
-        <v>177</v>
-      </c>
-      <c r="K14" s="9" t="s">
-        <v>171</v>
-      </c>
-      <c r="L14" s="10"/>
-      <c r="M14" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="N14" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="O14" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="P14" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="Q14" s="14" t="s">
-        <v>64</v>
-      </c>
-      <c r="R14" s="14" t="s">
-        <v>24</v>
-      </c>
-      <c r="S14" s="15" t="s">
-        <v>479</v>
-      </c>
-      <c r="T14" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="U14" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="V14" s="53" t="s">
-        <v>75</v>
-      </c>
-      <c r="W14" s="53" t="s">
-        <v>76</v>
-      </c>
-      <c r="X14" s="53" t="s">
-        <v>89</v>
-      </c>
-      <c r="Y14" s="53" t="s">
-        <v>90</v>
-      </c>
-      <c r="Z14" s="53" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="15" spans="2:26" ht="36" customHeight="1"/>
-    <row r="16" spans="2:26" ht="36" customHeight="1"/>
     <row r="17" ht="36" customHeight="1"/>
     <row r="18" ht="36" customHeight="1"/>
     <row r="19" ht="36" customHeight="1"/>
@@ -2966,18 +3118,22 @@
     <row r="25" ht="36" customHeight="1"/>
     <row r="26" ht="36" customHeight="1"/>
     <row r="27" ht="36" customHeight="1"/>
+    <row r="28" ht="36" customHeight="1"/>
+    <row r="29" ht="36" customHeight="1"/>
   </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="B12:Z12"/>
-    <mergeCell ref="M13:Z13"/>
+  <mergeCells count="12">
+    <mergeCell ref="B14:Z14"/>
+    <mergeCell ref="M15:Z15"/>
     <mergeCell ref="B2:L3"/>
-    <mergeCell ref="L5:M6"/>
-    <mergeCell ref="J5:J6"/>
-    <mergeCell ref="K5:K6"/>
-    <mergeCell ref="L7:M9"/>
-    <mergeCell ref="J7:J9"/>
-    <mergeCell ref="K7:K9"/>
-    <mergeCell ref="B13:K13"/>
+    <mergeCell ref="L6:M7"/>
+    <mergeCell ref="J6:J7"/>
+    <mergeCell ref="K6:K7"/>
+    <mergeCell ref="B15:K15"/>
+    <mergeCell ref="L4:M4"/>
+    <mergeCell ref="L5:M5"/>
+    <mergeCell ref="J8:J12"/>
+    <mergeCell ref="K8:K12"/>
+    <mergeCell ref="L8:M12"/>
   </mergeCells>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
   <pageSetup paperSize="9" fitToHeight="0" orientation="landscape"/>
@@ -3079,286 +3235,286 @@
   <sheetData>
     <row r="1" spans="1:94" ht="55.15" customHeight="1">
       <c r="A1" s="51" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B1" s="51" t="s">
+        <v>31</v>
+      </c>
+      <c r="C1" s="51" t="s">
+        <v>32</v>
+      </c>
+      <c r="D1" s="51" t="s">
+        <v>138</v>
+      </c>
+      <c r="E1" s="51" t="s">
         <v>33</v>
       </c>
-      <c r="C1" s="51" t="s">
+      <c r="F1" s="51" t="s">
+        <v>139</v>
+      </c>
+      <c r="G1" s="51" t="s">
+        <v>37</v>
+      </c>
+      <c r="H1" s="51" t="s">
+        <v>38</v>
+      </c>
+      <c r="I1" s="51" t="s">
+        <v>15</v>
+      </c>
+      <c r="J1" s="51" t="s">
+        <v>140</v>
+      </c>
+      <c r="K1" s="51" t="s">
+        <v>141</v>
+      </c>
+      <c r="L1" s="51" t="s">
         <v>34</v>
       </c>
-      <c r="D1" s="51" t="s">
-        <v>141</v>
-      </c>
-      <c r="E1" s="51" t="s">
+      <c r="M1" s="51" t="s">
         <v>35</v>
       </c>
-      <c r="F1" s="51" t="s">
+      <c r="N1" s="51" t="s">
+        <v>36</v>
+      </c>
+      <c r="O1" s="51" t="s">
         <v>142</v>
       </c>
-      <c r="G1" s="51" t="s">
+      <c r="P1" s="51" t="s">
+        <v>143</v>
+      </c>
+      <c r="Q1" s="51" t="s">
+        <v>144</v>
+      </c>
+      <c r="R1" s="51" t="s">
+        <v>145</v>
+      </c>
+      <c r="S1" s="51" t="s">
+        <v>146</v>
+      </c>
+      <c r="T1" s="51" t="s">
+        <v>147</v>
+      </c>
+      <c r="U1" s="51" t="s">
+        <v>148</v>
+      </c>
+      <c r="V1" s="51" t="s">
+        <v>149</v>
+      </c>
+      <c r="W1" s="51" t="s">
+        <v>150</v>
+      </c>
+      <c r="X1" s="51" t="s">
+        <v>151</v>
+      </c>
+      <c r="Y1" s="51" t="s">
+        <v>152</v>
+      </c>
+      <c r="Z1" s="51" t="s">
+        <v>153</v>
+      </c>
+      <c r="AA1" s="51" t="s">
+        <v>154</v>
+      </c>
+      <c r="AB1" s="51" t="s">
+        <v>155</v>
+      </c>
+      <c r="AC1" s="51" t="s">
+        <v>16</v>
+      </c>
+      <c r="AD1" s="51" t="s">
+        <v>156</v>
+      </c>
+      <c r="AE1" s="51" t="s">
+        <v>157</v>
+      </c>
+      <c r="AF1" s="51" t="s">
+        <v>158</v>
+      </c>
+      <c r="AG1" s="51" t="s">
+        <v>159</v>
+      </c>
+      <c r="AH1" s="51" t="s">
+        <v>160</v>
+      </c>
+      <c r="AI1" s="51" t="s">
+        <v>161</v>
+      </c>
+      <c r="AJ1" s="51" t="s">
+        <v>162</v>
+      </c>
+      <c r="AK1" s="51" t="s">
+        <v>163</v>
+      </c>
+      <c r="AL1" s="51" t="s">
+        <v>164</v>
+      </c>
+      <c r="AM1" s="51" t="s">
+        <v>165</v>
+      </c>
+      <c r="AN1" s="51" t="s">
+        <v>166</v>
+      </c>
+      <c r="AO1" s="51" t="s">
+        <v>167</v>
+      </c>
+      <c r="AP1" s="51" t="s">
+        <v>168</v>
+      </c>
+      <c r="AQ1" s="51" t="s">
+        <v>169</v>
+      </c>
+      <c r="AR1" s="51" t="s">
+        <v>170</v>
+      </c>
+      <c r="AS1" s="51" t="s">
+        <v>171</v>
+      </c>
+      <c r="AT1" s="51" t="s">
+        <v>172</v>
+      </c>
+      <c r="AU1" s="51" t="s">
+        <v>173</v>
+      </c>
+      <c r="AV1" s="51" t="s">
+        <v>174</v>
+      </c>
+      <c r="AW1" s="51" t="s">
+        <v>175</v>
+      </c>
+      <c r="AX1" s="51" t="s">
+        <v>176</v>
+      </c>
+      <c r="AY1" s="51" t="s">
+        <v>177</v>
+      </c>
+      <c r="AZ1" s="51" t="s">
+        <v>178</v>
+      </c>
+      <c r="BA1" s="51" t="s">
+        <v>179</v>
+      </c>
+      <c r="BB1" s="51" t="s">
+        <v>180</v>
+      </c>
+      <c r="BC1" s="51" t="s">
+        <v>181</v>
+      </c>
+      <c r="BD1" s="51" t="s">
+        <v>182</v>
+      </c>
+      <c r="BE1" s="51" t="s">
+        <v>183</v>
+      </c>
+      <c r="BF1" s="51" t="s">
+        <v>184</v>
+      </c>
+      <c r="BG1" s="51" t="s">
+        <v>185</v>
+      </c>
+      <c r="BH1" s="51" t="s">
+        <v>186</v>
+      </c>
+      <c r="BI1" s="51" t="s">
+        <v>187</v>
+      </c>
+      <c r="BJ1" s="51" t="s">
+        <v>188</v>
+      </c>
+      <c r="BK1" s="51" t="s">
+        <v>189</v>
+      </c>
+      <c r="BL1" s="51" t="s">
+        <v>190</v>
+      </c>
+      <c r="BM1" s="51" t="s">
+        <v>191</v>
+      </c>
+      <c r="BN1" s="51" t="s">
+        <v>192</v>
+      </c>
+      <c r="BO1" s="51" t="s">
+        <v>193</v>
+      </c>
+      <c r="BP1" s="51" t="s">
+        <v>194</v>
+      </c>
+      <c r="BQ1" s="51" t="s">
+        <v>195</v>
+      </c>
+      <c r="BR1" s="51" t="s">
+        <v>196</v>
+      </c>
+      <c r="BS1" s="51" t="s">
+        <v>197</v>
+      </c>
+      <c r="BT1" s="51" t="s">
+        <v>198</v>
+      </c>
+      <c r="BU1" s="51" t="s">
+        <v>199</v>
+      </c>
+      <c r="BV1" s="51" t="s">
+        <v>200</v>
+      </c>
+      <c r="BW1" s="51" t="s">
+        <v>201</v>
+      </c>
+      <c r="BX1" s="51" t="s">
+        <v>202</v>
+      </c>
+      <c r="BY1" s="51" t="s">
+        <v>203</v>
+      </c>
+      <c r="BZ1" s="51" t="s">
+        <v>204</v>
+      </c>
+      <c r="CA1" s="51" t="s">
+        <v>205</v>
+      </c>
+      <c r="CB1" s="51" t="s">
+        <v>206</v>
+      </c>
+      <c r="CC1" s="51" t="s">
         <v>39</v>
       </c>
-      <c r="H1" s="51" t="s">
-        <v>40</v>
-      </c>
-      <c r="I1" s="51" t="s">
-        <v>17</v>
-      </c>
-      <c r="J1" s="51" t="s">
-        <v>143</v>
-      </c>
-      <c r="K1" s="51" t="s">
-        <v>144</v>
-      </c>
-      <c r="L1" s="51" t="s">
-        <v>36</v>
-      </c>
-      <c r="M1" s="51" t="s">
-        <v>37</v>
-      </c>
-      <c r="N1" s="51" t="s">
-        <v>38</v>
-      </c>
-      <c r="O1" s="51" t="s">
-        <v>145</v>
-      </c>
-      <c r="P1" s="51" t="s">
-        <v>146</v>
-      </c>
-      <c r="Q1" s="51" t="s">
-        <v>147</v>
-      </c>
-      <c r="R1" s="51" t="s">
-        <v>148</v>
-      </c>
-      <c r="S1" s="51" t="s">
-        <v>149</v>
-      </c>
-      <c r="T1" s="51" t="s">
-        <v>150</v>
-      </c>
-      <c r="U1" s="51" t="s">
-        <v>151</v>
-      </c>
-      <c r="V1" s="51" t="s">
-        <v>152</v>
-      </c>
-      <c r="W1" s="51" t="s">
-        <v>153</v>
-      </c>
-      <c r="X1" s="51" t="s">
-        <v>154</v>
-      </c>
-      <c r="Y1" s="51" t="s">
-        <v>155</v>
-      </c>
-      <c r="Z1" s="51" t="s">
-        <v>156</v>
-      </c>
-      <c r="AA1" s="51" t="s">
-        <v>157</v>
-      </c>
-      <c r="AB1" s="51" t="s">
-        <v>158</v>
-      </c>
-      <c r="AC1" s="51" t="s">
-        <v>18</v>
-      </c>
-      <c r="AD1" s="51" t="s">
-        <v>159</v>
-      </c>
-      <c r="AE1" s="51" t="s">
-        <v>160</v>
-      </c>
-      <c r="AF1" s="51" t="s">
-        <v>161</v>
-      </c>
-      <c r="AG1" s="51" t="s">
-        <v>162</v>
-      </c>
-      <c r="AH1" s="51" t="s">
-        <v>163</v>
-      </c>
-      <c r="AI1" s="51" t="s">
-        <v>164</v>
-      </c>
-      <c r="AJ1" s="51" t="s">
-        <v>165</v>
-      </c>
-      <c r="AK1" s="51" t="s">
-        <v>166</v>
-      </c>
-      <c r="AL1" s="51" t="s">
-        <v>167</v>
-      </c>
-      <c r="AM1" s="51" t="s">
-        <v>168</v>
-      </c>
-      <c r="AN1" s="51" t="s">
-        <v>169</v>
-      </c>
-      <c r="AO1" s="51" t="s">
-        <v>170</v>
-      </c>
-      <c r="AP1" s="51" t="s">
-        <v>171</v>
-      </c>
-      <c r="AQ1" s="51" t="s">
-        <v>172</v>
-      </c>
-      <c r="AR1" s="51" t="s">
-        <v>173</v>
-      </c>
-      <c r="AS1" s="51" t="s">
-        <v>174</v>
-      </c>
-      <c r="AT1" s="51" t="s">
-        <v>175</v>
-      </c>
-      <c r="AU1" s="51" t="s">
-        <v>176</v>
-      </c>
-      <c r="AV1" s="51" t="s">
-        <v>177</v>
-      </c>
-      <c r="AW1" s="51" t="s">
-        <v>178</v>
-      </c>
-      <c r="AX1" s="51" t="s">
-        <v>179</v>
-      </c>
-      <c r="AY1" s="51" t="s">
-        <v>180</v>
-      </c>
-      <c r="AZ1" s="51" t="s">
-        <v>181</v>
-      </c>
-      <c r="BA1" s="51" t="s">
-        <v>182</v>
-      </c>
-      <c r="BB1" s="51" t="s">
-        <v>183</v>
-      </c>
-      <c r="BC1" s="51" t="s">
-        <v>184</v>
-      </c>
-      <c r="BD1" s="51" t="s">
-        <v>185</v>
-      </c>
-      <c r="BE1" s="51" t="s">
-        <v>186</v>
-      </c>
-      <c r="BF1" s="51" t="s">
-        <v>187</v>
-      </c>
-      <c r="BG1" s="51" t="s">
-        <v>188</v>
-      </c>
-      <c r="BH1" s="51" t="s">
-        <v>189</v>
-      </c>
-      <c r="BI1" s="51" t="s">
-        <v>190</v>
-      </c>
-      <c r="BJ1" s="51" t="s">
-        <v>191</v>
-      </c>
-      <c r="BK1" s="51" t="s">
-        <v>192</v>
-      </c>
-      <c r="BL1" s="51" t="s">
-        <v>193</v>
-      </c>
-      <c r="BM1" s="51" t="s">
-        <v>194</v>
-      </c>
-      <c r="BN1" s="51" t="s">
-        <v>195</v>
-      </c>
-      <c r="BO1" s="51" t="s">
-        <v>196</v>
-      </c>
-      <c r="BP1" s="51" t="s">
-        <v>197</v>
-      </c>
-      <c r="BQ1" s="51" t="s">
-        <v>198</v>
-      </c>
-      <c r="BR1" s="51" t="s">
-        <v>199</v>
-      </c>
-      <c r="BS1" s="51" t="s">
-        <v>200</v>
-      </c>
-      <c r="BT1" s="51" t="s">
-        <v>201</v>
-      </c>
-      <c r="BU1" s="51" t="s">
-        <v>202</v>
-      </c>
-      <c r="BV1" s="51" t="s">
-        <v>203</v>
-      </c>
-      <c r="BW1" s="51" t="s">
-        <v>204</v>
-      </c>
-      <c r="BX1" s="51" t="s">
-        <v>205</v>
-      </c>
-      <c r="BY1" s="51" t="s">
-        <v>206</v>
-      </c>
-      <c r="BZ1" s="51" t="s">
+      <c r="CD1" s="51" t="s">
         <v>207</v>
       </c>
-      <c r="CA1" s="51" t="s">
+      <c r="CE1" s="51" t="s">
         <v>208</v>
       </c>
-      <c r="CB1" s="51" t="s">
+      <c r="CF1" s="51" t="s">
         <v>209</v>
       </c>
-      <c r="CC1" s="51" t="s">
-        <v>41</v>
-      </c>
-      <c r="CD1" s="51" t="s">
+      <c r="CG1" s="51" t="s">
         <v>210</v>
       </c>
-      <c r="CE1" s="51" t="s">
+      <c r="CH1" s="51" t="s">
         <v>211</v>
       </c>
-      <c r="CF1" s="51" t="s">
+      <c r="CI1" s="51" t="s">
         <v>212</v>
       </c>
-      <c r="CG1" s="51" t="s">
+      <c r="CJ1" s="51" t="s">
         <v>213</v>
       </c>
-      <c r="CH1" s="51" t="s">
+      <c r="CK1" s="51" t="s">
         <v>214</v>
       </c>
-      <c r="CI1" s="51" t="s">
+      <c r="CL1" s="51" t="s">
         <v>215</v>
       </c>
-      <c r="CJ1" s="51" t="s">
+      <c r="CM1" s="51" t="s">
         <v>216</v>
       </c>
-      <c r="CK1" s="51" t="s">
+      <c r="CN1" s="51" t="s">
         <v>217</v>
       </c>
-      <c r="CL1" s="51" t="s">
+      <c r="CO1" s="51" t="s">
         <v>218</v>
       </c>
-      <c r="CM1" s="51" t="s">
+      <c r="CP1" s="51" t="s">
         <v>219</v>
-      </c>
-      <c r="CN1" s="51" t="s">
-        <v>220</v>
-      </c>
-      <c r="CO1" s="51" t="s">
-        <v>221</v>
-      </c>
-      <c r="CP1" s="51" t="s">
-        <v>222</v>
       </c>
     </row>
     <row r="2" spans="1:94" ht="22.15" hidden="1" customHeight="1">
@@ -3366,44 +3522,44 @@
       <c r="B2" s="52"/>
       <c r="C2" s="52"/>
       <c r="D2" s="52" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="E2" s="52" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="F2" s="52" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="G2" s="52"/>
       <c r="H2" s="52"/>
       <c r="I2" s="52" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="J2" s="52" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="K2" s="52" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="L2" s="52"/>
       <c r="M2" s="52"/>
       <c r="N2" s="52"/>
       <c r="O2" s="52" t="s">
+        <v>225</v>
+      </c>
+      <c r="P2" s="52" t="s">
+        <v>226</v>
+      </c>
+      <c r="Q2" s="52" t="s">
+        <v>227</v>
+      </c>
+      <c r="R2" s="52" t="s">
         <v>228</v>
-      </c>
-      <c r="P2" s="52" t="s">
-        <v>229</v>
-      </c>
-      <c r="Q2" s="52" t="s">
-        <v>230</v>
-      </c>
-      <c r="R2" s="52" t="s">
-        <v>231</v>
       </c>
       <c r="S2" s="52"/>
       <c r="T2" s="52"/>
       <c r="U2" s="52" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="V2" s="52"/>
       <c r="W2" s="52"/>
@@ -3424,31 +3580,31 @@
       <c r="AL2" s="52"/>
       <c r="AM2" s="52"/>
       <c r="AN2" s="52" t="s">
+        <v>229</v>
+      </c>
+      <c r="AO2" s="52" t="s">
+        <v>230</v>
+      </c>
+      <c r="AP2" s="52" t="s">
+        <v>379</v>
+      </c>
+      <c r="AQ2" s="52" t="s">
+        <v>231</v>
+      </c>
+      <c r="AR2" s="52" t="s">
         <v>232</v>
       </c>
-      <c r="AO2" s="52" t="s">
+      <c r="AS2" s="52" t="s">
+        <v>380</v>
+      </c>
+      <c r="AT2" s="52" t="s">
         <v>233</v>
       </c>
-      <c r="AP2" s="52" t="s">
-        <v>382</v>
-      </c>
-      <c r="AQ2" s="52" t="s">
+      <c r="AU2" s="52" t="s">
         <v>234</v>
       </c>
-      <c r="AR2" s="52" t="s">
-        <v>235</v>
-      </c>
-      <c r="AS2" s="52" t="s">
-        <v>383</v>
-      </c>
-      <c r="AT2" s="52" t="s">
-        <v>236</v>
-      </c>
-      <c r="AU2" s="52" t="s">
-        <v>237</v>
-      </c>
       <c r="AV2" s="52" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="AW2" s="52"/>
       <c r="AX2" s="52"/>
@@ -3492,7 +3648,7 @@
       <c r="CJ2" s="52"/>
       <c r="CK2" s="52"/>
       <c r="CL2" s="52" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="CM2" s="52"/>
       <c r="CN2" s="52"/>
@@ -3504,44 +3660,44 @@
       <c r="B3" s="52"/>
       <c r="C3" s="52"/>
       <c r="D3" s="52" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="E3" s="52" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="F3" s="52" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="G3" s="52"/>
       <c r="H3" s="52"/>
       <c r="I3" s="52" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="J3" s="52" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="K3" s="52" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="L3" s="52"/>
       <c r="M3" s="52"/>
       <c r="N3" s="52"/>
       <c r="O3" s="52" t="s">
+        <v>225</v>
+      </c>
+      <c r="P3" s="52" t="s">
+        <v>226</v>
+      </c>
+      <c r="Q3" s="52" t="s">
+        <v>227</v>
+      </c>
+      <c r="R3" s="52" t="s">
         <v>228</v>
-      </c>
-      <c r="P3" s="52" t="s">
-        <v>229</v>
-      </c>
-      <c r="Q3" s="52" t="s">
-        <v>230</v>
-      </c>
-      <c r="R3" s="52" t="s">
-        <v>231</v>
       </c>
       <c r="S3" s="52"/>
       <c r="T3" s="52"/>
       <c r="U3" s="52" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="V3" s="52"/>
       <c r="W3" s="52"/>
@@ -3562,31 +3718,31 @@
       <c r="AL3" s="52"/>
       <c r="AM3" s="52"/>
       <c r="AN3" s="52" t="s">
+        <v>229</v>
+      </c>
+      <c r="AO3" s="52" t="s">
+        <v>230</v>
+      </c>
+      <c r="AP3" s="52" t="s">
+        <v>381</v>
+      </c>
+      <c r="AQ3" s="52" t="s">
+        <v>231</v>
+      </c>
+      <c r="AR3" s="52" t="s">
         <v>232</v>
       </c>
-      <c r="AO3" s="52" t="s">
-        <v>233</v>
-      </c>
-      <c r="AP3" s="52" t="s">
-        <v>384</v>
-      </c>
-      <c r="AQ3" s="52" t="s">
-        <v>234</v>
-      </c>
-      <c r="AR3" s="52" t="s">
-        <v>235</v>
-      </c>
       <c r="AS3" s="52" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="AT3" s="52" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="AU3" s="52" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="AV3" s="52" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="AW3" s="52"/>
       <c r="AX3" s="52"/>
@@ -3630,7 +3786,7 @@
       <c r="CJ3" s="52"/>
       <c r="CK3" s="52"/>
       <c r="CL3" s="52" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="CM3" s="52"/>
       <c r="CN3" s="52"/>
@@ -3642,44 +3798,44 @@
       <c r="B4" s="52"/>
       <c r="C4" s="52"/>
       <c r="D4" s="52" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="E4" s="52" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="F4" s="52" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="G4" s="52"/>
       <c r="H4" s="52"/>
       <c r="I4" s="52" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="J4" s="52" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="K4" s="52" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="L4" s="52"/>
       <c r="M4" s="52"/>
       <c r="N4" s="52"/>
       <c r="O4" s="52" t="s">
+        <v>225</v>
+      </c>
+      <c r="P4" s="52" t="s">
+        <v>226</v>
+      </c>
+      <c r="Q4" s="52" t="s">
+        <v>227</v>
+      </c>
+      <c r="R4" s="52" t="s">
         <v>228</v>
-      </c>
-      <c r="P4" s="52" t="s">
-        <v>229</v>
-      </c>
-      <c r="Q4" s="52" t="s">
-        <v>230</v>
-      </c>
-      <c r="R4" s="52" t="s">
-        <v>231</v>
       </c>
       <c r="S4" s="52"/>
       <c r="T4" s="52"/>
       <c r="U4" s="52" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="V4" s="52"/>
       <c r="W4" s="52"/>
@@ -3700,31 +3856,31 @@
       <c r="AL4" s="52"/>
       <c r="AM4" s="52"/>
       <c r="AN4" s="52" t="s">
+        <v>229</v>
+      </c>
+      <c r="AO4" s="52" t="s">
+        <v>230</v>
+      </c>
+      <c r="AP4" s="52" t="s">
+        <v>384</v>
+      </c>
+      <c r="AQ4" s="52" t="s">
+        <v>231</v>
+      </c>
+      <c r="AR4" s="52" t="s">
         <v>232</v>
       </c>
-      <c r="AO4" s="52" t="s">
-        <v>233</v>
-      </c>
-      <c r="AP4" s="52" t="s">
-        <v>387</v>
-      </c>
-      <c r="AQ4" s="52" t="s">
-        <v>234</v>
-      </c>
-      <c r="AR4" s="52" t="s">
-        <v>235</v>
-      </c>
       <c r="AS4" s="52" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="AT4" s="52" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="AU4" s="52" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="AV4" s="52" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="AW4" s="52"/>
       <c r="AX4" s="52"/>
@@ -3768,7 +3924,7 @@
       <c r="CJ4" s="52"/>
       <c r="CK4" s="52"/>
       <c r="CL4" s="52" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="CM4" s="52"/>
       <c r="CN4" s="52"/>
@@ -3780,44 +3936,44 @@
       <c r="B5" s="52"/>
       <c r="C5" s="52"/>
       <c r="D5" s="52" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="E5" s="52" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="F5" s="52" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="G5" s="52"/>
       <c r="H5" s="52"/>
       <c r="I5" s="52" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="J5" s="52" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="K5" s="52" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="L5" s="52"/>
       <c r="M5" s="52"/>
       <c r="N5" s="52"/>
       <c r="O5" s="52" t="s">
+        <v>225</v>
+      </c>
+      <c r="P5" s="52" t="s">
+        <v>226</v>
+      </c>
+      <c r="Q5" s="52" t="s">
+        <v>227</v>
+      </c>
+      <c r="R5" s="52" t="s">
         <v>228</v>
-      </c>
-      <c r="P5" s="52" t="s">
-        <v>229</v>
-      </c>
-      <c r="Q5" s="52" t="s">
-        <v>230</v>
-      </c>
-      <c r="R5" s="52" t="s">
-        <v>231</v>
       </c>
       <c r="S5" s="52"/>
       <c r="T5" s="52"/>
       <c r="U5" s="52" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="V5" s="52"/>
       <c r="W5" s="52"/>
@@ -3838,31 +3994,31 @@
       <c r="AL5" s="52"/>
       <c r="AM5" s="52"/>
       <c r="AN5" s="52" t="s">
+        <v>229</v>
+      </c>
+      <c r="AO5" s="52" t="s">
+        <v>230</v>
+      </c>
+      <c r="AP5" s="52" t="s">
+        <v>373</v>
+      </c>
+      <c r="AQ5" s="52" t="s">
+        <v>244</v>
+      </c>
+      <c r="AR5" s="52" t="s">
+        <v>245</v>
+      </c>
+      <c r="AS5" s="52" t="s">
+        <v>387</v>
+      </c>
+      <c r="AT5" s="52" t="s">
+        <v>231</v>
+      </c>
+      <c r="AU5" s="52" t="s">
         <v>232</v>
       </c>
-      <c r="AO5" s="52" t="s">
-        <v>233</v>
-      </c>
-      <c r="AP5" s="52" t="s">
-        <v>376</v>
-      </c>
-      <c r="AQ5" s="52" t="s">
-        <v>247</v>
-      </c>
-      <c r="AR5" s="52" t="s">
-        <v>248</v>
-      </c>
-      <c r="AS5" s="52" t="s">
-        <v>390</v>
-      </c>
-      <c r="AT5" s="52" t="s">
-        <v>234</v>
-      </c>
-      <c r="AU5" s="52" t="s">
-        <v>235</v>
-      </c>
       <c r="AV5" s="52" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="AW5" s="52"/>
       <c r="AX5" s="52"/>
@@ -3906,7 +4062,7 @@
       <c r="CJ5" s="52"/>
       <c r="CK5" s="52"/>
       <c r="CL5" s="52" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="CM5" s="52"/>
       <c r="CN5" s="52"/>
@@ -3918,55 +4074,55 @@
       <c r="B6" s="52"/>
       <c r="C6" s="52"/>
       <c r="D6" s="52" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="E6" s="52" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="F6" s="52" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="G6" s="52"/>
       <c r="H6" s="52"/>
       <c r="I6" s="52" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="J6" s="52" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="K6" s="52" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="L6" s="52" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="M6" s="52"/>
       <c r="N6" s="52" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="O6" s="52" t="s">
+        <v>225</v>
+      </c>
+      <c r="P6" s="52" t="s">
+        <v>226</v>
+      </c>
+      <c r="Q6" s="52" t="s">
+        <v>227</v>
+      </c>
+      <c r="R6" s="52" t="s">
         <v>228</v>
-      </c>
-      <c r="P6" s="52" t="s">
-        <v>229</v>
-      </c>
-      <c r="Q6" s="52" t="s">
-        <v>230</v>
-      </c>
-      <c r="R6" s="52" t="s">
-        <v>231</v>
       </c>
       <c r="S6" s="52"/>
       <c r="T6" s="52"/>
       <c r="U6" s="52" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="V6" s="52"/>
       <c r="W6" s="52" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="X6" s="52" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="Y6" s="52"/>
       <c r="Z6" s="52"/>
@@ -3984,31 +4140,31 @@
       <c r="AL6" s="52"/>
       <c r="AM6" s="52"/>
       <c r="AN6" s="52" t="s">
+        <v>229</v>
+      </c>
+      <c r="AO6" s="52" t="s">
+        <v>230</v>
+      </c>
+      <c r="AP6" s="52" t="s">
+        <v>375</v>
+      </c>
+      <c r="AQ6" s="52" t="s">
+        <v>252</v>
+      </c>
+      <c r="AR6" s="52" t="s">
+        <v>253</v>
+      </c>
+      <c r="AS6" s="52" t="s">
+        <v>389</v>
+      </c>
+      <c r="AT6" s="52" t="s">
+        <v>231</v>
+      </c>
+      <c r="AU6" s="52" t="s">
         <v>232</v>
       </c>
-      <c r="AO6" s="52" t="s">
-        <v>233</v>
-      </c>
-      <c r="AP6" s="52" t="s">
-        <v>378</v>
-      </c>
-      <c r="AQ6" s="52" t="s">
-        <v>255</v>
-      </c>
-      <c r="AR6" s="52" t="s">
-        <v>256</v>
-      </c>
-      <c r="AS6" s="52" t="s">
-        <v>392</v>
-      </c>
-      <c r="AT6" s="52" t="s">
-        <v>234</v>
-      </c>
-      <c r="AU6" s="52" t="s">
-        <v>235</v>
-      </c>
       <c r="AV6" s="52" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="AW6" s="52"/>
       <c r="AX6" s="52"/>
@@ -4052,7 +4208,7 @@
       <c r="CJ6" s="52"/>
       <c r="CK6" s="52"/>
       <c r="CL6" s="52" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="CM6" s="52"/>
       <c r="CN6" s="52"/>
@@ -4064,44 +4220,44 @@
       <c r="B7" s="52"/>
       <c r="C7" s="52"/>
       <c r="D7" s="52" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="E7" s="52" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="F7" s="52" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="G7" s="52"/>
       <c r="H7" s="52"/>
       <c r="I7" s="52" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="J7" s="52" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="K7" s="52" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="L7" s="52"/>
       <c r="M7" s="52"/>
       <c r="N7" s="52"/>
       <c r="O7" s="52" t="s">
+        <v>225</v>
+      </c>
+      <c r="P7" s="52" t="s">
+        <v>226</v>
+      </c>
+      <c r="Q7" s="52" t="s">
+        <v>227</v>
+      </c>
+      <c r="R7" s="52" t="s">
         <v>228</v>
-      </c>
-      <c r="P7" s="52" t="s">
-        <v>229</v>
-      </c>
-      <c r="Q7" s="52" t="s">
-        <v>230</v>
-      </c>
-      <c r="R7" s="52" t="s">
-        <v>231</v>
       </c>
       <c r="S7" s="52"/>
       <c r="T7" s="52"/>
       <c r="U7" s="52" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="V7" s="52"/>
       <c r="W7" s="52"/>
@@ -4122,31 +4278,31 @@
       <c r="AL7" s="52"/>
       <c r="AM7" s="52"/>
       <c r="AN7" s="52" t="s">
+        <v>229</v>
+      </c>
+      <c r="AO7" s="52" t="s">
+        <v>230</v>
+      </c>
+      <c r="AP7" s="52" t="s">
+        <v>391</v>
+      </c>
+      <c r="AQ7" s="52" t="s">
+        <v>241</v>
+      </c>
+      <c r="AR7" s="52" t="s">
+        <v>242</v>
+      </c>
+      <c r="AS7" s="52" t="s">
+        <v>392</v>
+      </c>
+      <c r="AT7" s="52" t="s">
+        <v>231</v>
+      </c>
+      <c r="AU7" s="52" t="s">
         <v>232</v>
       </c>
-      <c r="AO7" s="52" t="s">
-        <v>233</v>
-      </c>
-      <c r="AP7" s="52" t="s">
-        <v>394</v>
-      </c>
-      <c r="AQ7" s="52" t="s">
-        <v>244</v>
-      </c>
-      <c r="AR7" s="52" t="s">
-        <v>245</v>
-      </c>
-      <c r="AS7" s="52" t="s">
-        <v>395</v>
-      </c>
-      <c r="AT7" s="52" t="s">
-        <v>234</v>
-      </c>
-      <c r="AU7" s="52" t="s">
-        <v>235</v>
-      </c>
       <c r="AV7" s="52" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="AW7" s="52"/>
       <c r="AX7" s="52"/>
@@ -4190,7 +4346,7 @@
       <c r="CJ7" s="52"/>
       <c r="CK7" s="52"/>
       <c r="CL7" s="52" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="CM7" s="52"/>
       <c r="CN7" s="52"/>
@@ -4202,44 +4358,44 @@
       <c r="B8" s="52"/>
       <c r="C8" s="52"/>
       <c r="D8" s="52" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="E8" s="52" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="F8" s="52" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="G8" s="52"/>
       <c r="H8" s="52"/>
       <c r="I8" s="52" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="J8" s="52" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="K8" s="52" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="L8" s="52"/>
       <c r="M8" s="52"/>
       <c r="N8" s="52"/>
       <c r="O8" s="52" t="s">
+        <v>225</v>
+      </c>
+      <c r="P8" s="52" t="s">
+        <v>226</v>
+      </c>
+      <c r="Q8" s="52" t="s">
+        <v>227</v>
+      </c>
+      <c r="R8" s="52" t="s">
         <v>228</v>
-      </c>
-      <c r="P8" s="52" t="s">
-        <v>229</v>
-      </c>
-      <c r="Q8" s="52" t="s">
-        <v>230</v>
-      </c>
-      <c r="R8" s="52" t="s">
-        <v>231</v>
       </c>
       <c r="S8" s="52"/>
       <c r="T8" s="52"/>
       <c r="U8" s="52" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="V8" s="52"/>
       <c r="W8" s="52"/>
@@ -4260,31 +4416,31 @@
       <c r="AL8" s="52"/>
       <c r="AM8" s="52"/>
       <c r="AN8" s="52" t="s">
+        <v>229</v>
+      </c>
+      <c r="AO8" s="52" t="s">
+        <v>230</v>
+      </c>
+      <c r="AP8" s="52" t="s">
+        <v>394</v>
+      </c>
+      <c r="AQ8" s="52" t="s">
+        <v>233</v>
+      </c>
+      <c r="AR8" s="52" t="s">
+        <v>234</v>
+      </c>
+      <c r="AS8" s="52" t="s">
+        <v>395</v>
+      </c>
+      <c r="AT8" s="52" t="s">
+        <v>231</v>
+      </c>
+      <c r="AU8" s="52" t="s">
         <v>232</v>
       </c>
-      <c r="AO8" s="52" t="s">
-        <v>233</v>
-      </c>
-      <c r="AP8" s="52" t="s">
-        <v>397</v>
-      </c>
-      <c r="AQ8" s="52" t="s">
-        <v>236</v>
-      </c>
-      <c r="AR8" s="52" t="s">
-        <v>237</v>
-      </c>
-      <c r="AS8" s="52" t="s">
-        <v>398</v>
-      </c>
-      <c r="AT8" s="52" t="s">
-        <v>234</v>
-      </c>
-      <c r="AU8" s="52" t="s">
-        <v>235</v>
-      </c>
       <c r="AV8" s="52" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="AW8" s="52"/>
       <c r="AX8" s="52"/>
@@ -4328,7 +4484,7 @@
       <c r="CJ8" s="52"/>
       <c r="CK8" s="52"/>
       <c r="CL8" s="52" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="CM8" s="52"/>
       <c r="CN8" s="52"/>
@@ -4340,44 +4496,44 @@
       <c r="B9" s="52"/>
       <c r="C9" s="52"/>
       <c r="D9" s="52" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="E9" s="52" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="F9" s="52" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="G9" s="52"/>
       <c r="H9" s="52"/>
       <c r="I9" s="52" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="J9" s="52" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="K9" s="52" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="L9" s="52"/>
       <c r="M9" s="52"/>
       <c r="N9" s="52"/>
       <c r="O9" s="52" t="s">
+        <v>225</v>
+      </c>
+      <c r="P9" s="52" t="s">
+        <v>226</v>
+      </c>
+      <c r="Q9" s="52" t="s">
+        <v>227</v>
+      </c>
+      <c r="R9" s="52" t="s">
         <v>228</v>
-      </c>
-      <c r="P9" s="52" t="s">
-        <v>229</v>
-      </c>
-      <c r="Q9" s="52" t="s">
-        <v>230</v>
-      </c>
-      <c r="R9" s="52" t="s">
-        <v>231</v>
       </c>
       <c r="S9" s="52"/>
       <c r="T9" s="52"/>
       <c r="U9" s="52" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="V9" s="52"/>
       <c r="W9" s="52"/>
@@ -4398,31 +4554,31 @@
       <c r="AL9" s="52"/>
       <c r="AM9" s="52"/>
       <c r="AN9" s="52" t="s">
+        <v>229</v>
+      </c>
+      <c r="AO9" s="52" t="s">
+        <v>230</v>
+      </c>
+      <c r="AP9" s="52" t="s">
+        <v>397</v>
+      </c>
+      <c r="AQ9" s="52" t="s">
+        <v>261</v>
+      </c>
+      <c r="AR9" s="52" t="s">
+        <v>262</v>
+      </c>
+      <c r="AS9" s="52" t="s">
+        <v>398</v>
+      </c>
+      <c r="AT9" s="52" t="s">
+        <v>231</v>
+      </c>
+      <c r="AU9" s="52" t="s">
         <v>232</v>
       </c>
-      <c r="AO9" s="52" t="s">
-        <v>233</v>
-      </c>
-      <c r="AP9" s="52" t="s">
-        <v>400</v>
-      </c>
-      <c r="AQ9" s="52" t="s">
-        <v>264</v>
-      </c>
-      <c r="AR9" s="52" t="s">
-        <v>265</v>
-      </c>
-      <c r="AS9" s="52" t="s">
-        <v>401</v>
-      </c>
-      <c r="AT9" s="52" t="s">
-        <v>234</v>
-      </c>
-      <c r="AU9" s="52" t="s">
-        <v>235</v>
-      </c>
       <c r="AV9" s="52" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="AW9" s="52"/>
       <c r="AX9" s="52"/>
@@ -4466,7 +4622,7 @@
       <c r="CJ9" s="52"/>
       <c r="CK9" s="52"/>
       <c r="CL9" s="52" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="CM9" s="52"/>
       <c r="CN9" s="52"/>
@@ -4478,44 +4634,44 @@
       <c r="B10" s="52"/>
       <c r="C10" s="52"/>
       <c r="D10" s="52" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="E10" s="52" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="F10" s="52" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="G10" s="52"/>
       <c r="H10" s="52"/>
       <c r="I10" s="52" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="J10" s="52" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="K10" s="52" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="L10" s="52"/>
       <c r="M10" s="52"/>
       <c r="N10" s="52"/>
       <c r="O10" s="52" t="s">
+        <v>225</v>
+      </c>
+      <c r="P10" s="52" t="s">
+        <v>226</v>
+      </c>
+      <c r="Q10" s="52" t="s">
+        <v>227</v>
+      </c>
+      <c r="R10" s="52" t="s">
         <v>228</v>
-      </c>
-      <c r="P10" s="52" t="s">
-        <v>229</v>
-      </c>
-      <c r="Q10" s="52" t="s">
-        <v>230</v>
-      </c>
-      <c r="R10" s="52" t="s">
-        <v>231</v>
       </c>
       <c r="S10" s="52"/>
       <c r="T10" s="52"/>
       <c r="U10" s="52" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="V10" s="52"/>
       <c r="W10" s="52"/>
@@ -4536,31 +4692,31 @@
       <c r="AL10" s="52"/>
       <c r="AM10" s="52"/>
       <c r="AN10" s="52" t="s">
+        <v>229</v>
+      </c>
+      <c r="AO10" s="52" t="s">
+        <v>230</v>
+      </c>
+      <c r="AP10" s="52" t="s">
+        <v>377</v>
+      </c>
+      <c r="AQ10" s="52" t="s">
+        <v>237</v>
+      </c>
+      <c r="AR10" s="52" t="s">
+        <v>238</v>
+      </c>
+      <c r="AS10" s="52" t="s">
+        <v>374</v>
+      </c>
+      <c r="AT10" s="52" t="s">
+        <v>231</v>
+      </c>
+      <c r="AU10" s="52" t="s">
         <v>232</v>
       </c>
-      <c r="AO10" s="52" t="s">
-        <v>233</v>
-      </c>
-      <c r="AP10" s="52" t="s">
-        <v>380</v>
-      </c>
-      <c r="AQ10" s="52" t="s">
-        <v>240</v>
-      </c>
-      <c r="AR10" s="52" t="s">
-        <v>241</v>
-      </c>
-      <c r="AS10" s="52" t="s">
-        <v>377</v>
-      </c>
-      <c r="AT10" s="52" t="s">
-        <v>234</v>
-      </c>
-      <c r="AU10" s="52" t="s">
-        <v>235</v>
-      </c>
       <c r="AV10" s="52" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="AW10" s="52"/>
       <c r="AX10" s="52"/>
@@ -4604,7 +4760,7 @@
       <c r="CJ10" s="52"/>
       <c r="CK10" s="52"/>
       <c r="CL10" s="52" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="CM10" s="52"/>
       <c r="CN10" s="52"/>
@@ -4616,44 +4772,44 @@
       <c r="B11" s="52"/>
       <c r="C11" s="52"/>
       <c r="D11" s="52" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="E11" s="52" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="F11" s="52" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="G11" s="52"/>
       <c r="H11" s="52"/>
       <c r="I11" s="52" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="J11" s="52" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="K11" s="52" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="L11" s="52"/>
       <c r="M11" s="52"/>
       <c r="N11" s="52"/>
       <c r="O11" s="52" t="s">
+        <v>225</v>
+      </c>
+      <c r="P11" s="52" t="s">
+        <v>226</v>
+      </c>
+      <c r="Q11" s="52" t="s">
+        <v>227</v>
+      </c>
+      <c r="R11" s="52" t="s">
         <v>228</v>
-      </c>
-      <c r="P11" s="52" t="s">
-        <v>229</v>
-      </c>
-      <c r="Q11" s="52" t="s">
-        <v>230</v>
-      </c>
-      <c r="R11" s="52" t="s">
-        <v>231</v>
       </c>
       <c r="S11" s="52"/>
       <c r="T11" s="52"/>
       <c r="U11" s="52" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="V11" s="52"/>
       <c r="W11" s="52"/>
@@ -4674,31 +4830,31 @@
       <c r="AL11" s="52"/>
       <c r="AM11" s="52"/>
       <c r="AN11" s="52" t="s">
+        <v>229</v>
+      </c>
+      <c r="AO11" s="52" t="s">
+        <v>230</v>
+      </c>
+      <c r="AP11" s="52" t="s">
+        <v>377</v>
+      </c>
+      <c r="AQ11" s="52" t="s">
+        <v>237</v>
+      </c>
+      <c r="AR11" s="52" t="s">
+        <v>238</v>
+      </c>
+      <c r="AS11" s="52" t="s">
+        <v>387</v>
+      </c>
+      <c r="AT11" s="52" t="s">
+        <v>231</v>
+      </c>
+      <c r="AU11" s="52" t="s">
         <v>232</v>
       </c>
-      <c r="AO11" s="52" t="s">
-        <v>233</v>
-      </c>
-      <c r="AP11" s="52" t="s">
-        <v>380</v>
-      </c>
-      <c r="AQ11" s="52" t="s">
-        <v>240</v>
-      </c>
-      <c r="AR11" s="52" t="s">
-        <v>241</v>
-      </c>
-      <c r="AS11" s="52" t="s">
+      <c r="AV11" s="52" t="s">
         <v>390</v>
-      </c>
-      <c r="AT11" s="52" t="s">
-        <v>234</v>
-      </c>
-      <c r="AU11" s="52" t="s">
-        <v>235</v>
-      </c>
-      <c r="AV11" s="52" t="s">
-        <v>393</v>
       </c>
       <c r="AW11" s="52"/>
       <c r="AX11" s="52"/>
@@ -4742,7 +4898,7 @@
       <c r="CJ11" s="52"/>
       <c r="CK11" s="52"/>
       <c r="CL11" s="52" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="CM11" s="52"/>
       <c r="CN11" s="52"/>
@@ -4754,44 +4910,44 @@
       <c r="B12" s="52"/>
       <c r="C12" s="52"/>
       <c r="D12" s="52" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="E12" s="52" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="F12" s="52" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="G12" s="52"/>
       <c r="H12" s="52"/>
       <c r="I12" s="52" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="J12" s="52" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="K12" s="52" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="L12" s="52"/>
       <c r="M12" s="52"/>
       <c r="N12" s="52"/>
       <c r="O12" s="52" t="s">
+        <v>225</v>
+      </c>
+      <c r="P12" s="52" t="s">
+        <v>226</v>
+      </c>
+      <c r="Q12" s="52" t="s">
+        <v>227</v>
+      </c>
+      <c r="R12" s="52" t="s">
         <v>228</v>
-      </c>
-      <c r="P12" s="52" t="s">
-        <v>229</v>
-      </c>
-      <c r="Q12" s="52" t="s">
-        <v>230</v>
-      </c>
-      <c r="R12" s="52" t="s">
-        <v>231</v>
       </c>
       <c r="S12" s="52"/>
       <c r="T12" s="52"/>
       <c r="U12" s="52" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="V12" s="52"/>
       <c r="W12" s="52"/>
@@ -4812,31 +4968,31 @@
       <c r="AL12" s="52"/>
       <c r="AM12" s="52"/>
       <c r="AN12" s="52" t="s">
+        <v>229</v>
+      </c>
+      <c r="AO12" s="52" t="s">
+        <v>230</v>
+      </c>
+      <c r="AP12" s="52" t="s">
+        <v>400</v>
+      </c>
+      <c r="AQ12" s="52" t="s">
+        <v>269</v>
+      </c>
+      <c r="AR12" s="52" t="s">
+        <v>270</v>
+      </c>
+      <c r="AS12" s="52" t="s">
+        <v>401</v>
+      </c>
+      <c r="AT12" s="52" t="s">
+        <v>231</v>
+      </c>
+      <c r="AU12" s="52" t="s">
         <v>232</v>
       </c>
-      <c r="AO12" s="52" t="s">
-        <v>233</v>
-      </c>
-      <c r="AP12" s="52" t="s">
-        <v>403</v>
-      </c>
-      <c r="AQ12" s="52" t="s">
-        <v>272</v>
-      </c>
-      <c r="AR12" s="52" t="s">
-        <v>273</v>
-      </c>
-      <c r="AS12" s="52" t="s">
-        <v>404</v>
-      </c>
-      <c r="AT12" s="52" t="s">
-        <v>234</v>
-      </c>
-      <c r="AU12" s="52" t="s">
-        <v>235</v>
-      </c>
       <c r="AV12" s="52" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="AW12" s="52"/>
       <c r="AX12" s="52"/>
@@ -4880,7 +5036,7 @@
       <c r="CJ12" s="52"/>
       <c r="CK12" s="52"/>
       <c r="CL12" s="52" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="CM12" s="52"/>
       <c r="CN12" s="52"/>
@@ -4892,44 +5048,44 @@
       <c r="B13" s="52"/>
       <c r="C13" s="52"/>
       <c r="D13" s="52" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="E13" s="52" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="F13" s="52" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="G13" s="52"/>
       <c r="H13" s="52"/>
       <c r="I13" s="52" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="J13" s="52" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="K13" s="52" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="L13" s="52"/>
       <c r="M13" s="52"/>
       <c r="N13" s="52"/>
       <c r="O13" s="52" t="s">
+        <v>225</v>
+      </c>
+      <c r="P13" s="52" t="s">
+        <v>226</v>
+      </c>
+      <c r="Q13" s="52" t="s">
+        <v>227</v>
+      </c>
+      <c r="R13" s="52" t="s">
         <v>228</v>
-      </c>
-      <c r="P13" s="52" t="s">
-        <v>229</v>
-      </c>
-      <c r="Q13" s="52" t="s">
-        <v>230</v>
-      </c>
-      <c r="R13" s="52" t="s">
-        <v>231</v>
       </c>
       <c r="S13" s="52"/>
       <c r="T13" s="52"/>
       <c r="U13" s="52" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="V13" s="52"/>
       <c r="W13" s="52"/>
@@ -4950,31 +5106,31 @@
       <c r="AL13" s="52"/>
       <c r="AM13" s="52"/>
       <c r="AN13" s="52" t="s">
+        <v>229</v>
+      </c>
+      <c r="AO13" s="52" t="s">
+        <v>230</v>
+      </c>
+      <c r="AP13" s="52" t="s">
+        <v>403</v>
+      </c>
+      <c r="AQ13" s="52" t="s">
+        <v>269</v>
+      </c>
+      <c r="AR13" s="52" t="s">
+        <v>270</v>
+      </c>
+      <c r="AS13" s="52" t="s">
+        <v>401</v>
+      </c>
+      <c r="AT13" s="52" t="s">
+        <v>231</v>
+      </c>
+      <c r="AU13" s="52" t="s">
         <v>232</v>
       </c>
-      <c r="AO13" s="52" t="s">
-        <v>233</v>
-      </c>
-      <c r="AP13" s="52" t="s">
-        <v>406</v>
-      </c>
-      <c r="AQ13" s="52" t="s">
-        <v>272</v>
-      </c>
-      <c r="AR13" s="52" t="s">
-        <v>273</v>
-      </c>
-      <c r="AS13" s="52" t="s">
+      <c r="AV13" s="52" t="s">
         <v>404</v>
-      </c>
-      <c r="AT13" s="52" t="s">
-        <v>234</v>
-      </c>
-      <c r="AU13" s="52" t="s">
-        <v>235</v>
-      </c>
-      <c r="AV13" s="52" t="s">
-        <v>407</v>
       </c>
       <c r="AW13" s="52"/>
       <c r="AX13" s="52"/>
@@ -5018,7 +5174,7 @@
       <c r="CJ13" s="52"/>
       <c r="CK13" s="52"/>
       <c r="CL13" s="52" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="CM13" s="52"/>
       <c r="CN13" s="52"/>
@@ -5030,44 +5186,44 @@
       <c r="B14" s="52"/>
       <c r="C14" s="52"/>
       <c r="D14" s="52" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="E14" s="52" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="F14" s="52" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="G14" s="52"/>
       <c r="H14" s="52"/>
       <c r="I14" s="52" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="J14" s="52" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="K14" s="52" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="L14" s="52"/>
       <c r="M14" s="52"/>
       <c r="N14" s="52"/>
       <c r="O14" s="52" t="s">
+        <v>225</v>
+      </c>
+      <c r="P14" s="52" t="s">
+        <v>226</v>
+      </c>
+      <c r="Q14" s="52" t="s">
+        <v>227</v>
+      </c>
+      <c r="R14" s="52" t="s">
         <v>228</v>
-      </c>
-      <c r="P14" s="52" t="s">
-        <v>229</v>
-      </c>
-      <c r="Q14" s="52" t="s">
-        <v>230</v>
-      </c>
-      <c r="R14" s="52" t="s">
-        <v>231</v>
       </c>
       <c r="S14" s="52"/>
       <c r="T14" s="52"/>
       <c r="U14" s="52" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="V14" s="52"/>
       <c r="W14" s="52"/>
@@ -5088,31 +5244,31 @@
       <c r="AL14" s="52"/>
       <c r="AM14" s="52"/>
       <c r="AN14" s="52" t="s">
+        <v>229</v>
+      </c>
+      <c r="AO14" s="52" t="s">
+        <v>230</v>
+      </c>
+      <c r="AP14" s="52" t="s">
+        <v>403</v>
+      </c>
+      <c r="AQ14" s="52" t="s">
+        <v>269</v>
+      </c>
+      <c r="AR14" s="52" t="s">
+        <v>270</v>
+      </c>
+      <c r="AS14" s="52" t="s">
+        <v>401</v>
+      </c>
+      <c r="AT14" s="52" t="s">
+        <v>231</v>
+      </c>
+      <c r="AU14" s="52" t="s">
         <v>232</v>
       </c>
-      <c r="AO14" s="52" t="s">
-        <v>233</v>
-      </c>
-      <c r="AP14" s="52" t="s">
-        <v>406</v>
-      </c>
-      <c r="AQ14" s="52" t="s">
-        <v>272</v>
-      </c>
-      <c r="AR14" s="52" t="s">
-        <v>273</v>
-      </c>
-      <c r="AS14" s="52" t="s">
+      <c r="AV14" s="52" t="s">
         <v>404</v>
-      </c>
-      <c r="AT14" s="52" t="s">
-        <v>234</v>
-      </c>
-      <c r="AU14" s="52" t="s">
-        <v>235</v>
-      </c>
-      <c r="AV14" s="52" t="s">
-        <v>407</v>
       </c>
       <c r="AW14" s="52"/>
       <c r="AX14" s="52"/>
@@ -5156,7 +5312,7 @@
       <c r="CJ14" s="52"/>
       <c r="CK14" s="52"/>
       <c r="CL14" s="52" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="CM14" s="52"/>
       <c r="CN14" s="52"/>
@@ -5168,44 +5324,44 @@
       <c r="B15" s="52"/>
       <c r="C15" s="52"/>
       <c r="D15" s="52" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="E15" s="52" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="F15" s="52" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="G15" s="52"/>
       <c r="H15" s="52"/>
       <c r="I15" s="52" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="J15" s="52" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="K15" s="52" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="L15" s="52"/>
       <c r="M15" s="52"/>
       <c r="N15" s="52"/>
       <c r="O15" s="52" t="s">
+        <v>225</v>
+      </c>
+      <c r="P15" s="52" t="s">
+        <v>226</v>
+      </c>
+      <c r="Q15" s="52" t="s">
+        <v>227</v>
+      </c>
+      <c r="R15" s="52" t="s">
         <v>228</v>
-      </c>
-      <c r="P15" s="52" t="s">
-        <v>229</v>
-      </c>
-      <c r="Q15" s="52" t="s">
-        <v>230</v>
-      </c>
-      <c r="R15" s="52" t="s">
-        <v>231</v>
       </c>
       <c r="S15" s="52"/>
       <c r="T15" s="52"/>
       <c r="U15" s="52" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="V15" s="52"/>
       <c r="W15" s="52"/>
@@ -5226,31 +5382,31 @@
       <c r="AL15" s="52"/>
       <c r="AM15" s="52"/>
       <c r="AN15" s="52" t="s">
+        <v>229</v>
+      </c>
+      <c r="AO15" s="52" t="s">
+        <v>230</v>
+      </c>
+      <c r="AP15" s="52" t="s">
+        <v>403</v>
+      </c>
+      <c r="AQ15" s="52" t="s">
+        <v>269</v>
+      </c>
+      <c r="AR15" s="52" t="s">
+        <v>270</v>
+      </c>
+      <c r="AS15" s="52" t="s">
+        <v>401</v>
+      </c>
+      <c r="AT15" s="52" t="s">
+        <v>231</v>
+      </c>
+      <c r="AU15" s="52" t="s">
         <v>232</v>
       </c>
-      <c r="AO15" s="52" t="s">
-        <v>233</v>
-      </c>
-      <c r="AP15" s="52" t="s">
-        <v>406</v>
-      </c>
-      <c r="AQ15" s="52" t="s">
-        <v>272</v>
-      </c>
-      <c r="AR15" s="52" t="s">
-        <v>273</v>
-      </c>
-      <c r="AS15" s="52" t="s">
+      <c r="AV15" s="52" t="s">
         <v>404</v>
-      </c>
-      <c r="AT15" s="52" t="s">
-        <v>234</v>
-      </c>
-      <c r="AU15" s="52" t="s">
-        <v>235</v>
-      </c>
-      <c r="AV15" s="52" t="s">
-        <v>407</v>
       </c>
       <c r="AW15" s="52"/>
       <c r="AX15" s="52"/>
@@ -5294,7 +5450,7 @@
       <c r="CJ15" s="52"/>
       <c r="CK15" s="52"/>
       <c r="CL15" s="52" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="CM15" s="52"/>
       <c r="CN15" s="52"/>
@@ -5306,44 +5462,44 @@
       <c r="B16" s="52"/>
       <c r="C16" s="52"/>
       <c r="D16" s="52" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="E16" s="52" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="F16" s="52" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="G16" s="52"/>
       <c r="H16" s="52"/>
       <c r="I16" s="52" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="J16" s="52" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="K16" s="52" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="L16" s="52"/>
       <c r="M16" s="52"/>
       <c r="N16" s="52"/>
       <c r="O16" s="52" t="s">
+        <v>225</v>
+      </c>
+      <c r="P16" s="52" t="s">
+        <v>226</v>
+      </c>
+      <c r="Q16" s="52" t="s">
+        <v>227</v>
+      </c>
+      <c r="R16" s="52" t="s">
         <v>228</v>
-      </c>
-      <c r="P16" s="52" t="s">
-        <v>229</v>
-      </c>
-      <c r="Q16" s="52" t="s">
-        <v>230</v>
-      </c>
-      <c r="R16" s="52" t="s">
-        <v>231</v>
       </c>
       <c r="S16" s="52"/>
       <c r="T16" s="52"/>
       <c r="U16" s="52" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="V16" s="52"/>
       <c r="W16" s="52"/>
@@ -5364,31 +5520,31 @@
       <c r="AL16" s="52"/>
       <c r="AM16" s="52"/>
       <c r="AN16" s="52" t="s">
+        <v>229</v>
+      </c>
+      <c r="AO16" s="52" t="s">
+        <v>230</v>
+      </c>
+      <c r="AP16" s="52" t="s">
+        <v>405</v>
+      </c>
+      <c r="AQ16" s="52" t="s">
+        <v>233</v>
+      </c>
+      <c r="AR16" s="52" t="s">
+        <v>234</v>
+      </c>
+      <c r="AS16" s="52" t="s">
+        <v>406</v>
+      </c>
+      <c r="AT16" s="52" t="s">
+        <v>231</v>
+      </c>
+      <c r="AU16" s="52" t="s">
         <v>232</v>
       </c>
-      <c r="AO16" s="52" t="s">
-        <v>233</v>
-      </c>
-      <c r="AP16" s="52" t="s">
-        <v>408</v>
-      </c>
-      <c r="AQ16" s="52" t="s">
-        <v>236</v>
-      </c>
-      <c r="AR16" s="52" t="s">
-        <v>237</v>
-      </c>
-      <c r="AS16" s="52" t="s">
-        <v>409</v>
-      </c>
-      <c r="AT16" s="52" t="s">
-        <v>234</v>
-      </c>
-      <c r="AU16" s="52" t="s">
-        <v>235</v>
-      </c>
       <c r="AV16" s="52" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="AW16" s="52"/>
       <c r="AX16" s="52"/>
@@ -5432,7 +5588,7 @@
       <c r="CJ16" s="52"/>
       <c r="CK16" s="52"/>
       <c r="CL16" s="52" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="CM16" s="52"/>
       <c r="CN16" s="52"/>
@@ -5444,44 +5600,44 @@
       <c r="B17" s="52"/>
       <c r="C17" s="52"/>
       <c r="D17" s="52" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="E17" s="52" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="F17" s="52" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="G17" s="52"/>
       <c r="H17" s="52"/>
       <c r="I17" s="52" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="J17" s="52" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="K17" s="52" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="L17" s="52"/>
       <c r="M17" s="52"/>
       <c r="N17" s="52"/>
       <c r="O17" s="52" t="s">
+        <v>225</v>
+      </c>
+      <c r="P17" s="52" t="s">
+        <v>226</v>
+      </c>
+      <c r="Q17" s="52" t="s">
+        <v>227</v>
+      </c>
+      <c r="R17" s="52" t="s">
         <v>228</v>
-      </c>
-      <c r="P17" s="52" t="s">
-        <v>229</v>
-      </c>
-      <c r="Q17" s="52" t="s">
-        <v>230</v>
-      </c>
-      <c r="R17" s="52" t="s">
-        <v>231</v>
       </c>
       <c r="S17" s="52"/>
       <c r="T17" s="52"/>
       <c r="U17" s="52" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="V17" s="52"/>
       <c r="W17" s="52"/>
@@ -5502,31 +5658,31 @@
       <c r="AL17" s="52"/>
       <c r="AM17" s="52"/>
       <c r="AN17" s="52" t="s">
+        <v>229</v>
+      </c>
+      <c r="AO17" s="52" t="s">
+        <v>230</v>
+      </c>
+      <c r="AP17" s="52" t="s">
+        <v>403</v>
+      </c>
+      <c r="AQ17" s="52" t="s">
+        <v>269</v>
+      </c>
+      <c r="AR17" s="52" t="s">
+        <v>270</v>
+      </c>
+      <c r="AS17" s="52" t="s">
+        <v>401</v>
+      </c>
+      <c r="AT17" s="52" t="s">
+        <v>231</v>
+      </c>
+      <c r="AU17" s="52" t="s">
         <v>232</v>
       </c>
-      <c r="AO17" s="52" t="s">
-        <v>233</v>
-      </c>
-      <c r="AP17" s="52" t="s">
-        <v>406</v>
-      </c>
-      <c r="AQ17" s="52" t="s">
-        <v>272</v>
-      </c>
-      <c r="AR17" s="52" t="s">
-        <v>273</v>
-      </c>
-      <c r="AS17" s="52" t="s">
+      <c r="AV17" s="52" t="s">
         <v>404</v>
-      </c>
-      <c r="AT17" s="52" t="s">
-        <v>234</v>
-      </c>
-      <c r="AU17" s="52" t="s">
-        <v>235</v>
-      </c>
-      <c r="AV17" s="52" t="s">
-        <v>407</v>
       </c>
       <c r="AW17" s="52"/>
       <c r="AX17" s="52"/>
@@ -5570,7 +5726,7 @@
       <c r="CJ17" s="52"/>
       <c r="CK17" s="52"/>
       <c r="CL17" s="52" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="CM17" s="52"/>
       <c r="CN17" s="52"/>
@@ -5582,57 +5738,57 @@
       <c r="B18" s="52"/>
       <c r="C18" s="52"/>
       <c r="D18" s="52" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="E18" s="52" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="F18" s="52" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="G18" s="52"/>
       <c r="H18" s="52"/>
       <c r="I18" s="52" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="J18" s="52" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="K18" s="52" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="L18" s="52" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="M18" s="52"/>
       <c r="N18" s="52" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="O18" s="52" t="s">
+        <v>225</v>
+      </c>
+      <c r="P18" s="52" t="s">
+        <v>226</v>
+      </c>
+      <c r="Q18" s="52" t="s">
+        <v>227</v>
+      </c>
+      <c r="R18" s="52" t="s">
         <v>228</v>
-      </c>
-      <c r="P18" s="52" t="s">
-        <v>229</v>
-      </c>
-      <c r="Q18" s="52" t="s">
-        <v>230</v>
-      </c>
-      <c r="R18" s="52" t="s">
-        <v>231</v>
       </c>
       <c r="S18" s="52"/>
       <c r="T18" s="52"/>
       <c r="U18" s="52" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="V18" s="52" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="W18" s="52" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="X18" s="52" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="Y18" s="52"/>
       <c r="Z18" s="52"/>
@@ -5650,31 +5806,31 @@
       <c r="AL18" s="52"/>
       <c r="AM18" s="52"/>
       <c r="AN18" s="52" t="s">
+        <v>229</v>
+      </c>
+      <c r="AO18" s="52" t="s">
+        <v>230</v>
+      </c>
+      <c r="AP18" s="52" t="s">
+        <v>373</v>
+      </c>
+      <c r="AQ18" s="52" t="s">
+        <v>244</v>
+      </c>
+      <c r="AR18" s="52" t="s">
+        <v>245</v>
+      </c>
+      <c r="AS18" s="52" t="s">
+        <v>387</v>
+      </c>
+      <c r="AT18" s="52" t="s">
+        <v>231</v>
+      </c>
+      <c r="AU18" s="52" t="s">
         <v>232</v>
       </c>
-      <c r="AO18" s="52" t="s">
-        <v>233</v>
-      </c>
-      <c r="AP18" s="52" t="s">
-        <v>376</v>
-      </c>
-      <c r="AQ18" s="52" t="s">
-        <v>247</v>
-      </c>
-      <c r="AR18" s="52" t="s">
-        <v>248</v>
-      </c>
-      <c r="AS18" s="52" t="s">
-        <v>390</v>
-      </c>
-      <c r="AT18" s="52" t="s">
-        <v>234</v>
-      </c>
-      <c r="AU18" s="52" t="s">
-        <v>235</v>
-      </c>
       <c r="AV18" s="52" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="AW18" s="52"/>
       <c r="AX18" s="52"/>
@@ -5718,7 +5874,7 @@
       <c r="CJ18" s="52"/>
       <c r="CK18" s="52"/>
       <c r="CL18" s="52" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="CM18" s="52"/>
       <c r="CN18" s="52"/>
@@ -5730,44 +5886,44 @@
       <c r="B19" s="52"/>
       <c r="C19" s="52"/>
       <c r="D19" s="52" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="E19" s="52" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="F19" s="52" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="G19" s="52"/>
       <c r="H19" s="52"/>
       <c r="I19" s="52" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="J19" s="52" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="K19" s="52" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="L19" s="52"/>
       <c r="M19" s="52"/>
       <c r="N19" s="52"/>
       <c r="O19" s="52" t="s">
+        <v>225</v>
+      </c>
+      <c r="P19" s="52" t="s">
+        <v>226</v>
+      </c>
+      <c r="Q19" s="52" t="s">
+        <v>227</v>
+      </c>
+      <c r="R19" s="52" t="s">
         <v>228</v>
-      </c>
-      <c r="P19" s="52" t="s">
-        <v>229</v>
-      </c>
-      <c r="Q19" s="52" t="s">
-        <v>230</v>
-      </c>
-      <c r="R19" s="52" t="s">
-        <v>231</v>
       </c>
       <c r="S19" s="52"/>
       <c r="T19" s="52"/>
       <c r="U19" s="52" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="V19" s="52"/>
       <c r="W19" s="52"/>
@@ -5788,31 +5944,31 @@
       <c r="AL19" s="52"/>
       <c r="AM19" s="52"/>
       <c r="AN19" s="52" t="s">
+        <v>229</v>
+      </c>
+      <c r="AO19" s="52" t="s">
+        <v>230</v>
+      </c>
+      <c r="AP19" s="52" t="s">
+        <v>407</v>
+      </c>
+      <c r="AQ19" s="52" t="s">
+        <v>252</v>
+      </c>
+      <c r="AR19" s="52" t="s">
+        <v>253</v>
+      </c>
+      <c r="AS19" s="52" t="s">
+        <v>408</v>
+      </c>
+      <c r="AT19" s="52" t="s">
+        <v>231</v>
+      </c>
+      <c r="AU19" s="52" t="s">
         <v>232</v>
       </c>
-      <c r="AO19" s="52" t="s">
-        <v>233</v>
-      </c>
-      <c r="AP19" s="52" t="s">
-        <v>410</v>
-      </c>
-      <c r="AQ19" s="52" t="s">
-        <v>255</v>
-      </c>
-      <c r="AR19" s="52" t="s">
-        <v>256</v>
-      </c>
-      <c r="AS19" s="52" t="s">
-        <v>411</v>
-      </c>
-      <c r="AT19" s="52" t="s">
-        <v>234</v>
-      </c>
-      <c r="AU19" s="52" t="s">
-        <v>235</v>
-      </c>
       <c r="AV19" s="52" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="AW19" s="52"/>
       <c r="AX19" s="52"/>
@@ -5856,7 +6012,7 @@
       <c r="CJ19" s="52"/>
       <c r="CK19" s="52"/>
       <c r="CL19" s="52" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="CM19" s="52"/>
       <c r="CN19" s="52"/>
@@ -5868,44 +6024,44 @@
       <c r="B20" s="52"/>
       <c r="C20" s="52"/>
       <c r="D20" s="52" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="E20" s="52" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="F20" s="52" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="G20" s="52"/>
       <c r="H20" s="52"/>
       <c r="I20" s="52" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="J20" s="52" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="K20" s="52" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="L20" s="52"/>
       <c r="M20" s="52"/>
       <c r="N20" s="52"/>
       <c r="O20" s="52" t="s">
+        <v>225</v>
+      </c>
+      <c r="P20" s="52" t="s">
+        <v>226</v>
+      </c>
+      <c r="Q20" s="52" t="s">
+        <v>227</v>
+      </c>
+      <c r="R20" s="52" t="s">
         <v>228</v>
-      </c>
-      <c r="P20" s="52" t="s">
-        <v>229</v>
-      </c>
-      <c r="Q20" s="52" t="s">
-        <v>230</v>
-      </c>
-      <c r="R20" s="52" t="s">
-        <v>231</v>
       </c>
       <c r="S20" s="52"/>
       <c r="T20" s="52"/>
       <c r="U20" s="52" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="V20" s="52"/>
       <c r="W20" s="52"/>
@@ -5926,31 +6082,31 @@
       <c r="AL20" s="52"/>
       <c r="AM20" s="52"/>
       <c r="AN20" s="52" t="s">
+        <v>229</v>
+      </c>
+      <c r="AO20" s="52" t="s">
+        <v>230</v>
+      </c>
+      <c r="AP20" s="52" t="s">
+        <v>410</v>
+      </c>
+      <c r="AQ20" s="52" t="s">
+        <v>231</v>
+      </c>
+      <c r="AR20" s="52" t="s">
         <v>232</v>
       </c>
-      <c r="AO20" s="52" t="s">
-        <v>233</v>
-      </c>
-      <c r="AP20" s="52" t="s">
-        <v>413</v>
-      </c>
-      <c r="AQ20" s="52" t="s">
-        <v>234</v>
-      </c>
-      <c r="AR20" s="52" t="s">
-        <v>235</v>
-      </c>
       <c r="AS20" s="52" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="AT20" s="52" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="AU20" s="52" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="AV20" s="52" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="AW20" s="52"/>
       <c r="AX20" s="52"/>
@@ -5994,7 +6150,7 @@
       <c r="CJ20" s="52"/>
       <c r="CK20" s="52"/>
       <c r="CL20" s="52" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="CM20" s="52"/>
       <c r="CN20" s="52"/>
@@ -6006,44 +6162,44 @@
       <c r="B21" s="52"/>
       <c r="C21" s="52"/>
       <c r="D21" s="52" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="E21" s="52" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="F21" s="52" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="G21" s="52"/>
       <c r="H21" s="52"/>
       <c r="I21" s="52" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="J21" s="52" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="K21" s="52" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="L21" s="52"/>
       <c r="M21" s="52"/>
       <c r="N21" s="52"/>
       <c r="O21" s="52" t="s">
+        <v>225</v>
+      </c>
+      <c r="P21" s="52" t="s">
+        <v>226</v>
+      </c>
+      <c r="Q21" s="52" t="s">
+        <v>227</v>
+      </c>
+      <c r="R21" s="52" t="s">
         <v>228</v>
-      </c>
-      <c r="P21" s="52" t="s">
-        <v>229</v>
-      </c>
-      <c r="Q21" s="52" t="s">
-        <v>230</v>
-      </c>
-      <c r="R21" s="52" t="s">
-        <v>231</v>
       </c>
       <c r="S21" s="52"/>
       <c r="T21" s="52"/>
       <c r="U21" s="52" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="V21" s="52"/>
       <c r="W21" s="52"/>
@@ -6064,31 +6220,31 @@
       <c r="AL21" s="52"/>
       <c r="AM21" s="52"/>
       <c r="AN21" s="52" t="s">
+        <v>229</v>
+      </c>
+      <c r="AO21" s="52" t="s">
+        <v>230</v>
+      </c>
+      <c r="AP21" s="52" t="s">
+        <v>410</v>
+      </c>
+      <c r="AQ21" s="52" t="s">
+        <v>231</v>
+      </c>
+      <c r="AR21" s="52" t="s">
         <v>232</v>
       </c>
-      <c r="AO21" s="52" t="s">
-        <v>233</v>
-      </c>
-      <c r="AP21" s="52" t="s">
+      <c r="AS21" s="52" t="s">
         <v>413</v>
       </c>
-      <c r="AQ21" s="52" t="s">
-        <v>234</v>
-      </c>
-      <c r="AR21" s="52" t="s">
-        <v>235</v>
-      </c>
-      <c r="AS21" s="52" t="s">
-        <v>416</v>
-      </c>
       <c r="AT21" s="52" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="AU21" s="52" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="AV21" s="52" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="AW21" s="52"/>
       <c r="AX21" s="52"/>
@@ -6132,7 +6288,7 @@
       <c r="CJ21" s="52"/>
       <c r="CK21" s="52"/>
       <c r="CL21" s="52" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="CM21" s="52"/>
       <c r="CN21" s="52"/>
@@ -6144,57 +6300,57 @@
       <c r="B22" s="52"/>
       <c r="C22" s="52"/>
       <c r="D22" s="52" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="E22" s="52" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="F22" s="52" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="G22" s="52"/>
       <c r="H22" s="52"/>
       <c r="I22" s="52" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="J22" s="52" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="K22" s="52" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="L22" s="52" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="M22" s="52"/>
       <c r="N22" s="52" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="O22" s="52" t="s">
+        <v>225</v>
+      </c>
+      <c r="P22" s="52" t="s">
+        <v>226</v>
+      </c>
+      <c r="Q22" s="52" t="s">
+        <v>227</v>
+      </c>
+      <c r="R22" s="52" t="s">
         <v>228</v>
-      </c>
-      <c r="P22" s="52" t="s">
-        <v>229</v>
-      </c>
-      <c r="Q22" s="52" t="s">
-        <v>230</v>
-      </c>
-      <c r="R22" s="52" t="s">
-        <v>231</v>
       </c>
       <c r="S22" s="52"/>
       <c r="T22" s="52"/>
       <c r="U22" s="52" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="V22" s="52" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="W22" s="52" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="X22" s="52" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="Y22" s="52"/>
       <c r="Z22" s="52"/>
@@ -6212,31 +6368,31 @@
       <c r="AL22" s="52"/>
       <c r="AM22" s="52"/>
       <c r="AN22" s="52" t="s">
+        <v>229</v>
+      </c>
+      <c r="AO22" s="52" t="s">
+        <v>230</v>
+      </c>
+      <c r="AP22" s="52" t="s">
+        <v>415</v>
+      </c>
+      <c r="AQ22" s="52" t="s">
+        <v>231</v>
+      </c>
+      <c r="AR22" s="52" t="s">
         <v>232</v>
       </c>
-      <c r="AO22" s="52" t="s">
-        <v>233</v>
-      </c>
-      <c r="AP22" s="52" t="s">
-        <v>418</v>
-      </c>
-      <c r="AQ22" s="52" t="s">
-        <v>234</v>
-      </c>
-      <c r="AR22" s="52" t="s">
-        <v>235</v>
-      </c>
       <c r="AS22" s="52" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="AT22" s="52" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="AU22" s="52" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="AV22" s="52" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="AW22" s="52"/>
       <c r="AX22" s="52"/>
@@ -6280,7 +6436,7 @@
       <c r="CJ22" s="52"/>
       <c r="CK22" s="52"/>
       <c r="CL22" s="52" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="CM22" s="52"/>
       <c r="CN22" s="52"/>
@@ -6292,57 +6448,57 @@
       <c r="B23" s="52"/>
       <c r="C23" s="52"/>
       <c r="D23" s="52" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="E23" s="52" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="F23" s="52" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="G23" s="52"/>
       <c r="H23" s="52"/>
       <c r="I23" s="52" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="J23" s="52" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="K23" s="52" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="L23" s="52" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="M23" s="52"/>
       <c r="N23" s="52" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="O23" s="52" t="s">
+        <v>225</v>
+      </c>
+      <c r="P23" s="52" t="s">
+        <v>226</v>
+      </c>
+      <c r="Q23" s="52" t="s">
+        <v>227</v>
+      </c>
+      <c r="R23" s="52" t="s">
         <v>228</v>
-      </c>
-      <c r="P23" s="52" t="s">
-        <v>229</v>
-      </c>
-      <c r="Q23" s="52" t="s">
-        <v>230</v>
-      </c>
-      <c r="R23" s="52" t="s">
-        <v>231</v>
       </c>
       <c r="S23" s="52"/>
       <c r="T23" s="52"/>
       <c r="U23" s="52" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="V23" s="52" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="W23" s="52" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="X23" s="52" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="Y23" s="52"/>
       <c r="Z23" s="52"/>
@@ -6360,31 +6516,31 @@
       <c r="AL23" s="52"/>
       <c r="AM23" s="52"/>
       <c r="AN23" s="52" t="s">
+        <v>229</v>
+      </c>
+      <c r="AO23" s="52" t="s">
+        <v>230</v>
+      </c>
+      <c r="AP23" s="52" t="s">
+        <v>416</v>
+      </c>
+      <c r="AQ23" s="52" t="s">
+        <v>231</v>
+      </c>
+      <c r="AR23" s="52" t="s">
         <v>232</v>
       </c>
-      <c r="AO23" s="52" t="s">
-        <v>233</v>
-      </c>
-      <c r="AP23" s="52" t="s">
-        <v>419</v>
-      </c>
-      <c r="AQ23" s="52" t="s">
-        <v>234</v>
-      </c>
-      <c r="AR23" s="52" t="s">
-        <v>235</v>
-      </c>
       <c r="AS23" s="52" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="AT23" s="52" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="AU23" s="52" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="AV23" s="52" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="AW23" s="52"/>
       <c r="AX23" s="52"/>
@@ -6428,7 +6584,7 @@
       <c r="CJ23" s="52"/>
       <c r="CK23" s="52"/>
       <c r="CL23" s="52" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="CM23" s="52"/>
       <c r="CN23" s="52"/>
@@ -6440,44 +6596,44 @@
       <c r="B24" s="52"/>
       <c r="C24" s="52"/>
       <c r="D24" s="52" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="E24" s="52" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="F24" s="52" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="G24" s="52"/>
       <c r="H24" s="52"/>
       <c r="I24" s="52" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="J24" s="52" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="K24" s="52" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="L24" s="52"/>
       <c r="M24" s="52"/>
       <c r="N24" s="52"/>
       <c r="O24" s="52" t="s">
+        <v>225</v>
+      </c>
+      <c r="P24" s="52" t="s">
+        <v>226</v>
+      </c>
+      <c r="Q24" s="52" t="s">
+        <v>227</v>
+      </c>
+      <c r="R24" s="52" t="s">
         <v>228</v>
-      </c>
-      <c r="P24" s="52" t="s">
-        <v>229</v>
-      </c>
-      <c r="Q24" s="52" t="s">
-        <v>230</v>
-      </c>
-      <c r="R24" s="52" t="s">
-        <v>231</v>
       </c>
       <c r="S24" s="52"/>
       <c r="T24" s="52"/>
       <c r="U24" s="52" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="V24" s="52"/>
       <c r="W24" s="52"/>
@@ -6498,31 +6654,31 @@
       <c r="AL24" s="52"/>
       <c r="AM24" s="52"/>
       <c r="AN24" s="52" t="s">
+        <v>229</v>
+      </c>
+      <c r="AO24" s="52" t="s">
+        <v>230</v>
+      </c>
+      <c r="AP24" s="52" t="s">
+        <v>418</v>
+      </c>
+      <c r="AQ24" s="52" t="s">
+        <v>231</v>
+      </c>
+      <c r="AR24" s="52" t="s">
         <v>232</v>
       </c>
-      <c r="AO24" s="52" t="s">
-        <v>233</v>
-      </c>
-      <c r="AP24" s="52" t="s">
-        <v>421</v>
-      </c>
-      <c r="AQ24" s="52" t="s">
-        <v>234</v>
-      </c>
-      <c r="AR24" s="52" t="s">
-        <v>235</v>
-      </c>
       <c r="AS24" s="52" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="AT24" s="52" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="AU24" s="52" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="AV24" s="52" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="AW24" s="52"/>
       <c r="AX24" s="52"/>
@@ -6566,7 +6722,7 @@
       <c r="CJ24" s="52"/>
       <c r="CK24" s="52"/>
       <c r="CL24" s="52" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="CM24" s="52"/>
       <c r="CN24" s="52"/>
@@ -6578,44 +6734,44 @@
       <c r="B25" s="52"/>
       <c r="C25" s="52"/>
       <c r="D25" s="52" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="E25" s="52" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="F25" s="52" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="G25" s="52"/>
       <c r="H25" s="52"/>
       <c r="I25" s="52" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="J25" s="52" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="K25" s="52" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="L25" s="52"/>
       <c r="M25" s="52"/>
       <c r="N25" s="52"/>
       <c r="O25" s="52" t="s">
+        <v>225</v>
+      </c>
+      <c r="P25" s="52" t="s">
+        <v>226</v>
+      </c>
+      <c r="Q25" s="52" t="s">
+        <v>227</v>
+      </c>
+      <c r="R25" s="52" t="s">
         <v>228</v>
-      </c>
-      <c r="P25" s="52" t="s">
-        <v>229</v>
-      </c>
-      <c r="Q25" s="52" t="s">
-        <v>230</v>
-      </c>
-      <c r="R25" s="52" t="s">
-        <v>231</v>
       </c>
       <c r="S25" s="52"/>
       <c r="T25" s="52"/>
       <c r="U25" s="52" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="V25" s="52"/>
       <c r="W25" s="52"/>
@@ -6636,31 +6792,31 @@
       <c r="AL25" s="52"/>
       <c r="AM25" s="52"/>
       <c r="AN25" s="52" t="s">
+        <v>229</v>
+      </c>
+      <c r="AO25" s="52" t="s">
+        <v>230</v>
+      </c>
+      <c r="AP25" s="52" t="s">
+        <v>420</v>
+      </c>
+      <c r="AQ25" s="52" t="s">
+        <v>231</v>
+      </c>
+      <c r="AR25" s="52" t="s">
         <v>232</v>
       </c>
-      <c r="AO25" s="52" t="s">
-        <v>233</v>
-      </c>
-      <c r="AP25" s="52" t="s">
-        <v>423</v>
-      </c>
-      <c r="AQ25" s="52" t="s">
-        <v>234</v>
-      </c>
-      <c r="AR25" s="52" t="s">
-        <v>235</v>
-      </c>
       <c r="AS25" s="52" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="AT25" s="52" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="AU25" s="52" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="AV25" s="52" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="AW25" s="52"/>
       <c r="AX25" s="52"/>
@@ -6704,7 +6860,7 @@
       <c r="CJ25" s="52"/>
       <c r="CK25" s="52"/>
       <c r="CL25" s="52" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="CM25" s="52"/>
       <c r="CN25" s="52"/>
@@ -6716,44 +6872,44 @@
       <c r="B26" s="52"/>
       <c r="C26" s="52"/>
       <c r="D26" s="52" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="E26" s="52" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="F26" s="52" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="G26" s="52"/>
       <c r="H26" s="52"/>
       <c r="I26" s="52" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="J26" s="52" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="K26" s="52" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="L26" s="52"/>
       <c r="M26" s="52"/>
       <c r="N26" s="52"/>
       <c r="O26" s="52" t="s">
+        <v>225</v>
+      </c>
+      <c r="P26" s="52" t="s">
+        <v>226</v>
+      </c>
+      <c r="Q26" s="52" t="s">
+        <v>227</v>
+      </c>
+      <c r="R26" s="52" t="s">
         <v>228</v>
-      </c>
-      <c r="P26" s="52" t="s">
-        <v>229</v>
-      </c>
-      <c r="Q26" s="52" t="s">
-        <v>230</v>
-      </c>
-      <c r="R26" s="52" t="s">
-        <v>231</v>
       </c>
       <c r="S26" s="52"/>
       <c r="T26" s="52"/>
       <c r="U26" s="52" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="V26" s="52"/>
       <c r="W26" s="52"/>
@@ -6774,31 +6930,31 @@
       <c r="AL26" s="52"/>
       <c r="AM26" s="52"/>
       <c r="AN26" s="52" t="s">
+        <v>229</v>
+      </c>
+      <c r="AO26" s="52" t="s">
+        <v>230</v>
+      </c>
+      <c r="AP26" s="52" t="s">
+        <v>421</v>
+      </c>
+      <c r="AQ26" s="52" t="s">
+        <v>231</v>
+      </c>
+      <c r="AR26" s="52" t="s">
         <v>232</v>
       </c>
-      <c r="AO26" s="52" t="s">
-        <v>233</v>
-      </c>
-      <c r="AP26" s="52" t="s">
-        <v>424</v>
-      </c>
-      <c r="AQ26" s="52" t="s">
-        <v>234</v>
-      </c>
-      <c r="AR26" s="52" t="s">
-        <v>235</v>
-      </c>
       <c r="AS26" s="52" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="AT26" s="52" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="AU26" s="52" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="AV26" s="52" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="AW26" s="52"/>
       <c r="AX26" s="52"/>
@@ -6842,7 +6998,7 @@
       <c r="CJ26" s="52"/>
       <c r="CK26" s="52"/>
       <c r="CL26" s="52" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="CM26" s="52"/>
       <c r="CN26" s="52"/>
@@ -6854,44 +7010,44 @@
       <c r="B27" s="52"/>
       <c r="C27" s="52"/>
       <c r="D27" s="52" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="E27" s="52" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="F27" s="52" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="G27" s="52"/>
       <c r="H27" s="52"/>
       <c r="I27" s="52" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="J27" s="52" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="K27" s="52" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="L27" s="52"/>
       <c r="M27" s="52"/>
       <c r="N27" s="52"/>
       <c r="O27" s="52" t="s">
+        <v>225</v>
+      </c>
+      <c r="P27" s="52" t="s">
+        <v>226</v>
+      </c>
+      <c r="Q27" s="52" t="s">
+        <v>227</v>
+      </c>
+      <c r="R27" s="52" t="s">
         <v>228</v>
-      </c>
-      <c r="P27" s="52" t="s">
-        <v>229</v>
-      </c>
-      <c r="Q27" s="52" t="s">
-        <v>230</v>
-      </c>
-      <c r="R27" s="52" t="s">
-        <v>231</v>
       </c>
       <c r="S27" s="52"/>
       <c r="T27" s="52"/>
       <c r="U27" s="52" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="V27" s="52"/>
       <c r="W27" s="52"/>
@@ -6912,31 +7068,31 @@
       <c r="AL27" s="52"/>
       <c r="AM27" s="52"/>
       <c r="AN27" s="52" t="s">
+        <v>229</v>
+      </c>
+      <c r="AO27" s="52" t="s">
+        <v>230</v>
+      </c>
+      <c r="AP27" s="52" t="s">
+        <v>423</v>
+      </c>
+      <c r="AQ27" s="52" t="s">
+        <v>231</v>
+      </c>
+      <c r="AR27" s="52" t="s">
         <v>232</v>
       </c>
-      <c r="AO27" s="52" t="s">
-        <v>233</v>
-      </c>
-      <c r="AP27" s="52" t="s">
-        <v>426</v>
-      </c>
-      <c r="AQ27" s="52" t="s">
-        <v>234</v>
-      </c>
-      <c r="AR27" s="52" t="s">
-        <v>235</v>
-      </c>
       <c r="AS27" s="52" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="AT27" s="52" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="AU27" s="52" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="AV27" s="52" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="AW27" s="52"/>
       <c r="AX27" s="52"/>
@@ -6980,7 +7136,7 @@
       <c r="CJ27" s="52"/>
       <c r="CK27" s="52"/>
       <c r="CL27" s="52" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="CM27" s="52"/>
       <c r="CN27" s="52"/>
@@ -6992,44 +7148,44 @@
       <c r="B28" s="52"/>
       <c r="C28" s="52"/>
       <c r="D28" s="52" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="E28" s="52" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="F28" s="52" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="G28" s="52"/>
       <c r="H28" s="52"/>
       <c r="I28" s="52" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="J28" s="52" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="K28" s="52" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="L28" s="52"/>
       <c r="M28" s="52"/>
       <c r="N28" s="52"/>
       <c r="O28" s="52" t="s">
+        <v>225</v>
+      </c>
+      <c r="P28" s="52" t="s">
+        <v>226</v>
+      </c>
+      <c r="Q28" s="52" t="s">
+        <v>227</v>
+      </c>
+      <c r="R28" s="52" t="s">
         <v>228</v>
-      </c>
-      <c r="P28" s="52" t="s">
-        <v>229</v>
-      </c>
-      <c r="Q28" s="52" t="s">
-        <v>230</v>
-      </c>
-      <c r="R28" s="52" t="s">
-        <v>231</v>
       </c>
       <c r="S28" s="52"/>
       <c r="T28" s="52"/>
       <c r="U28" s="52" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="V28" s="52"/>
       <c r="W28" s="52"/>
@@ -7050,31 +7206,31 @@
       <c r="AL28" s="52"/>
       <c r="AM28" s="52"/>
       <c r="AN28" s="52" t="s">
+        <v>229</v>
+      </c>
+      <c r="AO28" s="52" t="s">
+        <v>230</v>
+      </c>
+      <c r="AP28" s="52" t="s">
+        <v>424</v>
+      </c>
+      <c r="AQ28" s="52" t="s">
+        <v>231</v>
+      </c>
+      <c r="AR28" s="52" t="s">
         <v>232</v>
       </c>
-      <c r="AO28" s="52" t="s">
+      <c r="AS28" s="52" t="s">
+        <v>425</v>
+      </c>
+      <c r="AT28" s="52" t="s">
         <v>233</v>
       </c>
-      <c r="AP28" s="52" t="s">
-        <v>427</v>
-      </c>
-      <c r="AQ28" s="52" t="s">
+      <c r="AU28" s="52" t="s">
         <v>234</v>
       </c>
-      <c r="AR28" s="52" t="s">
-        <v>235</v>
-      </c>
-      <c r="AS28" s="52" t="s">
-        <v>428</v>
-      </c>
-      <c r="AT28" s="52" t="s">
-        <v>236</v>
-      </c>
-      <c r="AU28" s="52" t="s">
-        <v>237</v>
-      </c>
       <c r="AV28" s="52" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="AW28" s="52"/>
       <c r="AX28" s="52"/>
@@ -7118,7 +7274,7 @@
       <c r="CJ28" s="52"/>
       <c r="CK28" s="52"/>
       <c r="CL28" s="52" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="CM28" s="52"/>
       <c r="CN28" s="52"/>
@@ -7130,44 +7286,44 @@
       <c r="B29" s="52"/>
       <c r="C29" s="52"/>
       <c r="D29" s="52" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="E29" s="52" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="F29" s="52" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="G29" s="52"/>
       <c r="H29" s="52"/>
       <c r="I29" s="52" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="J29" s="52" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="K29" s="52" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="L29" s="52"/>
       <c r="M29" s="52"/>
       <c r="N29" s="52"/>
       <c r="O29" s="52" t="s">
+        <v>225</v>
+      </c>
+      <c r="P29" s="52" t="s">
+        <v>226</v>
+      </c>
+      <c r="Q29" s="52" t="s">
+        <v>227</v>
+      </c>
+      <c r="R29" s="52" t="s">
         <v>228</v>
-      </c>
-      <c r="P29" s="52" t="s">
-        <v>229</v>
-      </c>
-      <c r="Q29" s="52" t="s">
-        <v>230</v>
-      </c>
-      <c r="R29" s="52" t="s">
-        <v>231</v>
       </c>
       <c r="S29" s="52"/>
       <c r="T29" s="52"/>
       <c r="U29" s="52" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="V29" s="52"/>
       <c r="W29" s="52"/>
@@ -7188,31 +7344,31 @@
       <c r="AL29" s="52"/>
       <c r="AM29" s="52"/>
       <c r="AN29" s="52" t="s">
+        <v>229</v>
+      </c>
+      <c r="AO29" s="52" t="s">
+        <v>230</v>
+      </c>
+      <c r="AP29" s="52" t="s">
+        <v>426</v>
+      </c>
+      <c r="AQ29" s="52" t="s">
+        <v>252</v>
+      </c>
+      <c r="AR29" s="52" t="s">
+        <v>253</v>
+      </c>
+      <c r="AS29" s="52" t="s">
+        <v>427</v>
+      </c>
+      <c r="AT29" s="52" t="s">
+        <v>231</v>
+      </c>
+      <c r="AU29" s="52" t="s">
         <v>232</v>
       </c>
-      <c r="AO29" s="52" t="s">
-        <v>233</v>
-      </c>
-      <c r="AP29" s="52" t="s">
-        <v>429</v>
-      </c>
-      <c r="AQ29" s="52" t="s">
-        <v>255</v>
-      </c>
-      <c r="AR29" s="52" t="s">
-        <v>256</v>
-      </c>
-      <c r="AS29" s="52" t="s">
-        <v>430</v>
-      </c>
-      <c r="AT29" s="52" t="s">
-        <v>234</v>
-      </c>
-      <c r="AU29" s="52" t="s">
-        <v>235</v>
-      </c>
       <c r="AV29" s="52" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="AW29" s="52"/>
       <c r="AX29" s="52"/>
@@ -7256,7 +7412,7 @@
       <c r="CJ29" s="52"/>
       <c r="CK29" s="52"/>
       <c r="CL29" s="52" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="CM29" s="52"/>
       <c r="CN29" s="52"/>
@@ -7268,57 +7424,57 @@
       <c r="B30" s="52"/>
       <c r="C30" s="52"/>
       <c r="D30" s="52" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="E30" s="52" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="F30" s="52" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="G30" s="52"/>
       <c r="H30" s="52"/>
       <c r="I30" s="52" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="J30" s="52" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="K30" s="52" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="L30" s="52" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="M30" s="52"/>
       <c r="N30" s="52" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="O30" s="52" t="s">
+        <v>225</v>
+      </c>
+      <c r="P30" s="52" t="s">
+        <v>226</v>
+      </c>
+      <c r="Q30" s="52" t="s">
+        <v>227</v>
+      </c>
+      <c r="R30" s="52" t="s">
         <v>228</v>
-      </c>
-      <c r="P30" s="52" t="s">
-        <v>229</v>
-      </c>
-      <c r="Q30" s="52" t="s">
-        <v>230</v>
-      </c>
-      <c r="R30" s="52" t="s">
-        <v>231</v>
       </c>
       <c r="S30" s="52"/>
       <c r="T30" s="52"/>
       <c r="U30" s="52" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="V30" s="52" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="W30" s="52" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="X30" s="52" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="Y30" s="52"/>
       <c r="Z30" s="52"/>
@@ -7336,31 +7492,31 @@
       <c r="AL30" s="52"/>
       <c r="AM30" s="52"/>
       <c r="AN30" s="52" t="s">
+        <v>229</v>
+      </c>
+      <c r="AO30" s="52" t="s">
+        <v>230</v>
+      </c>
+      <c r="AP30" s="52" t="s">
+        <v>429</v>
+      </c>
+      <c r="AQ30" s="52" t="s">
+        <v>237</v>
+      </c>
+      <c r="AR30" s="52" t="s">
+        <v>238</v>
+      </c>
+      <c r="AS30" s="52" t="s">
+        <v>430</v>
+      </c>
+      <c r="AT30" s="52" t="s">
+        <v>231</v>
+      </c>
+      <c r="AU30" s="52" t="s">
         <v>232</v>
       </c>
-      <c r="AO30" s="52" t="s">
-        <v>233</v>
-      </c>
-      <c r="AP30" s="52" t="s">
-        <v>432</v>
-      </c>
-      <c r="AQ30" s="52" t="s">
-        <v>240</v>
-      </c>
-      <c r="AR30" s="52" t="s">
-        <v>241</v>
-      </c>
-      <c r="AS30" s="52" t="s">
-        <v>433</v>
-      </c>
-      <c r="AT30" s="52" t="s">
-        <v>234</v>
-      </c>
-      <c r="AU30" s="52" t="s">
-        <v>235</v>
-      </c>
       <c r="AV30" s="52" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="AW30" s="52"/>
       <c r="AX30" s="52"/>
@@ -7404,7 +7560,7 @@
       <c r="CJ30" s="52"/>
       <c r="CK30" s="52"/>
       <c r="CL30" s="52" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="CM30" s="52"/>
       <c r="CN30" s="52"/>
@@ -7416,44 +7572,44 @@
       <c r="B31" s="52"/>
       <c r="C31" s="52"/>
       <c r="D31" s="52" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="E31" s="52" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="F31" s="52" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="G31" s="52"/>
       <c r="H31" s="52"/>
       <c r="I31" s="52" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="J31" s="52" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="K31" s="52" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="L31" s="52"/>
       <c r="M31" s="52"/>
       <c r="N31" s="52"/>
       <c r="O31" s="52" t="s">
+        <v>225</v>
+      </c>
+      <c r="P31" s="52" t="s">
+        <v>226</v>
+      </c>
+      <c r="Q31" s="52" t="s">
+        <v>227</v>
+      </c>
+      <c r="R31" s="52" t="s">
         <v>228</v>
-      </c>
-      <c r="P31" s="52" t="s">
-        <v>229</v>
-      </c>
-      <c r="Q31" s="52" t="s">
-        <v>230</v>
-      </c>
-      <c r="R31" s="52" t="s">
-        <v>231</v>
       </c>
       <c r="S31" s="52"/>
       <c r="T31" s="52"/>
       <c r="U31" s="52" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="V31" s="52"/>
       <c r="W31" s="52"/>
@@ -7474,31 +7630,31 @@
       <c r="AL31" s="52"/>
       <c r="AM31" s="52"/>
       <c r="AN31" s="52" t="s">
+        <v>229</v>
+      </c>
+      <c r="AO31" s="52" t="s">
+        <v>230</v>
+      </c>
+      <c r="AP31" s="52" t="s">
+        <v>431</v>
+      </c>
+      <c r="AQ31" s="52" t="s">
+        <v>252</v>
+      </c>
+      <c r="AR31" s="52" t="s">
+        <v>253</v>
+      </c>
+      <c r="AS31" s="52" t="s">
+        <v>427</v>
+      </c>
+      <c r="AT31" s="52" t="s">
+        <v>231</v>
+      </c>
+      <c r="AU31" s="52" t="s">
         <v>232</v>
       </c>
-      <c r="AO31" s="52" t="s">
-        <v>233</v>
-      </c>
-      <c r="AP31" s="52" t="s">
-        <v>434</v>
-      </c>
-      <c r="AQ31" s="52" t="s">
-        <v>255</v>
-      </c>
-      <c r="AR31" s="52" t="s">
-        <v>256</v>
-      </c>
-      <c r="AS31" s="52" t="s">
-        <v>430</v>
-      </c>
-      <c r="AT31" s="52" t="s">
-        <v>234</v>
-      </c>
-      <c r="AU31" s="52" t="s">
-        <v>235</v>
-      </c>
       <c r="AV31" s="52" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="AW31" s="52"/>
       <c r="AX31" s="52"/>
@@ -7542,7 +7698,7 @@
       <c r="CJ31" s="52"/>
       <c r="CK31" s="52"/>
       <c r="CL31" s="52" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="CM31" s="52"/>
       <c r="CN31" s="52"/>
@@ -7554,44 +7710,44 @@
       <c r="B32" s="52"/>
       <c r="C32" s="52"/>
       <c r="D32" s="52" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="E32" s="52" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="F32" s="52" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="G32" s="52"/>
       <c r="H32" s="52"/>
       <c r="I32" s="52" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="J32" s="52" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="K32" s="52" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="L32" s="52"/>
       <c r="M32" s="52"/>
       <c r="N32" s="52"/>
       <c r="O32" s="52" t="s">
+        <v>225</v>
+      </c>
+      <c r="P32" s="52" t="s">
+        <v>226</v>
+      </c>
+      <c r="Q32" s="52" t="s">
+        <v>227</v>
+      </c>
+      <c r="R32" s="52" t="s">
         <v>228</v>
-      </c>
-      <c r="P32" s="52" t="s">
-        <v>229</v>
-      </c>
-      <c r="Q32" s="52" t="s">
-        <v>230</v>
-      </c>
-      <c r="R32" s="52" t="s">
-        <v>231</v>
       </c>
       <c r="S32" s="52"/>
       <c r="T32" s="52"/>
       <c r="U32" s="52" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="V32" s="52"/>
       <c r="W32" s="52"/>
@@ -7612,31 +7768,31 @@
       <c r="AL32" s="52"/>
       <c r="AM32" s="52"/>
       <c r="AN32" s="52" t="s">
+        <v>229</v>
+      </c>
+      <c r="AO32" s="52" t="s">
+        <v>230</v>
+      </c>
+      <c r="AP32" s="52" t="s">
+        <v>431</v>
+      </c>
+      <c r="AQ32" s="52" t="s">
+        <v>252</v>
+      </c>
+      <c r="AR32" s="52" t="s">
+        <v>253</v>
+      </c>
+      <c r="AS32" s="52" t="s">
+        <v>427</v>
+      </c>
+      <c r="AT32" s="52" t="s">
+        <v>231</v>
+      </c>
+      <c r="AU32" s="52" t="s">
         <v>232</v>
       </c>
-      <c r="AO32" s="52" t="s">
-        <v>233</v>
-      </c>
-      <c r="AP32" s="52" t="s">
-        <v>434</v>
-      </c>
-      <c r="AQ32" s="52" t="s">
-        <v>255</v>
-      </c>
-      <c r="AR32" s="52" t="s">
-        <v>256</v>
-      </c>
-      <c r="AS32" s="52" t="s">
-        <v>430</v>
-      </c>
-      <c r="AT32" s="52" t="s">
-        <v>234</v>
-      </c>
-      <c r="AU32" s="52" t="s">
-        <v>235</v>
-      </c>
       <c r="AV32" s="52" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="AW32" s="52"/>
       <c r="AX32" s="52"/>
@@ -7680,7 +7836,7 @@
       <c r="CJ32" s="52"/>
       <c r="CK32" s="52"/>
       <c r="CL32" s="52" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="CM32" s="52"/>
       <c r="CN32" s="52"/>
@@ -7692,44 +7848,44 @@
       <c r="B33" s="52"/>
       <c r="C33" s="52"/>
       <c r="D33" s="52" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="E33" s="52" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="F33" s="52" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="G33" s="52"/>
       <c r="H33" s="52"/>
       <c r="I33" s="52" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="J33" s="52" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="K33" s="52" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="L33" s="52"/>
       <c r="M33" s="52"/>
       <c r="N33" s="52"/>
       <c r="O33" s="52" t="s">
+        <v>225</v>
+      </c>
+      <c r="P33" s="52" t="s">
+        <v>226</v>
+      </c>
+      <c r="Q33" s="52" t="s">
+        <v>227</v>
+      </c>
+      <c r="R33" s="52" t="s">
         <v>228</v>
-      </c>
-      <c r="P33" s="52" t="s">
-        <v>229</v>
-      </c>
-      <c r="Q33" s="52" t="s">
-        <v>230</v>
-      </c>
-      <c r="R33" s="52" t="s">
-        <v>231</v>
       </c>
       <c r="S33" s="52"/>
       <c r="T33" s="52"/>
       <c r="U33" s="52" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="V33" s="52"/>
       <c r="W33" s="52"/>
@@ -7750,31 +7906,31 @@
       <c r="AL33" s="52"/>
       <c r="AM33" s="52"/>
       <c r="AN33" s="52" t="s">
+        <v>229</v>
+      </c>
+      <c r="AO33" s="52" t="s">
+        <v>230</v>
+      </c>
+      <c r="AP33" s="52" t="s">
+        <v>431</v>
+      </c>
+      <c r="AQ33" s="52" t="s">
+        <v>252</v>
+      </c>
+      <c r="AR33" s="52" t="s">
+        <v>253</v>
+      </c>
+      <c r="AS33" s="52" t="s">
+        <v>427</v>
+      </c>
+      <c r="AT33" s="52" t="s">
+        <v>231</v>
+      </c>
+      <c r="AU33" s="52" t="s">
         <v>232</v>
       </c>
-      <c r="AO33" s="52" t="s">
-        <v>233</v>
-      </c>
-      <c r="AP33" s="52" t="s">
-        <v>434</v>
-      </c>
-      <c r="AQ33" s="52" t="s">
-        <v>255</v>
-      </c>
-      <c r="AR33" s="52" t="s">
-        <v>256</v>
-      </c>
-      <c r="AS33" s="52" t="s">
-        <v>430</v>
-      </c>
-      <c r="AT33" s="52" t="s">
-        <v>234</v>
-      </c>
-      <c r="AU33" s="52" t="s">
-        <v>235</v>
-      </c>
       <c r="AV33" s="52" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="AW33" s="52"/>
       <c r="AX33" s="52"/>
@@ -7818,7 +7974,7 @@
       <c r="CJ33" s="52"/>
       <c r="CK33" s="52"/>
       <c r="CL33" s="52" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="CM33" s="52"/>
       <c r="CN33" s="52"/>
@@ -7830,44 +7986,44 @@
       <c r="B34" s="52"/>
       <c r="C34" s="52"/>
       <c r="D34" s="52" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="E34" s="52" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="F34" s="52" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="G34" s="52"/>
       <c r="H34" s="52"/>
       <c r="I34" s="52" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="J34" s="52" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="K34" s="52" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="L34" s="52"/>
       <c r="M34" s="52"/>
       <c r="N34" s="52"/>
       <c r="O34" s="52" t="s">
+        <v>225</v>
+      </c>
+      <c r="P34" s="52" t="s">
+        <v>226</v>
+      </c>
+      <c r="Q34" s="52" t="s">
+        <v>227</v>
+      </c>
+      <c r="R34" s="52" t="s">
         <v>228</v>
-      </c>
-      <c r="P34" s="52" t="s">
-        <v>229</v>
-      </c>
-      <c r="Q34" s="52" t="s">
-        <v>230</v>
-      </c>
-      <c r="R34" s="52" t="s">
-        <v>231</v>
       </c>
       <c r="S34" s="52"/>
       <c r="T34" s="52"/>
       <c r="U34" s="52" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="V34" s="52"/>
       <c r="W34" s="52"/>
@@ -7888,31 +8044,31 @@
       <c r="AL34" s="52"/>
       <c r="AM34" s="52"/>
       <c r="AN34" s="52" t="s">
+        <v>229</v>
+      </c>
+      <c r="AO34" s="52" t="s">
+        <v>230</v>
+      </c>
+      <c r="AP34" s="52" t="s">
+        <v>431</v>
+      </c>
+      <c r="AQ34" s="52" t="s">
+        <v>252</v>
+      </c>
+      <c r="AR34" s="52" t="s">
+        <v>253</v>
+      </c>
+      <c r="AS34" s="52" t="s">
+        <v>427</v>
+      </c>
+      <c r="AT34" s="52" t="s">
+        <v>231</v>
+      </c>
+      <c r="AU34" s="52" t="s">
         <v>232</v>
       </c>
-      <c r="AO34" s="52" t="s">
-        <v>233</v>
-      </c>
-      <c r="AP34" s="52" t="s">
-        <v>434</v>
-      </c>
-      <c r="AQ34" s="52" t="s">
-        <v>255</v>
-      </c>
-      <c r="AR34" s="52" t="s">
-        <v>256</v>
-      </c>
-      <c r="AS34" s="52" t="s">
-        <v>430</v>
-      </c>
-      <c r="AT34" s="52" t="s">
-        <v>234</v>
-      </c>
-      <c r="AU34" s="52" t="s">
-        <v>235</v>
-      </c>
       <c r="AV34" s="52" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="AW34" s="52"/>
       <c r="AX34" s="52"/>
@@ -7956,7 +8112,7 @@
       <c r="CJ34" s="52"/>
       <c r="CK34" s="52"/>
       <c r="CL34" s="52" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="CM34" s="52"/>
       <c r="CN34" s="52"/>
@@ -7968,44 +8124,44 @@
       <c r="B35" s="52"/>
       <c r="C35" s="52"/>
       <c r="D35" s="52" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="E35" s="52" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="F35" s="52" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="G35" s="52"/>
       <c r="H35" s="52"/>
       <c r="I35" s="52" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="J35" s="52" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="K35" s="52" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="L35" s="52"/>
       <c r="M35" s="52"/>
       <c r="N35" s="52"/>
       <c r="O35" s="52" t="s">
+        <v>225</v>
+      </c>
+      <c r="P35" s="52" t="s">
+        <v>226</v>
+      </c>
+      <c r="Q35" s="52" t="s">
+        <v>227</v>
+      </c>
+      <c r="R35" s="52" t="s">
         <v>228</v>
-      </c>
-      <c r="P35" s="52" t="s">
-        <v>229</v>
-      </c>
-      <c r="Q35" s="52" t="s">
-        <v>230</v>
-      </c>
-      <c r="R35" s="52" t="s">
-        <v>231</v>
       </c>
       <c r="S35" s="52"/>
       <c r="T35" s="52"/>
       <c r="U35" s="52" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="V35" s="52"/>
       <c r="W35" s="52"/>
@@ -8026,31 +8182,31 @@
       <c r="AL35" s="52"/>
       <c r="AM35" s="52"/>
       <c r="AN35" s="52" t="s">
+        <v>229</v>
+      </c>
+      <c r="AO35" s="52" t="s">
+        <v>230</v>
+      </c>
+      <c r="AP35" s="52" t="s">
+        <v>433</v>
+      </c>
+      <c r="AQ35" s="52" t="s">
+        <v>237</v>
+      </c>
+      <c r="AR35" s="52" t="s">
+        <v>238</v>
+      </c>
+      <c r="AS35" s="52" t="s">
+        <v>434</v>
+      </c>
+      <c r="AT35" s="52" t="s">
+        <v>231</v>
+      </c>
+      <c r="AU35" s="52" t="s">
         <v>232</v>
       </c>
-      <c r="AO35" s="52" t="s">
-        <v>233</v>
-      </c>
-      <c r="AP35" s="52" t="s">
-        <v>436</v>
-      </c>
-      <c r="AQ35" s="52" t="s">
-        <v>240</v>
-      </c>
-      <c r="AR35" s="52" t="s">
-        <v>241</v>
-      </c>
-      <c r="AS35" s="52" t="s">
-        <v>437</v>
-      </c>
-      <c r="AT35" s="52" t="s">
-        <v>234</v>
-      </c>
-      <c r="AU35" s="52" t="s">
-        <v>235</v>
-      </c>
       <c r="AV35" s="52" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="AW35" s="52"/>
       <c r="AX35" s="52"/>
@@ -8094,7 +8250,7 @@
       <c r="CJ35" s="52"/>
       <c r="CK35" s="52"/>
       <c r="CL35" s="52" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="CM35" s="52"/>
       <c r="CN35" s="52"/>
@@ -8106,44 +8262,44 @@
       <c r="B36" s="52"/>
       <c r="C36" s="52"/>
       <c r="D36" s="52" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="E36" s="52" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="F36" s="52" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="G36" s="52"/>
       <c r="H36" s="52"/>
       <c r="I36" s="52" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="J36" s="52" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="K36" s="52" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="L36" s="52"/>
       <c r="M36" s="52"/>
       <c r="N36" s="52"/>
       <c r="O36" s="52" t="s">
+        <v>225</v>
+      </c>
+      <c r="P36" s="52" t="s">
+        <v>226</v>
+      </c>
+      <c r="Q36" s="52" t="s">
+        <v>227</v>
+      </c>
+      <c r="R36" s="52" t="s">
         <v>228</v>
-      </c>
-      <c r="P36" s="52" t="s">
-        <v>229</v>
-      </c>
-      <c r="Q36" s="52" t="s">
-        <v>230</v>
-      </c>
-      <c r="R36" s="52" t="s">
-        <v>231</v>
       </c>
       <c r="S36" s="52"/>
       <c r="T36" s="52"/>
       <c r="U36" s="52" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="V36" s="52"/>
       <c r="W36" s="52"/>
@@ -8164,31 +8320,31 @@
       <c r="AL36" s="52"/>
       <c r="AM36" s="52"/>
       <c r="AN36" s="52" t="s">
+        <v>229</v>
+      </c>
+      <c r="AO36" s="52" t="s">
+        <v>230</v>
+      </c>
+      <c r="AP36" s="52" t="s">
+        <v>436</v>
+      </c>
+      <c r="AQ36" s="52" t="s">
+        <v>269</v>
+      </c>
+      <c r="AR36" s="52" t="s">
+        <v>270</v>
+      </c>
+      <c r="AS36" s="52" t="s">
+        <v>401</v>
+      </c>
+      <c r="AT36" s="52" t="s">
+        <v>231</v>
+      </c>
+      <c r="AU36" s="52" t="s">
         <v>232</v>
       </c>
-      <c r="AO36" s="52" t="s">
-        <v>233</v>
-      </c>
-      <c r="AP36" s="52" t="s">
-        <v>439</v>
-      </c>
-      <c r="AQ36" s="52" t="s">
-        <v>272</v>
-      </c>
-      <c r="AR36" s="52" t="s">
-        <v>273</v>
-      </c>
-      <c r="AS36" s="52" t="s">
-        <v>404</v>
-      </c>
-      <c r="AT36" s="52" t="s">
-        <v>234</v>
-      </c>
-      <c r="AU36" s="52" t="s">
-        <v>235</v>
-      </c>
       <c r="AV36" s="52" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="AW36" s="52"/>
       <c r="AX36" s="52"/>
@@ -8232,7 +8388,7 @@
       <c r="CJ36" s="52"/>
       <c r="CK36" s="52"/>
       <c r="CL36" s="52" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="CM36" s="52"/>
       <c r="CN36" s="52"/>
@@ -8244,44 +8400,44 @@
       <c r="B37" s="52"/>
       <c r="C37" s="52"/>
       <c r="D37" s="52" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="E37" s="52" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="F37" s="52" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="G37" s="52"/>
       <c r="H37" s="52"/>
       <c r="I37" s="52" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="J37" s="52" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="K37" s="52" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="L37" s="52"/>
       <c r="M37" s="52"/>
       <c r="N37" s="52"/>
       <c r="O37" s="52" t="s">
+        <v>225</v>
+      </c>
+      <c r="P37" s="52" t="s">
+        <v>226</v>
+      </c>
+      <c r="Q37" s="52" t="s">
+        <v>227</v>
+      </c>
+      <c r="R37" s="52" t="s">
         <v>228</v>
-      </c>
-      <c r="P37" s="52" t="s">
-        <v>229</v>
-      </c>
-      <c r="Q37" s="52" t="s">
-        <v>230</v>
-      </c>
-      <c r="R37" s="52" t="s">
-        <v>231</v>
       </c>
       <c r="S37" s="52"/>
       <c r="T37" s="52"/>
       <c r="U37" s="52" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="V37" s="52"/>
       <c r="W37" s="52"/>
@@ -8302,31 +8458,31 @@
       <c r="AL37" s="52"/>
       <c r="AM37" s="52"/>
       <c r="AN37" s="52" t="s">
+        <v>229</v>
+      </c>
+      <c r="AO37" s="52" t="s">
+        <v>230</v>
+      </c>
+      <c r="AP37" s="52" t="s">
+        <v>437</v>
+      </c>
+      <c r="AQ37" s="52" t="s">
+        <v>302</v>
+      </c>
+      <c r="AR37" s="52" t="s">
+        <v>303</v>
+      </c>
+      <c r="AS37" s="52" t="s">
+        <v>438</v>
+      </c>
+      <c r="AT37" s="52" t="s">
+        <v>231</v>
+      </c>
+      <c r="AU37" s="52" t="s">
         <v>232</v>
       </c>
-      <c r="AO37" s="52" t="s">
-        <v>233</v>
-      </c>
-      <c r="AP37" s="52" t="s">
-        <v>440</v>
-      </c>
-      <c r="AQ37" s="52" t="s">
-        <v>305</v>
-      </c>
-      <c r="AR37" s="52" t="s">
-        <v>306</v>
-      </c>
-      <c r="AS37" s="52" t="s">
-        <v>441</v>
-      </c>
-      <c r="AT37" s="52" t="s">
-        <v>234</v>
-      </c>
-      <c r="AU37" s="52" t="s">
-        <v>235</v>
-      </c>
       <c r="AV37" s="52" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="AW37" s="52"/>
       <c r="AX37" s="52"/>
@@ -8370,7 +8526,7 @@
       <c r="CJ37" s="52"/>
       <c r="CK37" s="52"/>
       <c r="CL37" s="52" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="CM37" s="52"/>
       <c r="CN37" s="52"/>
@@ -8382,44 +8538,44 @@
       <c r="B38" s="52"/>
       <c r="C38" s="52"/>
       <c r="D38" s="52" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="E38" s="52" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="F38" s="52" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="G38" s="52"/>
       <c r="H38" s="52"/>
       <c r="I38" s="52" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="J38" s="52" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="K38" s="52" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="L38" s="52"/>
       <c r="M38" s="52"/>
       <c r="N38" s="52"/>
       <c r="O38" s="52" t="s">
+        <v>225</v>
+      </c>
+      <c r="P38" s="52" t="s">
+        <v>226</v>
+      </c>
+      <c r="Q38" s="52" t="s">
+        <v>227</v>
+      </c>
+      <c r="R38" s="52" t="s">
         <v>228</v>
-      </c>
-      <c r="P38" s="52" t="s">
-        <v>229</v>
-      </c>
-      <c r="Q38" s="52" t="s">
-        <v>230</v>
-      </c>
-      <c r="R38" s="52" t="s">
-        <v>231</v>
       </c>
       <c r="S38" s="52"/>
       <c r="T38" s="52"/>
       <c r="U38" s="52" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="V38" s="52"/>
       <c r="W38" s="52"/>
@@ -8440,31 +8596,31 @@
       <c r="AL38" s="52"/>
       <c r="AM38" s="52"/>
       <c r="AN38" s="52" t="s">
+        <v>229</v>
+      </c>
+      <c r="AO38" s="52" t="s">
+        <v>230</v>
+      </c>
+      <c r="AP38" s="52" t="s">
+        <v>420</v>
+      </c>
+      <c r="AQ38" s="52" t="s">
+        <v>292</v>
+      </c>
+      <c r="AR38" s="52" t="s">
+        <v>293</v>
+      </c>
+      <c r="AS38" s="52" t="s">
+        <v>439</v>
+      </c>
+      <c r="AT38" s="52" t="s">
+        <v>231</v>
+      </c>
+      <c r="AU38" s="52" t="s">
         <v>232</v>
       </c>
-      <c r="AO38" s="52" t="s">
-        <v>233</v>
-      </c>
-      <c r="AP38" s="52" t="s">
-        <v>423</v>
-      </c>
-      <c r="AQ38" s="52" t="s">
-        <v>295</v>
-      </c>
-      <c r="AR38" s="52" t="s">
-        <v>296</v>
-      </c>
-      <c r="AS38" s="52" t="s">
-        <v>442</v>
-      </c>
-      <c r="AT38" s="52" t="s">
-        <v>234</v>
-      </c>
-      <c r="AU38" s="52" t="s">
-        <v>235</v>
-      </c>
       <c r="AV38" s="52" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="AW38" s="52"/>
       <c r="AX38" s="52"/>
@@ -8508,7 +8664,7 @@
       <c r="CJ38" s="52"/>
       <c r="CK38" s="52"/>
       <c r="CL38" s="52" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="CM38" s="52"/>
       <c r="CN38" s="52"/>
@@ -8520,44 +8676,44 @@
       <c r="B39" s="52"/>
       <c r="C39" s="52"/>
       <c r="D39" s="52" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="E39" s="52" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="F39" s="52" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="G39" s="52"/>
       <c r="H39" s="52"/>
       <c r="I39" s="52" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="J39" s="52" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="K39" s="52" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="L39" s="52"/>
       <c r="M39" s="52"/>
       <c r="N39" s="52"/>
       <c r="O39" s="52" t="s">
+        <v>225</v>
+      </c>
+      <c r="P39" s="52" t="s">
+        <v>226</v>
+      </c>
+      <c r="Q39" s="52" t="s">
+        <v>227</v>
+      </c>
+      <c r="R39" s="52" t="s">
         <v>228</v>
-      </c>
-      <c r="P39" s="52" t="s">
-        <v>229</v>
-      </c>
-      <c r="Q39" s="52" t="s">
-        <v>230</v>
-      </c>
-      <c r="R39" s="52" t="s">
-        <v>231</v>
       </c>
       <c r="S39" s="52"/>
       <c r="T39" s="52"/>
       <c r="U39" s="52" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="V39" s="52"/>
       <c r="W39" s="52"/>
@@ -8578,31 +8734,31 @@
       <c r="AL39" s="52"/>
       <c r="AM39" s="52"/>
       <c r="AN39" s="52" t="s">
+        <v>229</v>
+      </c>
+      <c r="AO39" s="52" t="s">
+        <v>230</v>
+      </c>
+      <c r="AP39" s="52" t="s">
+        <v>440</v>
+      </c>
+      <c r="AQ39" s="52" t="s">
+        <v>308</v>
+      </c>
+      <c r="AR39" s="52" t="s">
+        <v>309</v>
+      </c>
+      <c r="AS39" s="52" t="s">
+        <v>441</v>
+      </c>
+      <c r="AT39" s="52" t="s">
+        <v>231</v>
+      </c>
+      <c r="AU39" s="52" t="s">
         <v>232</v>
       </c>
-      <c r="AO39" s="52" t="s">
-        <v>233</v>
-      </c>
-      <c r="AP39" s="52" t="s">
-        <v>443</v>
-      </c>
-      <c r="AQ39" s="52" t="s">
-        <v>311</v>
-      </c>
-      <c r="AR39" s="52" t="s">
-        <v>312</v>
-      </c>
-      <c r="AS39" s="52" t="s">
-        <v>444</v>
-      </c>
-      <c r="AT39" s="52" t="s">
-        <v>234</v>
-      </c>
-      <c r="AU39" s="52" t="s">
-        <v>235</v>
-      </c>
       <c r="AV39" s="52" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="AW39" s="52"/>
       <c r="AX39" s="52"/>
@@ -8646,7 +8802,7 @@
       <c r="CJ39" s="52"/>
       <c r="CK39" s="52"/>
       <c r="CL39" s="52" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="CM39" s="52"/>
       <c r="CN39" s="52"/>
@@ -8658,44 +8814,44 @@
       <c r="B40" s="52"/>
       <c r="C40" s="52"/>
       <c r="D40" s="52" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="E40" s="52" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="F40" s="52" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="G40" s="52"/>
       <c r="H40" s="52"/>
       <c r="I40" s="52" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="J40" s="52" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="K40" s="52" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="L40" s="52"/>
       <c r="M40" s="52"/>
       <c r="N40" s="52"/>
       <c r="O40" s="52" t="s">
+        <v>225</v>
+      </c>
+      <c r="P40" s="52" t="s">
+        <v>226</v>
+      </c>
+      <c r="Q40" s="52" t="s">
+        <v>227</v>
+      </c>
+      <c r="R40" s="52" t="s">
         <v>228</v>
-      </c>
-      <c r="P40" s="52" t="s">
-        <v>229</v>
-      </c>
-      <c r="Q40" s="52" t="s">
-        <v>230</v>
-      </c>
-      <c r="R40" s="52" t="s">
-        <v>231</v>
       </c>
       <c r="S40" s="52"/>
       <c r="T40" s="52"/>
       <c r="U40" s="52" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="V40" s="52"/>
       <c r="W40" s="52"/>
@@ -8716,31 +8872,31 @@
       <c r="AL40" s="52"/>
       <c r="AM40" s="52"/>
       <c r="AN40" s="52" t="s">
+        <v>229</v>
+      </c>
+      <c r="AO40" s="52" t="s">
+        <v>230</v>
+      </c>
+      <c r="AP40" s="52" t="s">
+        <v>442</v>
+      </c>
+      <c r="AQ40" s="52" t="s">
+        <v>244</v>
+      </c>
+      <c r="AR40" s="52" t="s">
+        <v>245</v>
+      </c>
+      <c r="AS40" s="52" t="s">
+        <v>443</v>
+      </c>
+      <c r="AT40" s="52" t="s">
+        <v>231</v>
+      </c>
+      <c r="AU40" s="52" t="s">
         <v>232</v>
       </c>
-      <c r="AO40" s="52" t="s">
-        <v>233</v>
-      </c>
-      <c r="AP40" s="52" t="s">
-        <v>445</v>
-      </c>
-      <c r="AQ40" s="52" t="s">
-        <v>247</v>
-      </c>
-      <c r="AR40" s="52" t="s">
-        <v>248</v>
-      </c>
-      <c r="AS40" s="52" t="s">
-        <v>446</v>
-      </c>
-      <c r="AT40" s="52" t="s">
-        <v>234</v>
-      </c>
-      <c r="AU40" s="52" t="s">
-        <v>235</v>
-      </c>
       <c r="AV40" s="52" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="AW40" s="52"/>
       <c r="AX40" s="52"/>
@@ -8784,7 +8940,7 @@
       <c r="CJ40" s="52"/>
       <c r="CK40" s="52"/>
       <c r="CL40" s="52" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="CM40" s="52"/>
       <c r="CN40" s="52"/>
@@ -8796,44 +8952,44 @@
       <c r="B41" s="52"/>
       <c r="C41" s="52"/>
       <c r="D41" s="52" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="E41" s="52" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="F41" s="52" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="G41" s="52"/>
       <c r="H41" s="52"/>
       <c r="I41" s="52" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="J41" s="52" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="K41" s="52" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="L41" s="52"/>
       <c r="M41" s="52"/>
       <c r="N41" s="52"/>
       <c r="O41" s="52" t="s">
+        <v>225</v>
+      </c>
+      <c r="P41" s="52" t="s">
+        <v>226</v>
+      </c>
+      <c r="Q41" s="52" t="s">
+        <v>227</v>
+      </c>
+      <c r="R41" s="52" t="s">
         <v>228</v>
-      </c>
-      <c r="P41" s="52" t="s">
-        <v>229</v>
-      </c>
-      <c r="Q41" s="52" t="s">
-        <v>230</v>
-      </c>
-      <c r="R41" s="52" t="s">
-        <v>231</v>
       </c>
       <c r="S41" s="52"/>
       <c r="T41" s="52"/>
       <c r="U41" s="52" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="V41" s="52"/>
       <c r="W41" s="52"/>
@@ -8854,31 +9010,31 @@
       <c r="AL41" s="52"/>
       <c r="AM41" s="52"/>
       <c r="AN41" s="52" t="s">
+        <v>229</v>
+      </c>
+      <c r="AO41" s="52" t="s">
+        <v>230</v>
+      </c>
+      <c r="AP41" s="52" t="s">
+        <v>444</v>
+      </c>
+      <c r="AQ41" s="52" t="s">
+        <v>241</v>
+      </c>
+      <c r="AR41" s="52" t="s">
+        <v>242</v>
+      </c>
+      <c r="AS41" s="52" t="s">
+        <v>445</v>
+      </c>
+      <c r="AT41" s="52" t="s">
+        <v>231</v>
+      </c>
+      <c r="AU41" s="52" t="s">
         <v>232</v>
       </c>
-      <c r="AO41" s="52" t="s">
-        <v>233</v>
-      </c>
-      <c r="AP41" s="52" t="s">
-        <v>447</v>
-      </c>
-      <c r="AQ41" s="52" t="s">
-        <v>244</v>
-      </c>
-      <c r="AR41" s="52" t="s">
-        <v>245</v>
-      </c>
-      <c r="AS41" s="52" t="s">
-        <v>448</v>
-      </c>
-      <c r="AT41" s="52" t="s">
-        <v>234</v>
-      </c>
-      <c r="AU41" s="52" t="s">
-        <v>235</v>
-      </c>
       <c r="AV41" s="52" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="AW41" s="52"/>
       <c r="AX41" s="52"/>
@@ -8922,7 +9078,7 @@
       <c r="CJ41" s="52"/>
       <c r="CK41" s="52"/>
       <c r="CL41" s="52" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="CM41" s="52"/>
       <c r="CN41" s="52"/>
@@ -8934,44 +9090,44 @@
       <c r="B42" s="52"/>
       <c r="C42" s="52"/>
       <c r="D42" s="52" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="E42" s="52" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="F42" s="52" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="G42" s="52"/>
       <c r="H42" s="52"/>
       <c r="I42" s="52" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="J42" s="52" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="K42" s="52" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="L42" s="52"/>
       <c r="M42" s="52"/>
       <c r="N42" s="52"/>
       <c r="O42" s="52" t="s">
+        <v>225</v>
+      </c>
+      <c r="P42" s="52" t="s">
+        <v>226</v>
+      </c>
+      <c r="Q42" s="52" t="s">
+        <v>227</v>
+      </c>
+      <c r="R42" s="52" t="s">
         <v>228</v>
-      </c>
-      <c r="P42" s="52" t="s">
-        <v>229</v>
-      </c>
-      <c r="Q42" s="52" t="s">
-        <v>230</v>
-      </c>
-      <c r="R42" s="52" t="s">
-        <v>231</v>
       </c>
       <c r="S42" s="52"/>
       <c r="T42" s="52"/>
       <c r="U42" s="52" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="V42" s="52"/>
       <c r="W42" s="52"/>
@@ -8992,31 +9148,31 @@
       <c r="AL42" s="52"/>
       <c r="AM42" s="52"/>
       <c r="AN42" s="52" t="s">
+        <v>229</v>
+      </c>
+      <c r="AO42" s="52" t="s">
+        <v>230</v>
+      </c>
+      <c r="AP42" s="52" t="s">
+        <v>446</v>
+      </c>
+      <c r="AQ42" s="52" t="s">
+        <v>233</v>
+      </c>
+      <c r="AR42" s="52" t="s">
+        <v>234</v>
+      </c>
+      <c r="AS42" s="52" t="s">
+        <v>406</v>
+      </c>
+      <c r="AT42" s="52" t="s">
+        <v>231</v>
+      </c>
+      <c r="AU42" s="52" t="s">
         <v>232</v>
       </c>
-      <c r="AO42" s="52" t="s">
-        <v>233</v>
-      </c>
-      <c r="AP42" s="52" t="s">
-        <v>449</v>
-      </c>
-      <c r="AQ42" s="52" t="s">
-        <v>236</v>
-      </c>
-      <c r="AR42" s="52" t="s">
-        <v>237</v>
-      </c>
-      <c r="AS42" s="52" t="s">
-        <v>409</v>
-      </c>
-      <c r="AT42" s="52" t="s">
-        <v>234</v>
-      </c>
-      <c r="AU42" s="52" t="s">
-        <v>235</v>
-      </c>
       <c r="AV42" s="52" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="AW42" s="52"/>
       <c r="AX42" s="52"/>
@@ -9060,7 +9216,7 @@
       <c r="CJ42" s="52"/>
       <c r="CK42" s="52"/>
       <c r="CL42" s="52" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="CM42" s="52"/>
       <c r="CN42" s="52"/>
@@ -9072,44 +9228,44 @@
       <c r="B43" s="52"/>
       <c r="C43" s="52"/>
       <c r="D43" s="52" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="E43" s="52" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="F43" s="52" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="G43" s="52"/>
       <c r="H43" s="52"/>
       <c r="I43" s="52" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="J43" s="52" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="K43" s="52" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="L43" s="52"/>
       <c r="M43" s="52"/>
       <c r="N43" s="52"/>
       <c r="O43" s="52" t="s">
+        <v>225</v>
+      </c>
+      <c r="P43" s="52" t="s">
+        <v>226</v>
+      </c>
+      <c r="Q43" s="52" t="s">
+        <v>227</v>
+      </c>
+      <c r="R43" s="52" t="s">
         <v>228</v>
-      </c>
-      <c r="P43" s="52" t="s">
-        <v>229</v>
-      </c>
-      <c r="Q43" s="52" t="s">
-        <v>230</v>
-      </c>
-      <c r="R43" s="52" t="s">
-        <v>231</v>
       </c>
       <c r="S43" s="52"/>
       <c r="T43" s="52"/>
       <c r="U43" s="52" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="V43" s="52"/>
       <c r="W43" s="52"/>
@@ -9130,31 +9286,31 @@
       <c r="AL43" s="52"/>
       <c r="AM43" s="52"/>
       <c r="AN43" s="52" t="s">
+        <v>229</v>
+      </c>
+      <c r="AO43" s="52" t="s">
+        <v>230</v>
+      </c>
+      <c r="AP43" s="52" t="s">
+        <v>447</v>
+      </c>
+      <c r="AQ43" s="52" t="s">
+        <v>252</v>
+      </c>
+      <c r="AR43" s="52" t="s">
+        <v>253</v>
+      </c>
+      <c r="AS43" s="52" t="s">
+        <v>427</v>
+      </c>
+      <c r="AT43" s="52" t="s">
+        <v>231</v>
+      </c>
+      <c r="AU43" s="52" t="s">
         <v>232</v>
       </c>
-      <c r="AO43" s="52" t="s">
-        <v>233</v>
-      </c>
-      <c r="AP43" s="52" t="s">
-        <v>450</v>
-      </c>
-      <c r="AQ43" s="52" t="s">
-        <v>255</v>
-      </c>
-      <c r="AR43" s="52" t="s">
-        <v>256</v>
-      </c>
-      <c r="AS43" s="52" t="s">
-        <v>430</v>
-      </c>
-      <c r="AT43" s="52" t="s">
-        <v>234</v>
-      </c>
-      <c r="AU43" s="52" t="s">
-        <v>235</v>
-      </c>
       <c r="AV43" s="52" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="AW43" s="52"/>
       <c r="AX43" s="52"/>
@@ -9198,7 +9354,7 @@
       <c r="CJ43" s="52"/>
       <c r="CK43" s="52"/>
       <c r="CL43" s="52" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="CM43" s="52"/>
       <c r="CN43" s="52"/>
@@ -9210,55 +9366,55 @@
       <c r="B44" s="52"/>
       <c r="C44" s="52"/>
       <c r="D44" s="52" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="E44" s="52" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="F44" s="52" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="G44" s="52"/>
       <c r="H44" s="52"/>
       <c r="I44" s="52" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="J44" s="52" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="K44" s="52" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="L44" s="52" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="M44" s="52"/>
       <c r="N44" s="52" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="O44" s="52" t="s">
+        <v>225</v>
+      </c>
+      <c r="P44" s="52" t="s">
+        <v>226</v>
+      </c>
+      <c r="Q44" s="52" t="s">
+        <v>227</v>
+      </c>
+      <c r="R44" s="52" t="s">
         <v>228</v>
-      </c>
-      <c r="P44" s="52" t="s">
-        <v>229</v>
-      </c>
-      <c r="Q44" s="52" t="s">
-        <v>230</v>
-      </c>
-      <c r="R44" s="52" t="s">
-        <v>231</v>
       </c>
       <c r="S44" s="52"/>
       <c r="T44" s="52"/>
       <c r="U44" s="52" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="V44" s="52"/>
       <c r="W44" s="52" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="X44" s="52" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="Y44" s="52"/>
       <c r="Z44" s="52"/>
@@ -9276,31 +9432,31 @@
       <c r="AL44" s="52"/>
       <c r="AM44" s="52"/>
       <c r="AN44" s="52" t="s">
+        <v>229</v>
+      </c>
+      <c r="AO44" s="52" t="s">
+        <v>230</v>
+      </c>
+      <c r="AP44" s="52" t="s">
+        <v>448</v>
+      </c>
+      <c r="AQ44" s="52" t="s">
+        <v>252</v>
+      </c>
+      <c r="AR44" s="52" t="s">
+        <v>253</v>
+      </c>
+      <c r="AS44" s="52" t="s">
+        <v>449</v>
+      </c>
+      <c r="AT44" s="52" t="s">
+        <v>231</v>
+      </c>
+      <c r="AU44" s="52" t="s">
         <v>232</v>
       </c>
-      <c r="AO44" s="52" t="s">
-        <v>233</v>
-      </c>
-      <c r="AP44" s="52" t="s">
-        <v>451</v>
-      </c>
-      <c r="AQ44" s="52" t="s">
-        <v>255</v>
-      </c>
-      <c r="AR44" s="52" t="s">
-        <v>256</v>
-      </c>
-      <c r="AS44" s="52" t="s">
-        <v>452</v>
-      </c>
-      <c r="AT44" s="52" t="s">
-        <v>234</v>
-      </c>
-      <c r="AU44" s="52" t="s">
-        <v>235</v>
-      </c>
       <c r="AV44" s="52" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="AW44" s="52"/>
       <c r="AX44" s="52"/>
@@ -9344,7 +9500,7 @@
       <c r="CJ44" s="52"/>
       <c r="CK44" s="52"/>
       <c r="CL44" s="52" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="CM44" s="52"/>
       <c r="CN44" s="52"/>
@@ -9356,44 +9512,44 @@
       <c r="B45" s="52"/>
       <c r="C45" s="52"/>
       <c r="D45" s="52" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="E45" s="52" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="F45" s="52" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="G45" s="52"/>
       <c r="H45" s="52"/>
       <c r="I45" s="52" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="J45" s="52" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="K45" s="52" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="L45" s="52"/>
       <c r="M45" s="52"/>
       <c r="N45" s="52"/>
       <c r="O45" s="52" t="s">
+        <v>225</v>
+      </c>
+      <c r="P45" s="52" t="s">
+        <v>226</v>
+      </c>
+      <c r="Q45" s="52" t="s">
+        <v>227</v>
+      </c>
+      <c r="R45" s="52" t="s">
         <v>228</v>
-      </c>
-      <c r="P45" s="52" t="s">
-        <v>229</v>
-      </c>
-      <c r="Q45" s="52" t="s">
-        <v>230</v>
-      </c>
-      <c r="R45" s="52" t="s">
-        <v>231</v>
       </c>
       <c r="S45" s="52"/>
       <c r="T45" s="52"/>
       <c r="U45" s="52" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="V45" s="52"/>
       <c r="W45" s="52"/>
@@ -9414,31 +9570,31 @@
       <c r="AL45" s="52"/>
       <c r="AM45" s="52"/>
       <c r="AN45" s="52" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="AO45" s="52" t="s">
+        <v>230</v>
+      </c>
+      <c r="AP45" s="52" t="s">
+        <v>451</v>
+      </c>
+      <c r="AQ45" s="52" t="s">
         <v>233</v>
       </c>
-      <c r="AP45" s="52" t="s">
-        <v>454</v>
-      </c>
-      <c r="AQ45" s="52" t="s">
-        <v>236</v>
-      </c>
       <c r="AR45" s="52" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="AS45" s="52" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="AT45" s="52" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="AU45" s="52" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="AV45" s="52" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="AW45" s="52"/>
       <c r="AX45" s="52"/>
@@ -9482,7 +9638,7 @@
       <c r="CJ45" s="52"/>
       <c r="CK45" s="52"/>
       <c r="CL45" s="52" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="CM45" s="52"/>
       <c r="CN45" s="52"/>
@@ -9494,44 +9650,44 @@
       <c r="B46" s="52"/>
       <c r="C46" s="52"/>
       <c r="D46" s="52" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="E46" s="52" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="F46" s="52" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="G46" s="52"/>
       <c r="H46" s="52"/>
       <c r="I46" s="52" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="J46" s="52" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="K46" s="52" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="L46" s="52"/>
       <c r="M46" s="52"/>
       <c r="N46" s="52"/>
       <c r="O46" s="52" t="s">
+        <v>225</v>
+      </c>
+      <c r="P46" s="52" t="s">
+        <v>226</v>
+      </c>
+      <c r="Q46" s="52" t="s">
+        <v>227</v>
+      </c>
+      <c r="R46" s="52" t="s">
         <v>228</v>
-      </c>
-      <c r="P46" s="52" t="s">
-        <v>229</v>
-      </c>
-      <c r="Q46" s="52" t="s">
-        <v>230</v>
-      </c>
-      <c r="R46" s="52" t="s">
-        <v>231</v>
       </c>
       <c r="S46" s="52"/>
       <c r="T46" s="52"/>
       <c r="U46" s="52" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="V46" s="52"/>
       <c r="W46" s="52"/>
@@ -9552,31 +9708,31 @@
       <c r="AL46" s="52"/>
       <c r="AM46" s="52"/>
       <c r="AN46" s="52" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="AO46" s="52" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="AP46" s="52" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="AQ46" s="52" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="AR46" s="52" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="AS46" s="52" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="AT46" s="52" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="AU46" s="52" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="AV46" s="52" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="AW46" s="52"/>
       <c r="AX46" s="52"/>
@@ -9620,7 +9776,7 @@
       <c r="CJ46" s="52"/>
       <c r="CK46" s="52"/>
       <c r="CL46" s="52" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="CM46" s="52"/>
       <c r="CN46" s="52"/>
@@ -9632,44 +9788,44 @@
       <c r="B47" s="52"/>
       <c r="C47" s="52"/>
       <c r="D47" s="52" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="E47" s="52" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="F47" s="52" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="G47" s="52"/>
       <c r="H47" s="52"/>
       <c r="I47" s="52" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="J47" s="52" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="K47" s="52" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="L47" s="52"/>
       <c r="M47" s="52"/>
       <c r="N47" s="52"/>
       <c r="O47" s="52" t="s">
+        <v>225</v>
+      </c>
+      <c r="P47" s="52" t="s">
+        <v>226</v>
+      </c>
+      <c r="Q47" s="52" t="s">
+        <v>227</v>
+      </c>
+      <c r="R47" s="52" t="s">
         <v>228</v>
-      </c>
-      <c r="P47" s="52" t="s">
-        <v>229</v>
-      </c>
-      <c r="Q47" s="52" t="s">
-        <v>230</v>
-      </c>
-      <c r="R47" s="52" t="s">
-        <v>231</v>
       </c>
       <c r="S47" s="52"/>
       <c r="T47" s="52"/>
       <c r="U47" s="52" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="V47" s="52"/>
       <c r="W47" s="52"/>
@@ -9679,10 +9835,10 @@
       <c r="AA47" s="52"/>
       <c r="AB47" s="52"/>
       <c r="AC47" s="52" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="AD47" s="52" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="AE47" s="52"/>
       <c r="AF47" s="52"/>
@@ -9694,31 +9850,31 @@
       <c r="AL47" s="52"/>
       <c r="AM47" s="52"/>
       <c r="AN47" s="52" t="s">
+        <v>229</v>
+      </c>
+      <c r="AO47" s="52" t="s">
+        <v>230</v>
+      </c>
+      <c r="AP47" s="52" t="s">
+        <v>455</v>
+      </c>
+      <c r="AQ47" s="52" t="s">
+        <v>231</v>
+      </c>
+      <c r="AR47" s="52" t="s">
         <v>232</v>
       </c>
-      <c r="AO47" s="52" t="s">
-        <v>233</v>
-      </c>
-      <c r="AP47" s="52" t="s">
-        <v>458</v>
-      </c>
-      <c r="AQ47" s="52" t="s">
-        <v>234</v>
-      </c>
-      <c r="AR47" s="52" t="s">
-        <v>235</v>
-      </c>
       <c r="AS47" s="52" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="AT47" s="52" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="AU47" s="52" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="AV47" s="52" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="AW47" s="52"/>
       <c r="AX47" s="52"/>
@@ -9762,7 +9918,7 @@
       <c r="CJ47" s="52"/>
       <c r="CK47" s="52"/>
       <c r="CL47" s="52" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="CM47" s="52"/>
       <c r="CN47" s="52"/>
@@ -9774,44 +9930,44 @@
       <c r="B48" s="52"/>
       <c r="C48" s="52"/>
       <c r="D48" s="52" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="E48" s="52" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="F48" s="52" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="G48" s="52"/>
       <c r="H48" s="52"/>
       <c r="I48" s="52" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="J48" s="52" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="K48" s="52" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="L48" s="52"/>
       <c r="M48" s="52"/>
       <c r="N48" s="52"/>
       <c r="O48" s="52" t="s">
+        <v>225</v>
+      </c>
+      <c r="P48" s="52" t="s">
+        <v>226</v>
+      </c>
+      <c r="Q48" s="52" t="s">
+        <v>227</v>
+      </c>
+      <c r="R48" s="52" t="s">
         <v>228</v>
-      </c>
-      <c r="P48" s="52" t="s">
-        <v>229</v>
-      </c>
-      <c r="Q48" s="52" t="s">
-        <v>230</v>
-      </c>
-      <c r="R48" s="52" t="s">
-        <v>231</v>
       </c>
       <c r="S48" s="52"/>
       <c r="T48" s="52"/>
       <c r="U48" s="52" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="V48" s="52"/>
       <c r="W48" s="52"/>
@@ -9821,10 +9977,10 @@
       <c r="AA48" s="52"/>
       <c r="AB48" s="52"/>
       <c r="AC48" s="52" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="AD48" s="52" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="AE48" s="52"/>
       <c r="AF48" s="52"/>
@@ -9836,31 +9992,31 @@
       <c r="AL48" s="52"/>
       <c r="AM48" s="52"/>
       <c r="AN48" s="52" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="AO48" s="52" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="AP48" s="52" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="AQ48" s="52" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="AR48" s="52" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="AS48" s="52" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="AT48" s="52" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="AU48" s="52" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="AV48" s="52" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="AW48" s="52"/>
       <c r="AX48" s="52"/>
@@ -9904,7 +10060,7 @@
       <c r="CJ48" s="52"/>
       <c r="CK48" s="52"/>
       <c r="CL48" s="52" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="CM48" s="52"/>
       <c r="CN48" s="52"/>
@@ -9916,44 +10072,44 @@
       <c r="B49" s="52"/>
       <c r="C49" s="52"/>
       <c r="D49" s="52" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="E49" s="52" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="F49" s="52" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="G49" s="52"/>
       <c r="H49" s="52"/>
       <c r="I49" s="52" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="J49" s="52" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="K49" s="52" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="L49" s="52"/>
       <c r="M49" s="52"/>
       <c r="N49" s="52"/>
       <c r="O49" s="52" t="s">
+        <v>225</v>
+      </c>
+      <c r="P49" s="52" t="s">
+        <v>226</v>
+      </c>
+      <c r="Q49" s="52" t="s">
+        <v>227</v>
+      </c>
+      <c r="R49" s="52" t="s">
         <v>228</v>
-      </c>
-      <c r="P49" s="52" t="s">
-        <v>229</v>
-      </c>
-      <c r="Q49" s="52" t="s">
-        <v>230</v>
-      </c>
-      <c r="R49" s="52" t="s">
-        <v>231</v>
       </c>
       <c r="S49" s="52"/>
       <c r="T49" s="52"/>
       <c r="U49" s="52" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="V49" s="52"/>
       <c r="W49" s="52"/>
@@ -9963,10 +10119,10 @@
       <c r="AA49" s="52"/>
       <c r="AB49" s="52"/>
       <c r="AC49" s="52" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="AD49" s="52" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="AE49" s="52"/>
       <c r="AF49" s="52"/>
@@ -9978,31 +10134,31 @@
       <c r="AL49" s="52"/>
       <c r="AM49" s="52"/>
       <c r="AN49" s="52" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="AO49" s="52" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="AP49" s="52" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="AQ49" s="52" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="AR49" s="52" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="AS49" s="52" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="AT49" s="52" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="AU49" s="52" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="AV49" s="52" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="AW49" s="52"/>
       <c r="AX49" s="52"/>
@@ -10046,7 +10202,7 @@
       <c r="CJ49" s="52"/>
       <c r="CK49" s="52"/>
       <c r="CL49" s="52" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="CM49" s="52"/>
       <c r="CN49" s="52"/>
@@ -10058,44 +10214,44 @@
       <c r="B50" s="52"/>
       <c r="C50" s="52"/>
       <c r="D50" s="52" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="E50" s="52" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="F50" s="52" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="G50" s="52"/>
       <c r="H50" s="52"/>
       <c r="I50" s="52" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="J50" s="52" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="K50" s="52" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="L50" s="52"/>
       <c r="M50" s="52"/>
       <c r="N50" s="52"/>
       <c r="O50" s="52" t="s">
+        <v>225</v>
+      </c>
+      <c r="P50" s="52" t="s">
+        <v>226</v>
+      </c>
+      <c r="Q50" s="52" t="s">
+        <v>227</v>
+      </c>
+      <c r="R50" s="52" t="s">
         <v>228</v>
-      </c>
-      <c r="P50" s="52" t="s">
-        <v>229</v>
-      </c>
-      <c r="Q50" s="52" t="s">
-        <v>230</v>
-      </c>
-      <c r="R50" s="52" t="s">
-        <v>231</v>
       </c>
       <c r="S50" s="52"/>
       <c r="T50" s="52"/>
       <c r="U50" s="52" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="V50" s="52"/>
       <c r="W50" s="52"/>
@@ -10105,10 +10261,10 @@
       <c r="AA50" s="52"/>
       <c r="AB50" s="52"/>
       <c r="AC50" s="52" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="AD50" s="52" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="AE50" s="52"/>
       <c r="AF50" s="52"/>
@@ -10120,31 +10276,31 @@
       <c r="AL50" s="52"/>
       <c r="AM50" s="52"/>
       <c r="AN50" s="52" t="s">
+        <v>229</v>
+      </c>
+      <c r="AO50" s="52" t="s">
+        <v>230</v>
+      </c>
+      <c r="AP50" s="52" t="s">
+        <v>463</v>
+      </c>
+      <c r="AQ50" s="52" t="s">
+        <v>231</v>
+      </c>
+      <c r="AR50" s="52" t="s">
         <v>232</v>
       </c>
-      <c r="AO50" s="52" t="s">
-        <v>233</v>
-      </c>
-      <c r="AP50" s="52" t="s">
-        <v>466</v>
-      </c>
-      <c r="AQ50" s="52" t="s">
-        <v>234</v>
-      </c>
-      <c r="AR50" s="52" t="s">
-        <v>235</v>
-      </c>
       <c r="AS50" s="52" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="AT50" s="52" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="AU50" s="52" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="AV50" s="52" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="AW50" s="52"/>
       <c r="AX50" s="52"/>
@@ -10188,7 +10344,7 @@
       <c r="CJ50" s="52"/>
       <c r="CK50" s="52"/>
       <c r="CL50" s="52" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="CM50" s="52"/>
       <c r="CN50" s="52"/>
@@ -10200,44 +10356,44 @@
       <c r="B51" s="52"/>
       <c r="C51" s="52"/>
       <c r="D51" s="52" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="E51" s="52" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="F51" s="52" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="G51" s="52"/>
       <c r="H51" s="52"/>
       <c r="I51" s="52" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="J51" s="52" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="K51" s="52" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="L51" s="52"/>
       <c r="M51" s="52"/>
       <c r="N51" s="52"/>
       <c r="O51" s="52" t="s">
+        <v>225</v>
+      </c>
+      <c r="P51" s="52" t="s">
+        <v>226</v>
+      </c>
+      <c r="Q51" s="52" t="s">
+        <v>227</v>
+      </c>
+      <c r="R51" s="52" t="s">
         <v>228</v>
-      </c>
-      <c r="P51" s="52" t="s">
-        <v>229</v>
-      </c>
-      <c r="Q51" s="52" t="s">
-        <v>230</v>
-      </c>
-      <c r="R51" s="52" t="s">
-        <v>231</v>
       </c>
       <c r="S51" s="52"/>
       <c r="T51" s="52"/>
       <c r="U51" s="52" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="V51" s="52"/>
       <c r="W51" s="52"/>
@@ -10247,10 +10403,10 @@
       <c r="AA51" s="52"/>
       <c r="AB51" s="52"/>
       <c r="AC51" s="52" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="AD51" s="52" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="AE51" s="52"/>
       <c r="AF51" s="52"/>
@@ -10262,31 +10418,31 @@
       <c r="AL51" s="52"/>
       <c r="AM51" s="52"/>
       <c r="AN51" s="52" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="AO51" s="52" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="AP51" s="52" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="AQ51" s="52" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="AR51" s="52" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="AS51" s="52" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="AT51" s="52" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="AU51" s="52" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="AV51" s="52" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="AW51" s="52"/>
       <c r="AX51" s="52"/>
@@ -10330,7 +10486,7 @@
       <c r="CJ51" s="52"/>
       <c r="CK51" s="52"/>
       <c r="CL51" s="52" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="CM51" s="52"/>
       <c r="CN51" s="52"/>
@@ -10342,44 +10498,44 @@
       <c r="B52" s="52"/>
       <c r="C52" s="52"/>
       <c r="D52" s="52" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="E52" s="52" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="F52" s="52" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="G52" s="52"/>
       <c r="H52" s="52"/>
       <c r="I52" s="52" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="J52" s="52" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="K52" s="52" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="L52" s="52"/>
       <c r="M52" s="52"/>
       <c r="N52" s="52"/>
       <c r="O52" s="52" t="s">
+        <v>225</v>
+      </c>
+      <c r="P52" s="52" t="s">
+        <v>226</v>
+      </c>
+      <c r="Q52" s="52" t="s">
+        <v>227</v>
+      </c>
+      <c r="R52" s="52" t="s">
         <v>228</v>
-      </c>
-      <c r="P52" s="52" t="s">
-        <v>229</v>
-      </c>
-      <c r="Q52" s="52" t="s">
-        <v>230</v>
-      </c>
-      <c r="R52" s="52" t="s">
-        <v>231</v>
       </c>
       <c r="S52" s="52"/>
       <c r="T52" s="52"/>
       <c r="U52" s="52" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="V52" s="52"/>
       <c r="W52" s="52"/>
@@ -10389,10 +10545,10 @@
       <c r="AA52" s="52"/>
       <c r="AB52" s="52"/>
       <c r="AC52" s="52" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="AD52" s="52" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="AE52" s="52"/>
       <c r="AF52" s="52"/>
@@ -10404,31 +10560,31 @@
       <c r="AL52" s="52"/>
       <c r="AM52" s="52"/>
       <c r="AN52" s="52" t="s">
+        <v>229</v>
+      </c>
+      <c r="AO52" s="52" t="s">
+        <v>230</v>
+      </c>
+      <c r="AP52" s="52" t="s">
+        <v>468</v>
+      </c>
+      <c r="AQ52" s="52" t="s">
+        <v>231</v>
+      </c>
+      <c r="AR52" s="52" t="s">
         <v>232</v>
       </c>
-      <c r="AO52" s="52" t="s">
-        <v>233</v>
-      </c>
-      <c r="AP52" s="52" t="s">
-        <v>471</v>
-      </c>
-      <c r="AQ52" s="52" t="s">
-        <v>234</v>
-      </c>
-      <c r="AR52" s="52" t="s">
-        <v>235</v>
-      </c>
       <c r="AS52" s="52" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="AT52" s="52" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="AU52" s="52" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="AV52" s="52" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="AW52" s="52"/>
       <c r="AX52" s="52"/>
@@ -10472,7 +10628,7 @@
       <c r="CJ52" s="52"/>
       <c r="CK52" s="52"/>
       <c r="CL52" s="52" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="CM52" s="52"/>
       <c r="CN52" s="52"/>
@@ -10484,44 +10640,44 @@
       <c r="B53" s="52"/>
       <c r="C53" s="52"/>
       <c r="D53" s="52" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="E53" s="52" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="F53" s="52" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="G53" s="52"/>
       <c r="H53" s="52"/>
       <c r="I53" s="52" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="J53" s="52" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="K53" s="52" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="L53" s="52"/>
       <c r="M53" s="52"/>
       <c r="N53" s="52"/>
       <c r="O53" s="52" t="s">
+        <v>225</v>
+      </c>
+      <c r="P53" s="52" t="s">
+        <v>226</v>
+      </c>
+      <c r="Q53" s="52" t="s">
+        <v>227</v>
+      </c>
+      <c r="R53" s="52" t="s">
         <v>228</v>
-      </c>
-      <c r="P53" s="52" t="s">
-        <v>229</v>
-      </c>
-      <c r="Q53" s="52" t="s">
-        <v>230</v>
-      </c>
-      <c r="R53" s="52" t="s">
-        <v>231</v>
       </c>
       <c r="S53" s="52"/>
       <c r="T53" s="52"/>
       <c r="U53" s="52" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="V53" s="52"/>
       <c r="W53" s="52"/>
@@ -10531,10 +10687,10 @@
       <c r="AA53" s="52"/>
       <c r="AB53" s="52"/>
       <c r="AC53" s="52" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="AD53" s="52" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="AE53" s="52"/>
       <c r="AF53" s="52"/>
@@ -10546,31 +10702,31 @@
       <c r="AL53" s="52"/>
       <c r="AM53" s="52"/>
       <c r="AN53" s="52" t="s">
+        <v>229</v>
+      </c>
+      <c r="AO53" s="52" t="s">
+        <v>230</v>
+      </c>
+      <c r="AP53" s="52" t="s">
+        <v>470</v>
+      </c>
+      <c r="AQ53" s="52" t="s">
+        <v>231</v>
+      </c>
+      <c r="AR53" s="52" t="s">
         <v>232</v>
       </c>
-      <c r="AO53" s="52" t="s">
-        <v>233</v>
-      </c>
-      <c r="AP53" s="52" t="s">
-        <v>473</v>
-      </c>
-      <c r="AQ53" s="52" t="s">
-        <v>234</v>
-      </c>
-      <c r="AR53" s="52" t="s">
-        <v>235</v>
-      </c>
       <c r="AS53" s="52" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="AT53" s="52" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="AU53" s="52" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="AV53" s="52" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="AW53" s="52"/>
       <c r="AX53" s="52"/>
@@ -10614,7 +10770,7 @@
       <c r="CJ53" s="52"/>
       <c r="CK53" s="52"/>
       <c r="CL53" s="52" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="CM53" s="52"/>
       <c r="CN53" s="52"/>
@@ -10626,44 +10782,44 @@
       <c r="B54" s="52"/>
       <c r="C54" s="52"/>
       <c r="D54" s="52" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="E54" s="52" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="F54" s="52" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="G54" s="52"/>
       <c r="H54" s="52"/>
       <c r="I54" s="52" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="J54" s="52" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="K54" s="52" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="L54" s="52"/>
       <c r="M54" s="52"/>
       <c r="N54" s="52"/>
       <c r="O54" s="52" t="s">
+        <v>225</v>
+      </c>
+      <c r="P54" s="52" t="s">
+        <v>226</v>
+      </c>
+      <c r="Q54" s="52" t="s">
+        <v>227</v>
+      </c>
+      <c r="R54" s="52" t="s">
         <v>228</v>
-      </c>
-      <c r="P54" s="52" t="s">
-        <v>229</v>
-      </c>
-      <c r="Q54" s="52" t="s">
-        <v>230</v>
-      </c>
-      <c r="R54" s="52" t="s">
-        <v>231</v>
       </c>
       <c r="S54" s="52"/>
       <c r="T54" s="52"/>
       <c r="U54" s="52" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="V54" s="52"/>
       <c r="W54" s="52"/>
@@ -10673,10 +10829,10 @@
       <c r="AA54" s="52"/>
       <c r="AB54" s="52"/>
       <c r="AC54" s="52" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="AD54" s="52" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="AE54" s="52"/>
       <c r="AF54" s="52"/>
@@ -10688,31 +10844,31 @@
       <c r="AL54" s="52"/>
       <c r="AM54" s="52"/>
       <c r="AN54" s="52" t="s">
+        <v>229</v>
+      </c>
+      <c r="AO54" s="52" t="s">
+        <v>230</v>
+      </c>
+      <c r="AP54" s="52" t="s">
+        <v>472</v>
+      </c>
+      <c r="AQ54" s="52" t="s">
+        <v>302</v>
+      </c>
+      <c r="AR54" s="52" t="s">
+        <v>303</v>
+      </c>
+      <c r="AS54" s="52" t="s">
+        <v>378</v>
+      </c>
+      <c r="AT54" s="52" t="s">
+        <v>231</v>
+      </c>
+      <c r="AU54" s="52" t="s">
         <v>232</v>
       </c>
-      <c r="AO54" s="52" t="s">
-        <v>233</v>
-      </c>
-      <c r="AP54" s="52" t="s">
-        <v>475</v>
-      </c>
-      <c r="AQ54" s="52" t="s">
-        <v>305</v>
-      </c>
-      <c r="AR54" s="52" t="s">
-        <v>306</v>
-      </c>
-      <c r="AS54" s="52" t="s">
-        <v>381</v>
-      </c>
-      <c r="AT54" s="52" t="s">
-        <v>234</v>
-      </c>
-      <c r="AU54" s="52" t="s">
-        <v>235</v>
-      </c>
       <c r="AV54" s="52" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="AW54" s="52"/>
       <c r="AX54" s="52"/>
@@ -10756,7 +10912,7 @@
       <c r="CJ54" s="52"/>
       <c r="CK54" s="52"/>
       <c r="CL54" s="52" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="CM54" s="52"/>
       <c r="CN54" s="52"/>
@@ -10768,44 +10924,44 @@
       <c r="B55" s="52"/>
       <c r="C55" s="52"/>
       <c r="D55" s="52" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="E55" s="52" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="F55" s="52" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="G55" s="52"/>
       <c r="H55" s="52"/>
       <c r="I55" s="52" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="J55" s="52" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="K55" s="52" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="L55" s="52"/>
       <c r="M55" s="52"/>
       <c r="N55" s="52"/>
       <c r="O55" s="52" t="s">
+        <v>225</v>
+      </c>
+      <c r="P55" s="52" t="s">
+        <v>226</v>
+      </c>
+      <c r="Q55" s="52" t="s">
+        <v>227</v>
+      </c>
+      <c r="R55" s="52" t="s">
         <v>228</v>
-      </c>
-      <c r="P55" s="52" t="s">
-        <v>229</v>
-      </c>
-      <c r="Q55" s="52" t="s">
-        <v>230</v>
-      </c>
-      <c r="R55" s="52" t="s">
-        <v>231</v>
       </c>
       <c r="S55" s="52"/>
       <c r="T55" s="52"/>
       <c r="U55" s="52" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="V55" s="52"/>
       <c r="W55" s="52"/>
@@ -10815,10 +10971,10 @@
       <c r="AA55" s="52"/>
       <c r="AB55" s="52"/>
       <c r="AC55" s="52" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="AD55" s="52" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="AE55" s="52"/>
       <c r="AF55" s="52"/>
@@ -10830,31 +10986,31 @@
       <c r="AL55" s="52"/>
       <c r="AM55" s="52"/>
       <c r="AN55" s="52" t="s">
+        <v>229</v>
+      </c>
+      <c r="AO55" s="52" t="s">
+        <v>230</v>
+      </c>
+      <c r="AP55" s="52" t="s">
+        <v>472</v>
+      </c>
+      <c r="AQ55" s="52" t="s">
+        <v>302</v>
+      </c>
+      <c r="AR55" s="52" t="s">
+        <v>303</v>
+      </c>
+      <c r="AS55" s="52" t="s">
+        <v>474</v>
+      </c>
+      <c r="AT55" s="52" t="s">
+        <v>231</v>
+      </c>
+      <c r="AU55" s="52" t="s">
         <v>232</v>
       </c>
-      <c r="AO55" s="52" t="s">
-        <v>233</v>
-      </c>
-      <c r="AP55" s="52" t="s">
-        <v>475</v>
-      </c>
-      <c r="AQ55" s="52" t="s">
-        <v>305</v>
-      </c>
-      <c r="AR55" s="52" t="s">
-        <v>306</v>
-      </c>
-      <c r="AS55" s="52" t="s">
-        <v>477</v>
-      </c>
-      <c r="AT55" s="52" t="s">
-        <v>234</v>
-      </c>
-      <c r="AU55" s="52" t="s">
-        <v>235</v>
-      </c>
       <c r="AV55" s="52" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="AW55" s="52"/>
       <c r="AX55" s="52"/>
@@ -10898,7 +11054,7 @@
       <c r="CJ55" s="52"/>
       <c r="CK55" s="52"/>
       <c r="CL55" s="52" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="CM55" s="52"/>
       <c r="CN55" s="52"/>
@@ -11020,277 +11176,277 @@
   <sheetData>
     <row r="1" spans="1:91" ht="24.95" customHeight="1">
       <c r="A1" s="49" t="s">
+        <v>138</v>
+      </c>
+      <c r="B1" s="49" t="s">
+        <v>33</v>
+      </c>
+      <c r="C1" s="50" t="s">
+        <v>139</v>
+      </c>
+      <c r="D1" s="49" t="s">
+        <v>37</v>
+      </c>
+      <c r="E1" s="49" t="s">
+        <v>38</v>
+      </c>
+      <c r="F1" s="49" t="s">
+        <v>15</v>
+      </c>
+      <c r="G1" s="49" t="s">
+        <v>140</v>
+      </c>
+      <c r="H1" s="49" t="s">
         <v>141</v>
       </c>
-      <c r="B1" s="49" t="s">
+      <c r="I1" s="49" t="s">
+        <v>34</v>
+      </c>
+      <c r="J1" s="49" t="s">
         <v>35</v>
       </c>
-      <c r="C1" s="50" t="s">
+      <c r="K1" s="49" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1" s="49" t="s">
         <v>142</v>
       </c>
-      <c r="D1" s="49" t="s">
+      <c r="M1" s="49" t="s">
+        <v>143</v>
+      </c>
+      <c r="N1" s="49" t="s">
+        <v>144</v>
+      </c>
+      <c r="O1" s="49" t="s">
+        <v>145</v>
+      </c>
+      <c r="P1" s="49" t="s">
+        <v>146</v>
+      </c>
+      <c r="Q1" s="49" t="s">
+        <v>147</v>
+      </c>
+      <c r="R1" s="50" t="s">
+        <v>148</v>
+      </c>
+      <c r="S1" s="49" t="s">
+        <v>149</v>
+      </c>
+      <c r="T1" s="49" t="s">
+        <v>150</v>
+      </c>
+      <c r="U1" s="49" t="s">
+        <v>151</v>
+      </c>
+      <c r="V1" s="49" t="s">
+        <v>152</v>
+      </c>
+      <c r="W1" s="49" t="s">
+        <v>153</v>
+      </c>
+      <c r="X1" s="49" t="s">
+        <v>154</v>
+      </c>
+      <c r="Y1" s="49" t="s">
+        <v>155</v>
+      </c>
+      <c r="Z1" s="49" t="s">
+        <v>16</v>
+      </c>
+      <c r="AA1" s="49" t="s">
+        <v>156</v>
+      </c>
+      <c r="AB1" s="49" t="s">
+        <v>157</v>
+      </c>
+      <c r="AC1" s="49" t="s">
+        <v>158</v>
+      </c>
+      <c r="AD1" s="49" t="s">
+        <v>159</v>
+      </c>
+      <c r="AE1" s="49" t="s">
+        <v>160</v>
+      </c>
+      <c r="AF1" s="49" t="s">
+        <v>161</v>
+      </c>
+      <c r="AG1" s="49" t="s">
+        <v>162</v>
+      </c>
+      <c r="AH1" s="49" t="s">
+        <v>163</v>
+      </c>
+      <c r="AI1" s="49" t="s">
+        <v>164</v>
+      </c>
+      <c r="AJ1" s="49" t="s">
+        <v>165</v>
+      </c>
+      <c r="AK1" s="49" t="s">
+        <v>166</v>
+      </c>
+      <c r="AL1" s="49" t="s">
+        <v>167</v>
+      </c>
+      <c r="AM1" s="49" t="s">
+        <v>168</v>
+      </c>
+      <c r="AN1" s="50" t="s">
+        <v>169</v>
+      </c>
+      <c r="AO1" s="49" t="s">
+        <v>170</v>
+      </c>
+      <c r="AP1" s="49" t="s">
+        <v>171</v>
+      </c>
+      <c r="AQ1" s="50" t="s">
+        <v>172</v>
+      </c>
+      <c r="AR1" s="49" t="s">
+        <v>173</v>
+      </c>
+      <c r="AS1" s="49" t="s">
+        <v>174</v>
+      </c>
+      <c r="AT1" s="49" t="s">
+        <v>175</v>
+      </c>
+      <c r="AU1" s="49" t="s">
+        <v>176</v>
+      </c>
+      <c r="AV1" s="49" t="s">
+        <v>177</v>
+      </c>
+      <c r="AW1" s="49" t="s">
+        <v>178</v>
+      </c>
+      <c r="AX1" s="49" t="s">
+        <v>179</v>
+      </c>
+      <c r="AY1" s="49" t="s">
+        <v>180</v>
+      </c>
+      <c r="AZ1" s="49" t="s">
+        <v>181</v>
+      </c>
+      <c r="BA1" s="49" t="s">
+        <v>182</v>
+      </c>
+      <c r="BB1" s="49" t="s">
+        <v>183</v>
+      </c>
+      <c r="BC1" s="49" t="s">
+        <v>184</v>
+      </c>
+      <c r="BD1" s="49" t="s">
+        <v>185</v>
+      </c>
+      <c r="BE1" s="49" t="s">
+        <v>186</v>
+      </c>
+      <c r="BF1" s="49" t="s">
+        <v>187</v>
+      </c>
+      <c r="BG1" s="49" t="s">
+        <v>188</v>
+      </c>
+      <c r="BH1" s="49" t="s">
+        <v>189</v>
+      </c>
+      <c r="BI1" s="49" t="s">
+        <v>190</v>
+      </c>
+      <c r="BJ1" s="49" t="s">
+        <v>191</v>
+      </c>
+      <c r="BK1" s="49" t="s">
+        <v>192</v>
+      </c>
+      <c r="BL1" s="49" t="s">
+        <v>193</v>
+      </c>
+      <c r="BM1" s="49" t="s">
+        <v>194</v>
+      </c>
+      <c r="BN1" s="49" t="s">
+        <v>195</v>
+      </c>
+      <c r="BO1" s="49" t="s">
+        <v>196</v>
+      </c>
+      <c r="BP1" s="49" t="s">
+        <v>197</v>
+      </c>
+      <c r="BQ1" s="49" t="s">
+        <v>198</v>
+      </c>
+      <c r="BR1" s="49" t="s">
+        <v>199</v>
+      </c>
+      <c r="BS1" s="49" t="s">
+        <v>200</v>
+      </c>
+      <c r="BT1" s="49" t="s">
+        <v>201</v>
+      </c>
+      <c r="BU1" s="49" t="s">
+        <v>202</v>
+      </c>
+      <c r="BV1" s="49" t="s">
+        <v>203</v>
+      </c>
+      <c r="BW1" s="49" t="s">
+        <v>204</v>
+      </c>
+      <c r="BX1" s="49" t="s">
+        <v>205</v>
+      </c>
+      <c r="BY1" s="49" t="s">
+        <v>206</v>
+      </c>
+      <c r="BZ1" s="49" t="s">
         <v>39</v>
       </c>
-      <c r="E1" s="49" t="s">
-        <v>40</v>
-      </c>
-      <c r="F1" s="49" t="s">
-        <v>17</v>
-      </c>
-      <c r="G1" s="49" t="s">
-        <v>143</v>
-      </c>
-      <c r="H1" s="49" t="s">
-        <v>144</v>
-      </c>
-      <c r="I1" s="49" t="s">
-        <v>36</v>
-      </c>
-      <c r="J1" s="49" t="s">
-        <v>37</v>
-      </c>
-      <c r="K1" s="49" t="s">
-        <v>38</v>
-      </c>
-      <c r="L1" s="49" t="s">
-        <v>145</v>
-      </c>
-      <c r="M1" s="49" t="s">
-        <v>146</v>
-      </c>
-      <c r="N1" s="49" t="s">
-        <v>147</v>
-      </c>
-      <c r="O1" s="49" t="s">
-        <v>148</v>
-      </c>
-      <c r="P1" s="49" t="s">
-        <v>149</v>
-      </c>
-      <c r="Q1" s="49" t="s">
-        <v>150</v>
-      </c>
-      <c r="R1" s="50" t="s">
-        <v>151</v>
-      </c>
-      <c r="S1" s="49" t="s">
-        <v>152</v>
-      </c>
-      <c r="T1" s="49" t="s">
-        <v>153</v>
-      </c>
-      <c r="U1" s="49" t="s">
-        <v>154</v>
-      </c>
-      <c r="V1" s="49" t="s">
-        <v>155</v>
-      </c>
-      <c r="W1" s="49" t="s">
-        <v>156</v>
-      </c>
-      <c r="X1" s="49" t="s">
-        <v>157</v>
-      </c>
-      <c r="Y1" s="49" t="s">
-        <v>158</v>
-      </c>
-      <c r="Z1" s="49" t="s">
-        <v>18</v>
-      </c>
-      <c r="AA1" s="49" t="s">
-        <v>159</v>
-      </c>
-      <c r="AB1" s="49" t="s">
-        <v>160</v>
-      </c>
-      <c r="AC1" s="49" t="s">
-        <v>161</v>
-      </c>
-      <c r="AD1" s="49" t="s">
-        <v>162</v>
-      </c>
-      <c r="AE1" s="49" t="s">
-        <v>163</v>
-      </c>
-      <c r="AF1" s="49" t="s">
-        <v>164</v>
-      </c>
-      <c r="AG1" s="49" t="s">
-        <v>165</v>
-      </c>
-      <c r="AH1" s="49" t="s">
-        <v>166</v>
-      </c>
-      <c r="AI1" s="49" t="s">
-        <v>167</v>
-      </c>
-      <c r="AJ1" s="49" t="s">
-        <v>168</v>
-      </c>
-      <c r="AK1" s="49" t="s">
-        <v>169</v>
-      </c>
-      <c r="AL1" s="49" t="s">
-        <v>170</v>
-      </c>
-      <c r="AM1" s="49" t="s">
-        <v>171</v>
-      </c>
-      <c r="AN1" s="50" t="s">
-        <v>172</v>
-      </c>
-      <c r="AO1" s="49" t="s">
-        <v>173</v>
-      </c>
-      <c r="AP1" s="49" t="s">
-        <v>174</v>
-      </c>
-      <c r="AQ1" s="50" t="s">
-        <v>175</v>
-      </c>
-      <c r="AR1" s="49" t="s">
-        <v>176</v>
-      </c>
-      <c r="AS1" s="49" t="s">
-        <v>177</v>
-      </c>
-      <c r="AT1" s="49" t="s">
-        <v>178</v>
-      </c>
-      <c r="AU1" s="49" t="s">
-        <v>179</v>
-      </c>
-      <c r="AV1" s="49" t="s">
-        <v>180</v>
-      </c>
-      <c r="AW1" s="49" t="s">
-        <v>181</v>
-      </c>
-      <c r="AX1" s="49" t="s">
-        <v>182</v>
-      </c>
-      <c r="AY1" s="49" t="s">
-        <v>183</v>
-      </c>
-      <c r="AZ1" s="49" t="s">
-        <v>184</v>
-      </c>
-      <c r="BA1" s="49" t="s">
-        <v>185</v>
-      </c>
-      <c r="BB1" s="49" t="s">
-        <v>186</v>
-      </c>
-      <c r="BC1" s="49" t="s">
-        <v>187</v>
-      </c>
-      <c r="BD1" s="49" t="s">
-        <v>188</v>
-      </c>
-      <c r="BE1" s="49" t="s">
-        <v>189</v>
-      </c>
-      <c r="BF1" s="49" t="s">
-        <v>190</v>
-      </c>
-      <c r="BG1" s="49" t="s">
-        <v>191</v>
-      </c>
-      <c r="BH1" s="49" t="s">
-        <v>192</v>
-      </c>
-      <c r="BI1" s="49" t="s">
-        <v>193</v>
-      </c>
-      <c r="BJ1" s="49" t="s">
-        <v>194</v>
-      </c>
-      <c r="BK1" s="49" t="s">
-        <v>195</v>
-      </c>
-      <c r="BL1" s="49" t="s">
-        <v>196</v>
-      </c>
-      <c r="BM1" s="49" t="s">
-        <v>197</v>
-      </c>
-      <c r="BN1" s="49" t="s">
-        <v>198</v>
-      </c>
-      <c r="BO1" s="49" t="s">
-        <v>199</v>
-      </c>
-      <c r="BP1" s="49" t="s">
-        <v>200</v>
-      </c>
-      <c r="BQ1" s="49" t="s">
-        <v>201</v>
-      </c>
-      <c r="BR1" s="49" t="s">
-        <v>202</v>
-      </c>
-      <c r="BS1" s="49" t="s">
-        <v>203</v>
-      </c>
-      <c r="BT1" s="49" t="s">
-        <v>204</v>
-      </c>
-      <c r="BU1" s="49" t="s">
-        <v>205</v>
-      </c>
-      <c r="BV1" s="49" t="s">
-        <v>206</v>
-      </c>
-      <c r="BW1" s="49" t="s">
+      <c r="CA1" s="49" t="s">
         <v>207</v>
       </c>
-      <c r="BX1" s="49" t="s">
+      <c r="CB1" s="49" t="s">
         <v>208</v>
       </c>
-      <c r="BY1" s="49" t="s">
+      <c r="CC1" s="49" t="s">
         <v>209</v>
       </c>
-      <c r="BZ1" s="49" t="s">
-        <v>41</v>
-      </c>
-      <c r="CA1" s="49" t="s">
+      <c r="CD1" s="49" t="s">
         <v>210</v>
       </c>
-      <c r="CB1" s="49" t="s">
+      <c r="CE1" s="49" t="s">
         <v>211</v>
       </c>
-      <c r="CC1" s="49" t="s">
+      <c r="CF1" s="49" t="s">
         <v>212</v>
       </c>
-      <c r="CD1" s="49" t="s">
+      <c r="CG1" s="49" t="s">
         <v>213</v>
       </c>
-      <c r="CE1" s="49" t="s">
+      <c r="CH1" s="49" t="s">
         <v>214</v>
       </c>
-      <c r="CF1" s="49" t="s">
+      <c r="CI1" s="49" t="s">
         <v>215</v>
       </c>
-      <c r="CG1" s="49" t="s">
+      <c r="CJ1" s="49" t="s">
         <v>216</v>
       </c>
-      <c r="CH1" s="49" t="s">
+      <c r="CK1" s="49" t="s">
         <v>217</v>
       </c>
-      <c r="CI1" s="49" t="s">
+      <c r="CL1" s="49" t="s">
         <v>218</v>
       </c>
-      <c r="CJ1" s="49" t="s">
+      <c r="CM1" s="49" t="s">
         <v>219</v>
-      </c>
-      <c r="CK1" s="49" t="s">
-        <v>220</v>
-      </c>
-      <c r="CL1" s="49" t="s">
-        <v>221</v>
-      </c>
-      <c r="CM1" s="49" t="s">
-        <v>222</v>
       </c>
     </row>
   </sheetData>
@@ -11383,13 +11539,13 @@
   <sheetData>
     <row r="1" spans="1:106" s="17" customFormat="1" ht="29.25" customHeight="1">
       <c r="A1" s="16" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="2" spans="1:106" ht="6.75" customHeight="1"/>
     <row r="3" spans="1:106" s="21" customFormat="1" ht="15">
       <c r="A3" s="18" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B3" s="19">
         <v>1</v>
@@ -11687,35 +11843,35 @@
       </c>
     </row>
     <row r="4" spans="1:106" s="22" customFormat="1" ht="15" customHeight="1">
-      <c r="N4" s="67" t="s">
-        <v>44</v>
-      </c>
-      <c r="O4" s="68"/>
-      <c r="P4" s="68"/>
-      <c r="Q4" s="68"/>
-      <c r="R4" s="68"/>
-      <c r="S4" s="68"/>
-      <c r="T4" s="68"/>
-      <c r="U4" s="68"/>
-      <c r="V4" s="68"/>
-      <c r="W4" s="68"/>
-      <c r="X4" s="68"/>
-      <c r="Y4" s="68"/>
-      <c r="Z4" s="68"/>
-      <c r="AA4" s="68"/>
-      <c r="AB4" s="68"/>
-      <c r="AC4" s="68"/>
-      <c r="AD4" s="68"/>
-      <c r="AE4" s="68"/>
-      <c r="AF4" s="68"/>
-      <c r="AG4" s="69"/>
+      <c r="N4" s="62" t="s">
+        <v>42</v>
+      </c>
+      <c r="O4" s="63"/>
+      <c r="P4" s="63"/>
+      <c r="Q4" s="63"/>
+      <c r="R4" s="63"/>
+      <c r="S4" s="63"/>
+      <c r="T4" s="63"/>
+      <c r="U4" s="63"/>
+      <c r="V4" s="63"/>
+      <c r="W4" s="63"/>
+      <c r="X4" s="63"/>
+      <c r="Y4" s="63"/>
+      <c r="Z4" s="63"/>
+      <c r="AA4" s="63"/>
+      <c r="AB4" s="63"/>
+      <c r="AC4" s="63"/>
+      <c r="AD4" s="63"/>
+      <c r="AE4" s="63"/>
+      <c r="AF4" s="63"/>
+      <c r="AG4" s="64"/>
       <c r="AH4" s="23" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="AI4" s="23"/>
       <c r="AJ4" s="23"/>
       <c r="AK4" s="24" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AL4" s="25"/>
       <c r="AM4" s="25"/>
@@ -11777,332 +11933,332 @@
       <c r="CQ4" s="25"/>
       <c r="CR4" s="25"/>
       <c r="CS4" s="27" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="CT4" s="28"/>
       <c r="CU4" s="28"/>
-      <c r="CW4" s="70" t="s">
-        <v>48</v>
-      </c>
-      <c r="CX4" s="70"/>
-      <c r="CY4" s="70"/>
-      <c r="CZ4" s="70"/>
-      <c r="DA4" s="70"/>
-      <c r="DB4" s="70"/>
+      <c r="CW4" s="65" t="s">
+        <v>46</v>
+      </c>
+      <c r="CX4" s="65"/>
+      <c r="CY4" s="65"/>
+      <c r="CZ4" s="65"/>
+      <c r="DA4" s="65"/>
+      <c r="DB4" s="65"/>
     </row>
     <row r="5" spans="1:106" s="47" customFormat="1" ht="18.75" customHeight="1">
       <c r="A5" s="29"/>
       <c r="B5" s="30" t="s">
+        <v>47</v>
+      </c>
+      <c r="C5" s="30" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" s="30" t="s">
+        <v>19</v>
+      </c>
+      <c r="E5" s="30" t="s">
+        <v>48</v>
+      </c>
+      <c r="F5" s="30" t="s">
         <v>49</v>
       </c>
-      <c r="C5" s="30" t="s">
+      <c r="G5" s="30" t="s">
+        <v>50</v>
+      </c>
+      <c r="H5" s="30" t="s">
+        <v>51</v>
+      </c>
+      <c r="I5" s="30" t="s">
+        <v>52</v>
+      </c>
+      <c r="J5" s="30" t="s">
+        <v>53</v>
+      </c>
+      <c r="K5" s="30" t="s">
+        <v>54</v>
+      </c>
+      <c r="L5" s="30" t="s">
+        <v>55</v>
+      </c>
+      <c r="M5" s="31" t="s">
+        <v>56</v>
+      </c>
+      <c r="N5" s="32" t="s">
         <v>20</v>
       </c>
-      <c r="D5" s="30" t="s">
+      <c r="O5" s="33" t="s">
+        <v>57</v>
+      </c>
+      <c r="P5" s="33" t="s">
+        <v>58</v>
+      </c>
+      <c r="Q5" s="33" t="s">
+        <v>59</v>
+      </c>
+      <c r="R5" s="33" t="s">
+        <v>60</v>
+      </c>
+      <c r="S5" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="E5" s="30" t="s">
-        <v>50</v>
-      </c>
-      <c r="F5" s="30" t="s">
-        <v>51</v>
-      </c>
-      <c r="G5" s="30" t="s">
-        <v>52</v>
-      </c>
-      <c r="H5" s="30" t="s">
-        <v>53</v>
-      </c>
-      <c r="I5" s="30" t="s">
-        <v>54</v>
-      </c>
-      <c r="J5" s="30" t="s">
-        <v>55</v>
-      </c>
-      <c r="K5" s="30" t="s">
-        <v>56</v>
-      </c>
-      <c r="L5" s="30" t="s">
-        <v>57</v>
-      </c>
-      <c r="M5" s="31" t="s">
-        <v>58</v>
-      </c>
-      <c r="N5" s="32" t="s">
+      <c r="T5" s="33" t="s">
+        <v>61</v>
+      </c>
+      <c r="U5" s="34" t="s">
+        <v>62</v>
+      </c>
+      <c r="V5" s="34" t="s">
+        <v>63</v>
+      </c>
+      <c r="W5" s="34" t="s">
+        <v>64</v>
+      </c>
+      <c r="X5" s="33" t="s">
+        <v>65</v>
+      </c>
+      <c r="Y5" s="33" t="s">
+        <v>66</v>
+      </c>
+      <c r="Z5" s="34" t="s">
+        <v>67</v>
+      </c>
+      <c r="AA5" s="34" t="s">
         <v>22</v>
       </c>
-      <c r="O5" s="33" t="s">
-        <v>59</v>
-      </c>
-      <c r="P5" s="33" t="s">
-        <v>60</v>
-      </c>
-      <c r="Q5" s="33" t="s">
-        <v>61</v>
-      </c>
-      <c r="R5" s="33" t="s">
-        <v>62</v>
-      </c>
-      <c r="S5" s="33" t="s">
+      <c r="AB5" s="33" t="s">
+        <v>68</v>
+      </c>
+      <c r="AC5" s="33" t="s">
         <v>23</v>
       </c>
-      <c r="T5" s="33" t="s">
-        <v>63</v>
-      </c>
-      <c r="U5" s="34" t="s">
-        <v>64</v>
-      </c>
-      <c r="V5" s="34" t="s">
-        <v>65</v>
-      </c>
-      <c r="W5" s="34" t="s">
-        <v>66</v>
-      </c>
-      <c r="X5" s="33" t="s">
-        <v>67</v>
-      </c>
-      <c r="Y5" s="33" t="s">
-        <v>68</v>
-      </c>
-      <c r="Z5" s="34" t="s">
+      <c r="AD5" s="33" t="s">
+        <v>24</v>
+      </c>
+      <c r="AE5" s="33" t="s">
         <v>69</v>
       </c>
-      <c r="AA5" s="34" t="s">
-        <v>24</v>
-      </c>
-      <c r="AB5" s="33" t="s">
+      <c r="AF5" s="34" t="s">
         <v>70</v>
       </c>
-      <c r="AC5" s="33" t="s">
+      <c r="AG5" s="35" t="s">
+        <v>71</v>
+      </c>
+      <c r="AH5" s="36" t="s">
+        <v>72</v>
+      </c>
+      <c r="AI5" s="37" t="s">
+        <v>73</v>
+      </c>
+      <c r="AJ5" s="38" t="s">
+        <v>74</v>
+      </c>
+      <c r="AK5" s="32" t="s">
+        <v>75</v>
+      </c>
+      <c r="AL5" s="33" t="s">
+        <v>76</v>
+      </c>
+      <c r="AM5" s="33" t="s">
+        <v>77</v>
+      </c>
+      <c r="AN5" s="33" t="s">
+        <v>78</v>
+      </c>
+      <c r="AO5" s="33" t="s">
+        <v>79</v>
+      </c>
+      <c r="AP5" s="39" t="s">
+        <v>80</v>
+      </c>
+      <c r="AQ5" s="39" t="s">
+        <v>81</v>
+      </c>
+      <c r="AR5" s="39" t="s">
+        <v>82</v>
+      </c>
+      <c r="AS5" s="34" t="s">
+        <v>83</v>
+      </c>
+      <c r="AT5" s="34" t="s">
+        <v>84</v>
+      </c>
+      <c r="AU5" s="34" t="s">
+        <v>85</v>
+      </c>
+      <c r="AV5" s="33" t="s">
+        <v>86</v>
+      </c>
+      <c r="AW5" s="33" t="s">
+        <v>87</v>
+      </c>
+      <c r="AX5" s="34" t="s">
+        <v>88</v>
+      </c>
+      <c r="AY5" s="34" t="s">
+        <v>89</v>
+      </c>
+      <c r="AZ5" s="34" t="s">
+        <v>90</v>
+      </c>
+      <c r="BA5" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="BB5" s="40" t="s">
         <v>25</v>
       </c>
-      <c r="AD5" s="33" t="s">
+      <c r="BC5" s="40" t="s">
+        <v>92</v>
+      </c>
+      <c r="BD5" s="41" t="s">
         <v>26</v>
       </c>
-      <c r="AE5" s="33" t="s">
-        <v>71</v>
-      </c>
-      <c r="AF5" s="34" t="s">
-        <v>72</v>
-      </c>
-      <c r="AG5" s="35" t="s">
-        <v>73</v>
-      </c>
-      <c r="AH5" s="36" t="s">
-        <v>74</v>
-      </c>
-      <c r="AI5" s="37" t="s">
-        <v>75</v>
-      </c>
-      <c r="AJ5" s="38" t="s">
-        <v>76</v>
-      </c>
-      <c r="AK5" s="32" t="s">
-        <v>77</v>
-      </c>
-      <c r="AL5" s="33" t="s">
-        <v>78</v>
-      </c>
-      <c r="AM5" s="33" t="s">
-        <v>79</v>
-      </c>
-      <c r="AN5" s="33" t="s">
-        <v>80</v>
-      </c>
-      <c r="AO5" s="33" t="s">
-        <v>81</v>
-      </c>
-      <c r="AP5" s="39" t="s">
-        <v>82</v>
-      </c>
-      <c r="AQ5" s="39" t="s">
-        <v>83</v>
-      </c>
-      <c r="AR5" s="39" t="s">
-        <v>84</v>
-      </c>
-      <c r="AS5" s="34" t="s">
-        <v>85</v>
-      </c>
-      <c r="AT5" s="34" t="s">
-        <v>86</v>
-      </c>
-      <c r="AU5" s="34" t="s">
-        <v>87</v>
-      </c>
-      <c r="AV5" s="33" t="s">
-        <v>88</v>
-      </c>
-      <c r="AW5" s="33" t="s">
-        <v>89</v>
-      </c>
-      <c r="AX5" s="34" t="s">
-        <v>90</v>
-      </c>
-      <c r="AY5" s="34" t="s">
-        <v>91</v>
-      </c>
-      <c r="AZ5" s="34" t="s">
-        <v>92</v>
-      </c>
-      <c r="BA5" s="35" t="s">
+      <c r="BE5" s="41" t="s">
         <v>93</v>
       </c>
-      <c r="BB5" s="40" t="s">
+      <c r="BF5" s="40" t="s">
+        <v>94</v>
+      </c>
+      <c r="BG5" s="42" t="s">
+        <v>95</v>
+      </c>
+      <c r="BH5" s="40" t="s">
+        <v>96</v>
+      </c>
+      <c r="BI5" s="40" t="s">
         <v>27</v>
       </c>
-      <c r="BC5" s="40" t="s">
-        <v>94</v>
-      </c>
-      <c r="BD5" s="41" t="s">
+      <c r="BJ5" s="40" t="s">
+        <v>97</v>
+      </c>
+      <c r="BK5" s="43" t="s">
         <v>28</v>
       </c>
-      <c r="BE5" s="41" t="s">
-        <v>95</v>
-      </c>
-      <c r="BF5" s="40" t="s">
-        <v>96</v>
-      </c>
-      <c r="BG5" s="42" t="s">
-        <v>97</v>
-      </c>
-      <c r="BH5" s="40" t="s">
+      <c r="BL5" s="43" t="s">
         <v>98</v>
       </c>
-      <c r="BI5" s="40" t="s">
+      <c r="BM5" s="43" t="s">
         <v>29</v>
       </c>
-      <c r="BJ5" s="40" t="s">
+      <c r="BN5" s="43" t="s">
         <v>99</v>
       </c>
-      <c r="BK5" s="43" t="s">
+      <c r="BO5" s="43" t="s">
+        <v>100</v>
+      </c>
+      <c r="BP5" s="43" t="s">
+        <v>101</v>
+      </c>
+      <c r="BQ5" s="43" t="s">
+        <v>102</v>
+      </c>
+      <c r="BR5" s="43" t="s">
+        <v>103</v>
+      </c>
+      <c r="BS5" s="43" t="s">
         <v>30</v>
       </c>
-      <c r="BL5" s="43" t="s">
-        <v>100</v>
-      </c>
-      <c r="BM5" s="43" t="s">
-        <v>31</v>
-      </c>
-      <c r="BN5" s="43" t="s">
-        <v>101</v>
-      </c>
-      <c r="BO5" s="43" t="s">
-        <v>102</v>
-      </c>
-      <c r="BP5" s="43" t="s">
-        <v>103</v>
-      </c>
-      <c r="BQ5" s="43" t="s">
+      <c r="BT5" s="40" t="s">
         <v>104</v>
       </c>
-      <c r="BR5" s="43" t="s">
+      <c r="BU5" s="40" t="s">
         <v>105</v>
       </c>
-      <c r="BS5" s="43" t="s">
+      <c r="BV5" s="40" t="s">
+        <v>106</v>
+      </c>
+      <c r="BW5" s="40" t="s">
+        <v>107</v>
+      </c>
+      <c r="BX5" s="40" t="s">
+        <v>108</v>
+      </c>
+      <c r="BY5" s="40" t="s">
+        <v>109</v>
+      </c>
+      <c r="BZ5" s="40" t="s">
+        <v>110</v>
+      </c>
+      <c r="CA5" s="40" t="s">
+        <v>111</v>
+      </c>
+      <c r="CB5" s="40" t="s">
+        <v>112</v>
+      </c>
+      <c r="CC5" s="43" t="s">
+        <v>113</v>
+      </c>
+      <c r="CD5" s="43" t="s">
+        <v>114</v>
+      </c>
+      <c r="CE5" s="43" t="s">
+        <v>115</v>
+      </c>
+      <c r="CF5" s="43" t="s">
+        <v>116</v>
+      </c>
+      <c r="CG5" s="43" t="s">
+        <v>117</v>
+      </c>
+      <c r="CH5" s="43" t="s">
+        <v>118</v>
+      </c>
+      <c r="CI5" s="43" t="s">
+        <v>119</v>
+      </c>
+      <c r="CJ5" s="43" t="s">
+        <v>120</v>
+      </c>
+      <c r="CK5" s="44" t="s">
+        <v>121</v>
+      </c>
+      <c r="CL5" s="44" t="s">
+        <v>122</v>
+      </c>
+      <c r="CM5" s="44" t="s">
+        <v>123</v>
+      </c>
+      <c r="CN5" s="44" t="s">
+        <v>124</v>
+      </c>
+      <c r="CO5" s="44" t="s">
+        <v>125</v>
+      </c>
+      <c r="CP5" s="44" t="s">
+        <v>126</v>
+      </c>
+      <c r="CQ5" s="44" t="s">
+        <v>127</v>
+      </c>
+      <c r="CR5" s="44" t="s">
+        <v>128</v>
+      </c>
+      <c r="CS5" s="45" t="s">
+        <v>129</v>
+      </c>
+      <c r="CT5" s="46" t="s">
+        <v>130</v>
+      </c>
+      <c r="CU5" s="46" t="s">
         <v>32</v>
       </c>
-      <c r="BT5" s="40" t="s">
-        <v>106</v>
-      </c>
-      <c r="BU5" s="40" t="s">
-        <v>107</v>
-      </c>
-      <c r="BV5" s="40" t="s">
-        <v>108</v>
-      </c>
-      <c r="BW5" s="40" t="s">
-        <v>109</v>
-      </c>
-      <c r="BX5" s="40" t="s">
-        <v>110</v>
-      </c>
-      <c r="BY5" s="40" t="s">
-        <v>111</v>
-      </c>
-      <c r="BZ5" s="40" t="s">
-        <v>112</v>
-      </c>
-      <c r="CA5" s="40" t="s">
-        <v>113</v>
-      </c>
-      <c r="CB5" s="40" t="s">
-        <v>114</v>
-      </c>
-      <c r="CC5" s="43" t="s">
-        <v>115</v>
-      </c>
-      <c r="CD5" s="43" t="s">
-        <v>116</v>
-      </c>
-      <c r="CE5" s="43" t="s">
-        <v>117</v>
-      </c>
-      <c r="CF5" s="43" t="s">
-        <v>118</v>
-      </c>
-      <c r="CG5" s="43" t="s">
-        <v>119</v>
-      </c>
-      <c r="CH5" s="43" t="s">
-        <v>120</v>
-      </c>
-      <c r="CI5" s="43" t="s">
-        <v>121</v>
-      </c>
-      <c r="CJ5" s="43" t="s">
-        <v>122</v>
-      </c>
-      <c r="CK5" s="44" t="s">
-        <v>123</v>
-      </c>
-      <c r="CL5" s="44" t="s">
-        <v>124</v>
-      </c>
-      <c r="CM5" s="44" t="s">
-        <v>125</v>
-      </c>
-      <c r="CN5" s="44" t="s">
-        <v>126</v>
-      </c>
-      <c r="CO5" s="44" t="s">
-        <v>127</v>
-      </c>
-      <c r="CP5" s="44" t="s">
-        <v>128</v>
-      </c>
-      <c r="CQ5" s="44" t="s">
-        <v>129</v>
-      </c>
-      <c r="CR5" s="44" t="s">
-        <v>130</v>
-      </c>
-      <c r="CS5" s="45" t="s">
+      <c r="CW5" s="48" t="s">
         <v>131</v>
       </c>
-      <c r="CT5" s="46" t="s">
+      <c r="CX5" s="48" t="s">
         <v>132</v>
       </c>
-      <c r="CU5" s="46" t="s">
-        <v>34</v>
-      </c>
-      <c r="CW5" s="48" t="s">
+      <c r="CY5" s="48" t="s">
         <v>133</v>
       </c>
-      <c r="CX5" s="48" t="s">
+      <c r="CZ5" s="48" t="s">
         <v>134</v>
       </c>
-      <c r="CY5" s="48" t="s">
+      <c r="DA5" s="48" t="s">
         <v>135</v>
       </c>
-      <c r="CZ5" s="48" t="s">
+      <c r="DB5" s="48" t="s">
         <v>136</v>
-      </c>
-      <c r="DA5" s="48" t="s">
-        <v>137</v>
-      </c>
-      <c r="DB5" s="48" t="s">
-        <v>138</v>
       </c>
     </row>
   </sheetData>
@@ -12116,29 +12272,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="a692c345-fe85-4329-9b32-d42bd9ce568f" xsi:nil="true"/>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8bd2d439-aea9-4035-b4e9-8ef80bf90cb6">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <Tags xmlns="8bd2d439-aea9-4035-b4e9-8ef80bf90cb6" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100C8F66A14B1547C4C9D7BAD680DA88C61" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="002aa387ec480ae932de6dc40f75283b">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="8bd2d439-aea9-4035-b4e9-8ef80bf90cb6" xmlns:ns3="a692c345-fe85-4329-9b32-d42bd9ce568f" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d9230dd1b22e970ac78e7c979b83a161" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -12368,27 +12501,30 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{06837ADB-92C0-45FC-8A3D-6A37CAE6A84A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="a692c345-fe85-4329-9b32-d42bd9ce568f"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="8bd2d439-aea9-4035-b4e9-8ef80bf90cb6"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{92CCEDE5-69F5-4261-9C3E-4530177D980C}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="a692c345-fe85-4329-9b32-d42bd9ce568f" xsi:nil="true"/>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8bd2d439-aea9-4035-b4e9-8ef80bf90cb6">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <Tags xmlns="8bd2d439-aea9-4035-b4e9-8ef80bf90cb6" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1CEA9648-8367-47DC-ADE8-4476C3E6331A}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -12406,4 +12542,24 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{92CCEDE5-69F5-4261-9C3E-4530177D980C}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{06837ADB-92C0-45FC-8A3D-6A37CAE6A84A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="a692c345-fe85-4329-9b32-d42bd9ce568f"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="8bd2d439-aea9-4035-b4e9-8ef80bf90cb6"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>